--- a/surveys/biochar_survey_december_2025.xlsx
+++ b/surveys/biochar_survey_december_2025.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD7DBC87-79F7-4317-8581-D00659013AB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F12D2D41-994E-45E4-9336-C8146BD259CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2461" uniqueCount="810">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2463" uniqueCount="806">
   <si>
     <t>type</t>
   </si>
@@ -77,19 +77,19 @@
     <t>focal_point_name</t>
   </si>
   <si>
-    <t>What is the name of the Focal Point (Interviewer)?</t>
+    <t>A.1) What is the name of the Focal Point (Interviewer)?</t>
   </si>
   <si>
     <t>farmer_name</t>
   </si>
   <si>
-    <t>What is the name of the farmer?</t>
+    <t>A.2) What is the name of the farmer?</t>
   </si>
   <si>
     <t>farmer_id</t>
   </si>
   <si>
-    <t>What is the ID of the farmer?</t>
+    <t>A.3) What is the ID of the farmer?</t>
   </si>
   <si>
     <t>select_one mc51t23</t>
@@ -98,7 +98,7 @@
     <t>farmer_cohort</t>
   </si>
   <si>
-    <t>To which cohort does the farmer belong to?</t>
+    <t>A.4) To which cohort does the farmer belong to?</t>
   </si>
   <si>
     <t>end_group</t>
@@ -116,13 +116,13 @@
     <t>growed_and_harvested_produce</t>
   </si>
   <si>
-    <t>What kinds of produce/crops did you grow and what did you harvest from the wild the most recent growing season (rainy season)?</t>
+    <t>B.1) What kinds of produce/crops did you grow and what did you harvest from the wild the most recent growing season (rainy season)?</t>
   </si>
   <si>
     <t>other_produced_crops</t>
   </si>
   <si>
-    <t>Please specify the produce/crops:</t>
+    <t>B.1.a) Please specify the produce/crops:</t>
   </si>
   <si>
     <t>selected(${growed_and_harvested_produce}, 'other')</t>
@@ -131,7 +131,7 @@
     <t>group_cereals</t>
   </si>
   <si>
-    <t>If you grew cereals, what kinds?</t>
+    <t>B.2) If you grew cereals, what kinds?</t>
   </si>
   <si>
     <t>selected(${growed_and_harvested_produce}, 'cereals')</t>
@@ -275,7 +275,7 @@
     <t>group_groundnut</t>
   </si>
   <si>
-    <t>If you grew groundnuts in the most recent growing season, what type?</t>
+    <t>B.3) If you grew groundnuts in the most recent growing season, what type?</t>
   </si>
   <si>
     <t>selected(${growed_and_harvested_produce}, 'legumes')</t>
@@ -356,7 +356,7 @@
     <t>group_vegetable</t>
   </si>
   <si>
-    <t>If you cultivated any vegetable crops in the most recent rainy season, which ones?</t>
+    <t>B.4) If you cultivated any vegetable crops in the most recent rainy season, which ones?</t>
   </si>
   <si>
     <t>selected(${growed_and_harvested_produce}, 'vegetables')</t>
@@ -725,7 +725,7 @@
     <t>group_tuber</t>
   </si>
   <si>
-    <t>If you cultivated tuber crops this past rainy season, which ones?</t>
+    <t>B.5) If you cultivated tuber crops this past rainy season, which ones?</t>
   </si>
   <si>
     <t>selected(${growed_and_harvested_produce}, 'tubers')</t>
@@ -806,7 +806,7 @@
     <t>group_wild_fruit</t>
   </si>
   <si>
-    <t>If you harvested any wild fruits when they were last fruiting, which ones?</t>
+    <t>B.6) If you harvested any wild fruits when they were last fruiting, which ones?</t>
   </si>
   <si>
     <t>selected(${growed_and_harvested_produce}, 'wild_fruits')</t>
@@ -887,7 +887,7 @@
     <t>group_fruit_tree</t>
   </si>
   <si>
-    <t>If you have fruit trees, which ones?</t>
+    <t>B.7) If you have fruit trees, which ones?</t>
   </si>
   <si>
     <t>selected(${growed_and_harvested_produce}, 'fruit_trees')</t>
@@ -1061,843 +1061,837 @@
     <t>fruit_tree_info_pineapples_1_sellingblockage</t>
   </si>
   <si>
+    <t>group_wc4ky54</t>
+  </si>
+  <si>
+    <t>Effects of Biochar on Farming</t>
+  </si>
+  <si>
+    <t>select_one oc39z90</t>
+  </si>
+  <si>
+    <t>made_biochar</t>
+  </si>
+  <si>
+    <t>C.1) Since you were trained in making biochar, have you made it?</t>
+  </si>
+  <si>
+    <t>select_one ab5ut15</t>
+  </si>
+  <si>
+    <t>used_on_crops</t>
+  </si>
+  <si>
+    <t>C.1.a) Did you use it on crops?</t>
+  </si>
+  <si>
+    <t>${made_biochar} = 'yes'</t>
+  </si>
+  <si>
+    <t>group_biochar</t>
+  </si>
+  <si>
+    <t>C.1.b) What crops did you use it on?</t>
+  </si>
+  <si>
+    <t>${used_on_crops} = 'yes'</t>
+  </si>
+  <si>
+    <t>biochar_info_maize_1</t>
+  </si>
+  <si>
+    <t>selected(${growed_and_harvested_produce}, 'cereals') and ${cereals_info_maize_1_harvested} = 'yes'</t>
+  </si>
+  <si>
+    <t>biochar_info_maize_1_note</t>
+  </si>
+  <si>
+    <t>w1</t>
+  </si>
+  <si>
+    <t>select_one ab3lr32</t>
+  </si>
+  <si>
+    <t>biochar_info_maize_1_used</t>
+  </si>
+  <si>
+    <t>&lt;span&gt;Did you apply biochar on the plot this crop was grown?&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>select_multiple pp0mv31</t>
+  </si>
+  <si>
+    <t>biochar_info_maize_1_seasons</t>
+  </si>
+  <si>
+    <t>&lt;span&gt;During which seasons?&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>biochar_info_rice_1</t>
+  </si>
+  <si>
+    <t>selected(${growed_and_harvested_produce}, 'cereals') and ${cereals_info_rice_1_harvested} = 'yes'</t>
+  </si>
+  <si>
+    <t>biochar_info_rice_1_note</t>
+  </si>
+  <si>
+    <t>biochar_info_rice_1_used</t>
+  </si>
+  <si>
+    <t>biochar_info_rice_1_seasons</t>
+  </si>
+  <si>
+    <t>biochar_info_findi_1</t>
+  </si>
+  <si>
+    <t> </t>
+  </si>
+  <si>
+    <t>selected(${growed_and_harvested_produce}, 'cereals') and ${cereals_info_findi_1_harvested} = 'yes'</t>
+  </si>
+  <si>
+    <t>biochar_info_findi_1_note</t>
+  </si>
+  <si>
+    <t>biochar_info_findi_1_used</t>
+  </si>
+  <si>
+    <t>biochar_info_findi_1_seasons</t>
+  </si>
+  <si>
+    <t>During which seasons?</t>
+  </si>
+  <si>
+    <t>biochar_info_millet_1</t>
+  </si>
+  <si>
+    <t>selected(${growed_and_harvested_produce}, 'cereals') and ${cereals_info_millet_1_harvested} = 'yes'</t>
+  </si>
+  <si>
+    <t>biochar_info_millet_1_note</t>
+  </si>
+  <si>
+    <t>biochar_info_millet_1_used</t>
+  </si>
+  <si>
+    <t>biochar_info_millet_1_seasons</t>
+  </si>
+  <si>
+    <t>biochar_info_burucoorse_1</t>
+  </si>
+  <si>
+    <t>selected(${growed_and_harvested_produce}, 'legumes') and ${groundnut_info_burucoorse_1_harvested} = 'yes'</t>
+  </si>
+  <si>
+    <t>biochar_info_burucoorse_1_note</t>
+  </si>
+  <si>
+    <t>biochar_info_burucoorse_1_used</t>
+  </si>
+  <si>
+    <t>biochar_info_burucoorse_1_seasons</t>
+  </si>
+  <si>
+    <t>biochar_info_chorrpoor_1</t>
+  </si>
+  <si>
+    <t>selected(${growed_and_harvested_produce}, 'legumes') and ${groundnut_info_chorrpoor_1_harvested} = 'yes'</t>
+  </si>
+  <si>
+    <t>biochar_info_chorrpoor_1_note</t>
+  </si>
+  <si>
+    <t>biochar_info_chorrpoor_1_used</t>
+  </si>
+  <si>
+    <t>biochar_info_chorrpoor_1_seasons</t>
+  </si>
+  <si>
+    <t>biochar_info_arssama_1</t>
+  </si>
+  <si>
+    <t>selected(${growed_and_harvested_produce}, 'legumes') and ${groundnut_info_arssama_1_harvested} = 'yes'</t>
+  </si>
+  <si>
+    <t>biochar_info_arssama_1_note</t>
+  </si>
+  <si>
+    <t>biochar_info_arssama_1_used</t>
+  </si>
+  <si>
+    <t>biochar_info_arssama_1_seasons</t>
+  </si>
+  <si>
+    <t>biochar_info_mangoes_1</t>
+  </si>
+  <si>
+    <t>selected(${growed_and_harvested_produce}, 'fruit_trees') and ${fruit_tree_info_mangoes_1_harvested} = 'yes'</t>
+  </si>
+  <si>
+    <t>biochar_info_mangoes_1_note</t>
+  </si>
+  <si>
+    <t>biochar_info_mangoes_1_used</t>
+  </si>
+  <si>
+    <t>biochar_info_mangoes_1_seasons</t>
+  </si>
+  <si>
+    <t>biochar_info_bananas_1</t>
+  </si>
+  <si>
+    <t>selected(${growed_and_harvested_produce}, 'fruit_trees') and ${fruit_tree_info_bananas_1_harvested} = 'yes'</t>
+  </si>
+  <si>
+    <t>biochar_info_bananas_1_note</t>
+  </si>
+  <si>
+    <t>biochar_info_bananas_1_used</t>
+  </si>
+  <si>
+    <t>biochar_info_bananas_1_seasons</t>
+  </si>
+  <si>
+    <t>biochar_info_oranges_1</t>
+  </si>
+  <si>
+    <t>selected(${growed_and_harvested_produce}, 'fruit_trees') and ${fruit_tree_info_oranges_1_harvested} = 'yes'</t>
+  </si>
+  <si>
+    <t>biochar_info_oranges_1_note</t>
+  </si>
+  <si>
+    <t>biochar_info_oranges_1_used</t>
+  </si>
+  <si>
+    <t>biochar_info_oranges_1_seasons</t>
+  </si>
+  <si>
+    <t>biochar_info_lemons_1</t>
+  </si>
+  <si>
+    <t>selected(${growed_and_harvested_produce}, 'fruit_trees') and ${fruit_tree_info_lemons_1_harvested} = 'yes'</t>
+  </si>
+  <si>
+    <t>biochar_info_lemons_1_note</t>
+  </si>
+  <si>
+    <t>biochar_info_lemons_1_used</t>
+  </si>
+  <si>
+    <t>biochar_info_lemons_1_seasons</t>
+  </si>
+  <si>
+    <t>biochar_info_papayas_1</t>
+  </si>
+  <si>
+    <t>selected(${growed_and_harvested_produce}, 'fruit_trees') and ${fruit_tree_info_papayas_1_harvested} = 'yes'</t>
+  </si>
+  <si>
+    <t>biochar_info_papayas_1_note</t>
+  </si>
+  <si>
+    <t>biochar_info_papayas_1_used</t>
+  </si>
+  <si>
+    <t>biochar_info_papayas_1_seasons</t>
+  </si>
+  <si>
+    <t>biochar_info_guavas_1</t>
+  </si>
+  <si>
+    <t>selected(${growed_and_harvested_produce}, 'fruit_trees') and ${fruit_tree_info_guavas_1_harvested} = 'yes'</t>
+  </si>
+  <si>
+    <t>biochar_info_guavas_1_note</t>
+  </si>
+  <si>
+    <t>biochar_info_guavas_1_used</t>
+  </si>
+  <si>
+    <t>biochar_info_guavas_1_seasons</t>
+  </si>
+  <si>
+    <t>biochar_info_pineapples_1</t>
+  </si>
+  <si>
+    <t>selected(${growed_and_harvested_produce}, 'fruit_trees') and ${fruit_tree_info_pineapples_1_harvested} = 'yes'</t>
+  </si>
+  <si>
+    <t>biochar_info_pineapples_1_note</t>
+  </si>
+  <si>
+    <t>biochar_info_pineapples_1_used</t>
+  </si>
+  <si>
+    <t>biochar_info_pineapples_1_seasons</t>
+  </si>
+  <si>
+    <t>biochar_info_onions_1</t>
+  </si>
+  <si>
+    <t>selected(${growed_and_harvested_produce}, 'vegetables') and ${vegetable_info_onions_1_harvested} = 'yes'</t>
+  </si>
+  <si>
+    <t>biochar_info_onions_1_note</t>
+  </si>
+  <si>
+    <t>biochar_info_onions_1_used</t>
+  </si>
+  <si>
+    <t>biochar_info_onions_1_seasons</t>
+  </si>
+  <si>
+    <t>biochar_info_carrots_1</t>
+  </si>
+  <si>
+    <t>selected(${growed_and_harvested_produce}, 'vegetables') and ${vegetable_info_carrots_1_harvested} = 'yes'</t>
+  </si>
+  <si>
+    <t>biochar_info_carrots_1_note</t>
+  </si>
+  <si>
+    <t>biochar_info_carrots_1_used</t>
+  </si>
+  <si>
+    <t>biochar_info_carrots_1_seasons</t>
+  </si>
+  <si>
+    <t>biochar_info_okra_1</t>
+  </si>
+  <si>
+    <t>selected(${growed_and_harvested_produce}, 'vegetables') and ${vegetable_info_okra_1_harvested} = 'yes'</t>
+  </si>
+  <si>
+    <t>biochar_info_okra_1_note</t>
+  </si>
+  <si>
+    <t>biochar_info_okra_1_used</t>
+  </si>
+  <si>
+    <t>biochar_info_okra_1_seasons</t>
+  </si>
+  <si>
+    <t>biochar_info_cabbage_1</t>
+  </si>
+  <si>
+    <t>selected(${growed_and_harvested_produce}, 'vegetables') and ${vegetable_info_cabagge_1_harvested} = 'yes'</t>
+  </si>
+  <si>
+    <t>biochar_info_cabbage_1_note</t>
+  </si>
+  <si>
+    <t>biochar_info_cabbage_1_used</t>
+  </si>
+  <si>
+    <t>biochar_info_cabbage_1_seasons</t>
+  </si>
+  <si>
+    <t>biochar_info_eggplant_1</t>
+  </si>
+  <si>
+    <t>selected(${growed_and_harvested_produce}, 'vegetables') and ${vegetable_info_eggplant_1_harvested} = 'yes'</t>
+  </si>
+  <si>
+    <t>biochar_info_eggplant_1_note</t>
+  </si>
+  <si>
+    <t>biochar_info_eggplant_1_used</t>
+  </si>
+  <si>
+    <t>biochar_info_eggplant_1_seasons</t>
+  </si>
+  <si>
+    <t>biochar_info_cucumber_1</t>
+  </si>
+  <si>
+    <t>selected(${growed_and_harvested_produce}, 'vegetables') and ${vegetable_info_cucumber_1_harvested} = 'yes'</t>
+  </si>
+  <si>
+    <t>biochar_info_cucumber_1_note</t>
+  </si>
+  <si>
+    <t>biochar_info_cucumber_1_used</t>
+  </si>
+  <si>
+    <t>biochar_info_cucumber_1_seasons</t>
+  </si>
+  <si>
+    <t>biochar_info_green_pepper_1</t>
+  </si>
+  <si>
+    <t>selected(${growed_and_harvested_produce}, 'vegetables') and ${vegetable_info_green_pepper_1_harvested} = 'yes'</t>
+  </si>
+  <si>
+    <t>biochar_info_green_pepper_1_note</t>
+  </si>
+  <si>
+    <t>##### Green Pepper</t>
+  </si>
+  <si>
+    <t>biochar_info_green_pepper_1_used</t>
+  </si>
+  <si>
+    <t>biochar_info_green_pepper_1_seasons</t>
+  </si>
+  <si>
+    <t>biochar_info_yellow_pepper_1</t>
+  </si>
+  <si>
+    <t>selected(${growed_and_harvested_produce}, 'vegetables') and ${vegetable_info_yellow_pepper_1_harvested} = 'yes'</t>
+  </si>
+  <si>
+    <t>biochar_info_yellow_pepper_1_note</t>
+  </si>
+  <si>
+    <t>##### Yellow Pepper</t>
+  </si>
+  <si>
+    <t>biochar_info_yellow_pepper_1_used</t>
+  </si>
+  <si>
+    <t>biochar_info_yellow_pepper_1_seasons</t>
+  </si>
+  <si>
+    <t>biochar_info_brown_pepper_1</t>
+  </si>
+  <si>
+    <t>selected(${growed_and_harvested_produce}, 'vegetables') and ${vegetable_info_brown_pepper_1_harvested} = 'yes'</t>
+  </si>
+  <si>
+    <t>biochar_info_brown_pepper_1_note</t>
+  </si>
+  <si>
+    <t>##### Brown Pepper</t>
+  </si>
+  <si>
+    <t>biochar_info_brown_pepper_1_used</t>
+  </si>
+  <si>
+    <t>biochar_info_brown_pepper_1_seasons</t>
+  </si>
+  <si>
+    <t>biochar_info_tomatoes_1</t>
+  </si>
+  <si>
+    <t>selected(${growed_and_harvested_produce}, 'vegetables') and ${vegetable_info_tomatoes_1_harvested} = 'yes'</t>
+  </si>
+  <si>
+    <t>biochar_info_tomatoes_1_note</t>
+  </si>
+  <si>
+    <t>biochar_info_tomatoes_1_used</t>
+  </si>
+  <si>
+    <t>biochar_info_tomatoes_1_seasons</t>
+  </si>
+  <si>
+    <t>biochar_info_bitter_tomatoes_1</t>
+  </si>
+  <si>
+    <t>selected(${growed_and_harvested_produce}, 'vegetables') and ${vegetable_info_bitter_tomatoes_1_harvested} = 'yes'</t>
+  </si>
+  <si>
+    <t>biochar_info_bitter_tomatoes_1_note</t>
+  </si>
+  <si>
+    <t>biochar_info_bitter_tomatoes_1_used</t>
+  </si>
+  <si>
+    <t>biochar_info_bitter_tomatoes_1_seasons</t>
+  </si>
+  <si>
+    <t>biochar_info_chili_pepper_1</t>
+  </si>
+  <si>
+    <t>selected(${growed_and_harvested_produce}, 'vegetables') and ${vegetable_info_chilli_pepper_1_harvested} = 'yes'</t>
+  </si>
+  <si>
+    <t>biochar_info_chili_pepper_1_note</t>
+  </si>
+  <si>
+    <t>biochar_info_chili_pepper_1_used</t>
+  </si>
+  <si>
+    <t>biochar_info_chili_pepper_1_seasons</t>
+  </si>
+  <si>
+    <t>biochar_info_sweet_pepper_1</t>
+  </si>
+  <si>
+    <t>selected(${growed_and_harvested_produce}, 'vegetables') and ${vegetable_info_sweet_pepper_1_harvested} = 'yes'</t>
+  </si>
+  <si>
+    <t>biochar_info_sweet_pepper_1_note</t>
+  </si>
+  <si>
+    <t>biochar_info_sweet_pepper_1_used</t>
+  </si>
+  <si>
+    <t>biochar_info_sweet_pepper_1_seasons</t>
+  </si>
+  <si>
+    <t>biochar_info_lettuce_1</t>
+  </si>
+  <si>
+    <t>selected(${growed_and_harvested_produce}, 'vegetables') and ${vegetable_info_lettuce_1_harvested} = 'yes'</t>
+  </si>
+  <si>
+    <t>biochar_info_lettuce_1_note</t>
+  </si>
+  <si>
+    <t>biochar_info_lettuce_1_used</t>
+  </si>
+  <si>
+    <t>biochar_info_lettuce_1_seasons</t>
+  </si>
+  <si>
+    <t>biochar_info_watermelon_1</t>
+  </si>
+  <si>
+    <t>selected(${growed_and_harvested_produce}, 'vegetables') and ${vegetable_info_watermelon_1_harvested} = 'yes'</t>
+  </si>
+  <si>
+    <t>biochar_info_watermelon_1_note</t>
+  </si>
+  <si>
+    <t>biochar_info_watermelon_1_used</t>
+  </si>
+  <si>
+    <t>biochar_info_watermelon_1_seasons</t>
+  </si>
+  <si>
+    <t>biochar_info_cassava_1</t>
+  </si>
+  <si>
+    <t>selected(${growed_and_harvested_produce}, 'tubers') and ${tuber_info_cassava_1_harvested} = 'yes'</t>
+  </si>
+  <si>
+    <t>biochar_info_cassava_1_note</t>
+  </si>
+  <si>
+    <t>biochar_info_cassava_1_used</t>
+  </si>
+  <si>
+    <t>biochar_info_cassava_1_seasons</t>
+  </si>
+  <si>
+    <t>biochar_info_sweet_potato_1</t>
+  </si>
+  <si>
+    <t>selected(${growed_and_harvested_produce}, 'tubers') and ${tuber_info_sweetpotato_1_harvested} = 'yes'</t>
+  </si>
+  <si>
+    <t>biochar_info_sweet_potato_1_note</t>
+  </si>
+  <si>
+    <t>biochar_info_sweet_potato_1_used</t>
+  </si>
+  <si>
+    <t>biochar_info_sweet_potato_1_seasons</t>
+  </si>
+  <si>
+    <t>biochar_info_yams_1</t>
+  </si>
+  <si>
+    <t>selected(${growed_and_harvested_produce}, 'tubers') and ${tuber_info_yams_1_harvested} = 'yes'</t>
+  </si>
+  <si>
+    <t>biochar_info_yams_1_note</t>
+  </si>
+  <si>
+    <t>biochar_info_yams_1_used</t>
+  </si>
+  <si>
+    <t>biochar_info_yams_1_seasons</t>
+  </si>
+  <si>
+    <t>boichar_info_end_label</t>
+  </si>
+  <si>
+    <t>Continue:</t>
+  </si>
+  <si>
+    <t>select_one gc78m99</t>
+  </si>
+  <si>
+    <t>biochar_crop_usage</t>
+  </si>
+  <si>
+    <t>C.2) For the crops where you used biochar, did you use it equally on the entire crop or only on part of it?</t>
+  </si>
+  <si>
+    <t>select_multiple hs11j39</t>
+  </si>
+  <si>
+    <t>biochar_application</t>
+  </si>
+  <si>
+    <t>C.3) If you used biochar on your crops, how did you apply it?</t>
+  </si>
+  <si>
+    <t>select_one ve5vd39</t>
+  </si>
+  <si>
+    <t>biochar_application_interval</t>
+  </si>
+  <si>
+    <t>C.4) During the seasons you applied biochar, how often did you apply it?</t>
+  </si>
+  <si>
+    <t>most_affected_crop</t>
+  </si>
+  <si>
+    <t>C.5) If you used biochar on more than one crop, for which crops did it make the biggest difference? (Leave empty when cannot judge)</t>
+  </si>
+  <si>
+    <t>select_multiple yw1ml89</t>
+  </si>
+  <si>
+    <t>fertilizer_before_biochar</t>
+  </si>
+  <si>
+    <t>C.6) Before using biochar, did you use fertilizer?</t>
+  </si>
+  <si>
+    <t>select_multiple td2jb01</t>
+  </si>
+  <si>
+    <t>fertilizers_used_with_biochar</t>
+  </si>
+  <si>
+    <t>C.7) When you applied biochar, did you also use another soil fertilizer in addition to biochar? (Select all that apply)</t>
+  </si>
+  <si>
+    <t>select_multiple pc1lg93</t>
+  </si>
+  <si>
+    <t>fertilizers_used_before_biocha</t>
+  </si>
+  <si>
+    <t>C.8) What kind of fertilizer did you use before biochar? (Select all that apply)</t>
+  </si>
+  <si>
+    <t>group_ad9ws92</t>
+  </si>
+  <si>
+    <t>Observation and Results</t>
+  </si>
+  <si>
+    <t>select_one sj05t62</t>
+  </si>
+  <si>
+    <t>biochar_used_on_different_area</t>
+  </si>
+  <si>
+    <t>D.1) On the crops where you used biochar, did you use it on some plots and not one other plots?</t>
+  </si>
+  <si>
+    <t>select_one xj9am89</t>
+  </si>
+  <si>
+    <t>noticed_difference</t>
+  </si>
+  <si>
+    <t>D.2) Did  you notice any difference between the plots where you used biochar and the plots where you did not?</t>
+  </si>
+  <si>
+    <t>${biochar_used_on_different_area} = 'yes'</t>
+  </si>
+  <si>
+    <t>select_one hd83z15</t>
+  </si>
+  <si>
+    <t>significance_difference</t>
+  </si>
+  <si>
+    <t>D.2.a) How significant was the difference?</t>
+  </si>
+  <si>
+    <t>${noticed_difference} = 'yes'</t>
+  </si>
+  <si>
+    <t>select_one hy91q54</t>
+  </si>
+  <si>
+    <t>noticeable_difference_in_yield</t>
+  </si>
+  <si>
+    <t>D.3) For crops for which you used biochar over the entire plot, can you judge whether there was a different in the yield from the crop was last cultivated, without biochar?</t>
+  </si>
+  <si>
+    <t>select_one ln0re11</t>
+  </si>
+  <si>
+    <t>significance_difference_yield</t>
+  </si>
+  <si>
+    <t>D.3.a) How significant was the difference in yield volume to the last yield without biochar?</t>
+  </si>
+  <si>
+    <t>${noticeable_difference_in_yield} = 'yes'</t>
+  </si>
+  <si>
+    <t>D.4) If you used biochar on more than one crop, for which crops did it make the biggest difference? (Leave empty when cannot judge)</t>
+  </si>
+  <si>
+    <t>select_one po8ix91</t>
+  </si>
+  <si>
+    <t>wants_to_continue_biochar</t>
+  </si>
+  <si>
+    <t>D.5) Do you plan to continue making and using biochar?</t>
+  </si>
+  <si>
+    <t>reason_why_stopping_biochar</t>
+  </si>
+  <si>
+    <t>D.5.a) Why do you not plan to continue making biochar</t>
+  </si>
+  <si>
+    <t>${wants_to_continue_biochar} = 'no'</t>
+  </si>
+  <si>
+    <t>select_multiple bx92j53</t>
+  </si>
+  <si>
+    <t>simplification_for_biochar_use</t>
+  </si>
+  <si>
+    <t>D.6) What would make it easier for you to use biochar in future seasons?</t>
+  </si>
+  <si>
+    <t>specified_simplifications</t>
+  </si>
+  <si>
+    <t>D.6.a) Please specify what would make it easier:</t>
+  </si>
+  <si>
+    <t>selected(${simplification_for_biochar_use}, 'other')</t>
+  </si>
+  <si>
+    <t>select_one sl9eb19</t>
+  </si>
+  <si>
+    <t>would_purchase_biochar</t>
+  </si>
+  <si>
+    <t>D.7) Would you purchase biochar if it were available?</t>
+  </si>
+  <si>
+    <t>select_multiple rm9rw73</t>
+  </si>
+  <si>
+    <t>why_not_purchase_biochar</t>
+  </si>
+  <si>
+    <t>D.7.a) Why not?</t>
+  </si>
+  <si>
+    <t>${would_purchase_biochar} = 'no'</t>
+  </si>
+  <si>
+    <t>specification_why_not_purchase</t>
+  </si>
+  <si>
+    <t>D.7.b) Please specify why not:</t>
+  </si>
+  <si>
+    <t>selected(${why_not_purchase_biochar}, 'other')</t>
+  </si>
+  <si>
+    <t>group_go5wl54</t>
+  </si>
+  <si>
+    <t>Assessment of Biochar</t>
+  </si>
+  <si>
+    <t>biochar_impact_rating</t>
+  </si>
+  <si>
+    <t>biochar_impact_rating_note</t>
+  </si>
+  <si>
+    <t>Rate the impact of biochar on the following aspects:</t>
+  </si>
+  <si>
+    <t>select_one xk6do75</t>
+  </si>
+  <si>
+    <t>Soil_Fertility</t>
+  </si>
+  <si>
+    <t>E.1) Soil Fertility</t>
+  </si>
+  <si>
+    <t>Crop_Health</t>
+  </si>
+  <si>
+    <t>E.2) Crop Health</t>
+  </si>
+  <si>
+    <t>Water_Retention</t>
+  </si>
+  <si>
+    <t>E.3) Water Retention</t>
+  </si>
+  <si>
+    <t>biochar_impact_rating_end_note</t>
+  </si>
+  <si>
+    <t>select_one cx3zq25</t>
+  </si>
+  <si>
+    <t>overall_satisfaction_rating</t>
+  </si>
+  <si>
+    <t>E.4) Rate your overall satisfaction with the results of using Biochar</t>
+  </si>
+  <si>
+    <t>group_gr3wz63</t>
+  </si>
+  <si>
+    <t>Final Questions</t>
+  </si>
+  <si>
+    <t>select_multiple rx5ov52</t>
+  </si>
+  <si>
+    <t>preferred_data</t>
+  </si>
+  <si>
+    <t>F.1) If you could store and analyze data about your crops and yields, what kind of data would you like to have?</t>
+  </si>
+  <si>
+    <t>specified_preferred_data</t>
+  </si>
+  <si>
+    <t>F.1.a) Please specify the data:</t>
+  </si>
+  <si>
+    <t>selected(${preferred_data}, 'other')</t>
+  </si>
+  <si>
     <t>select_multiple rd0qj47</t>
   </si>
   <si>
     <t>help_to_excess_produce</t>
   </si>
   <si>
-    <t>If you had harvest that was spoiled, wasted, or not harvest because it was in excess, what might help you use your excess produce better?</t>
+    <t>F.2) If you had harvest that was spoiled, wasted, or not harvest because it was in excess, what might help you use your excess produce better?</t>
   </si>
   <si>
     <t>specify_help</t>
   </si>
   <si>
-    <t>Please specify:</t>
+    <t>F.2.a) Please specify:</t>
   </si>
   <si>
     <t>selected(${help_to_excess_produce}, 'other')</t>
   </si>
   <si>
-    <t>group_wc4ky54</t>
-  </si>
-  <si>
-    <t>Effects of Biochar on Farming</t>
-  </si>
-  <si>
-    <t>select_one oc39z90</t>
-  </si>
-  <si>
-    <t>made_biochar</t>
-  </si>
-  <si>
-    <t>Since you were trained in making biochar, have you made it?</t>
-  </si>
-  <si>
-    <t>select_one ab5ut15</t>
-  </si>
-  <si>
-    <t>used_on_crops</t>
-  </si>
-  <si>
-    <t>Did you use it on crops?</t>
-  </si>
-  <si>
-    <t>${made_biochar} = 'yes'</t>
-  </si>
-  <si>
-    <t>group_biochar</t>
-  </si>
-  <si>
-    <t>What crops did you use it on?</t>
-  </si>
-  <si>
-    <t>${used_on_crops} = 'yes'</t>
-  </si>
-  <si>
-    <t>biochar_info_maize_1</t>
-  </si>
-  <si>
-    <t>selected(${growed_and_harvested_produce}, 'cereals') and ${cereals_info_maize_1_harvested} = 'yes'</t>
-  </si>
-  <si>
-    <t>biochar_info_maize_1_note</t>
-  </si>
-  <si>
-    <t>w1</t>
-  </si>
-  <si>
-    <t>select_one ab3lr32</t>
-  </si>
-  <si>
-    <t>biochar_info_maize_1_used</t>
-  </si>
-  <si>
-    <t>&lt;span&gt;Did you use biochar on this crop?&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t>select_multiple pp0mv31</t>
-  </si>
-  <si>
-    <t>biochar_info_maize_1_seasons</t>
-  </si>
-  <si>
-    <t>&lt;span&gt;During which seasons?&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t>biochar_info_rice_1</t>
-  </si>
-  <si>
-    <t>selected(${growed_and_harvested_produce}, 'cereals') and ${cereals_info_rice_1_harvested} = 'yes'</t>
-  </si>
-  <si>
-    <t>biochar_info_rice_1_note</t>
-  </si>
-  <si>
-    <t>biochar_info_rice_1_used</t>
-  </si>
-  <si>
-    <t>biochar_info_rice_1_seasons</t>
-  </si>
-  <si>
-    <t>biochar_info_findi_1</t>
-  </si>
-  <si>
-    <t> </t>
-  </si>
-  <si>
-    <t>selected(${growed_and_harvested_produce}, 'cereals') and ${cereals_info_findi_1_harvested} = 'yes'</t>
-  </si>
-  <si>
-    <t>biochar_info_findi_1_note</t>
-  </si>
-  <si>
-    <t>biochar_info_findi_1_used</t>
-  </si>
-  <si>
-    <t>Did you use biochar on this crop?</t>
-  </si>
-  <si>
-    <t>biochar_info_findi_1_seasons</t>
-  </si>
-  <si>
-    <t>During which seasons?</t>
-  </si>
-  <si>
-    <t>biochar_info_millet_1</t>
-  </si>
-  <si>
-    <t>selected(${growed_and_harvested_produce}, 'cereals') and ${cereals_info_millet_1_harvested} = 'yes'</t>
-  </si>
-  <si>
-    <t>biochar_info_millet_1_note</t>
-  </si>
-  <si>
-    <t>biochar_info_millet_1_used</t>
-  </si>
-  <si>
-    <t>biochar_info_millet_1_seasons</t>
-  </si>
-  <si>
-    <t>biochar_info_burucoorse_1</t>
-  </si>
-  <si>
-    <t>selected(${growed_and_harvested_produce}, 'legumes') and ${groundnut_info_burucoorse_1_harvested} = 'yes'</t>
-  </si>
-  <si>
-    <t>biochar_info_burucoorse_1_note</t>
-  </si>
-  <si>
-    <t>biochar_info_burucoorse_1_used</t>
-  </si>
-  <si>
-    <t>biochar_info_burucoorse_1_seasons</t>
-  </si>
-  <si>
-    <t>biochar_info_chorrpoor_1</t>
-  </si>
-  <si>
-    <t>selected(${growed_and_harvested_produce}, 'legumes') and ${groundnut_info_chorrpoor_1_harvested} = 'yes'</t>
-  </si>
-  <si>
-    <t>biochar_info_chorrpoor_1_note</t>
-  </si>
-  <si>
-    <t>biochar_info_chorrpoor_1_used</t>
-  </si>
-  <si>
-    <t>biochar_info_chorrpoor_1_seasons</t>
-  </si>
-  <si>
-    <t>biochar_info_arssama_1</t>
-  </si>
-  <si>
-    <t>selected(${growed_and_harvested_produce}, 'legumes') and ${groundnut_info_arssama_1_harvested} = 'yes'</t>
-  </si>
-  <si>
-    <t>biochar_info_arssama_1_note</t>
-  </si>
-  <si>
-    <t>biochar_info_arssama_1_used</t>
-  </si>
-  <si>
-    <t>biochar_info_arssama_1_seasons</t>
-  </si>
-  <si>
-    <t>biochar_info_mangoes_1</t>
-  </si>
-  <si>
-    <t>selected(${growed_and_harvested_produce}, 'fruit_trees') and ${fruit_tree_info_mangoes_1_harvested} = 'yes'</t>
-  </si>
-  <si>
-    <t>biochar_info_mangoes_1_note</t>
-  </si>
-  <si>
-    <t>biochar_info_mangoes_1_used</t>
-  </si>
-  <si>
-    <t>biochar_info_mangoes_1_seasons</t>
-  </si>
-  <si>
-    <t>biochar_info_bananas_1</t>
-  </si>
-  <si>
-    <t>selected(${growed_and_harvested_produce}, 'fruit_trees') and ${fruit_tree_info_bananas_1_harvested} = 'yes'</t>
-  </si>
-  <si>
-    <t>biochar_info_bananas_1_note</t>
-  </si>
-  <si>
-    <t>biochar_info_bananas_1_used</t>
-  </si>
-  <si>
-    <t>biochar_info_bananas_1_seasons</t>
-  </si>
-  <si>
-    <t>biochar_info_oranges_1</t>
-  </si>
-  <si>
-    <t>selected(${growed_and_harvested_produce}, 'fruit_trees') and ${fruit_tree_info_oranges_1_harvested} = 'yes'</t>
-  </si>
-  <si>
-    <t>biochar_info_oranges_1_note</t>
-  </si>
-  <si>
-    <t>biochar_info_oranges_1_used</t>
-  </si>
-  <si>
-    <t>biochar_info_oranges_1_seasons</t>
-  </si>
-  <si>
-    <t>biochar_info_lemons_1</t>
-  </si>
-  <si>
-    <t>selected(${growed_and_harvested_produce}, 'fruit_trees') and ${fruit_tree_info_lemons_1_harvested} = 'yes'</t>
-  </si>
-  <si>
-    <t>biochar_info_lemons_1_note</t>
-  </si>
-  <si>
-    <t>biochar_info_lemons_1_used</t>
-  </si>
-  <si>
-    <t>biochar_info_lemons_1_seasons</t>
-  </si>
-  <si>
-    <t>biochar_info_papayas_1</t>
-  </si>
-  <si>
-    <t>selected(${growed_and_harvested_produce}, 'fruit_trees') and ${fruit_tree_info_papayas_1_harvested} = 'yes'</t>
-  </si>
-  <si>
-    <t>biochar_info_papayas_1_note</t>
-  </si>
-  <si>
-    <t>biochar_info_papayas_1_used</t>
-  </si>
-  <si>
-    <t>biochar_info_papayas_1_seasons</t>
-  </si>
-  <si>
-    <t>biochar_info_guavas_1</t>
-  </si>
-  <si>
-    <t>selected(${growed_and_harvested_produce}, 'fruit_trees') and ${fruit_tree_info_guavas_1_harvested} = 'yes'</t>
-  </si>
-  <si>
-    <t>biochar_info_guavas_1_note</t>
-  </si>
-  <si>
-    <t>biochar_info_guavas_1_used</t>
-  </si>
-  <si>
-    <t>biochar_info_guavas_1_seasons</t>
-  </si>
-  <si>
-    <t>biochar_info_pineapples_1</t>
-  </si>
-  <si>
-    <t>selected(${growed_and_harvested_produce}, 'fruit_trees') and ${fruit_tree_info_pineapples_1_harvested} = 'yes'</t>
-  </si>
-  <si>
-    <t>biochar_info_pineapples_1_note</t>
-  </si>
-  <si>
-    <t>biochar_info_pineapples_1_used</t>
-  </si>
-  <si>
-    <t>biochar_info_pineapples_1_seasons</t>
-  </si>
-  <si>
-    <t>biochar_info_onions_1</t>
-  </si>
-  <si>
-    <t>selected(${growed_and_harvested_produce}, 'vegetables') and ${vegetable_info_onions_1_harvested} = 'yes'</t>
-  </si>
-  <si>
-    <t>biochar_info_onions_1_note</t>
-  </si>
-  <si>
-    <t>biochar_info_onions_1_used</t>
-  </si>
-  <si>
-    <t>biochar_info_onions_1_seasons</t>
-  </si>
-  <si>
-    <t>biochar_info_carrots_1</t>
-  </si>
-  <si>
-    <t>selected(${growed_and_harvested_produce}, 'vegetables') and ${vegetable_info_carrots_1_harvested} = 'yes'</t>
-  </si>
-  <si>
-    <t>biochar_info_carrots_1_note</t>
-  </si>
-  <si>
-    <t>biochar_info_carrots_1_used</t>
-  </si>
-  <si>
-    <t>biochar_info_carrots_1_seasons</t>
-  </si>
-  <si>
-    <t>biochar_info_okra_1</t>
-  </si>
-  <si>
-    <t>selected(${growed_and_harvested_produce}, 'vegetables') and ${vegetable_info_okra_1_harvested} = 'yes'</t>
-  </si>
-  <si>
-    <t>biochar_info_okra_1_note</t>
-  </si>
-  <si>
-    <t>biochar_info_okra_1_used</t>
-  </si>
-  <si>
-    <t>biochar_info_okra_1_seasons</t>
-  </si>
-  <si>
-    <t>biochar_info_cabbage_1</t>
-  </si>
-  <si>
-    <t>selected(${growed_and_harvested_produce}, 'vegetables') and ${vegetable_info_cabagge_1_harvested} = 'yes'</t>
-  </si>
-  <si>
-    <t>biochar_info_cabbage_1_note</t>
-  </si>
-  <si>
-    <t>biochar_info_cabbage_1_used</t>
-  </si>
-  <si>
-    <t>biochar_info_cabbage_1_seasons</t>
-  </si>
-  <si>
-    <t>biochar_info_eggplant_1</t>
-  </si>
-  <si>
-    <t>selected(${growed_and_harvested_produce}, 'vegetables') and ${vegetable_info_eggplant_1_harvested} = 'yes'</t>
-  </si>
-  <si>
-    <t>biochar_info_eggplant_1_note</t>
-  </si>
-  <si>
-    <t>biochar_info_eggplant_1_used</t>
-  </si>
-  <si>
-    <t>biochar_info_eggplant_1_seasons</t>
-  </si>
-  <si>
-    <t>biochar_info_cucumber_1</t>
-  </si>
-  <si>
-    <t>selected(${growed_and_harvested_produce}, 'vegetables') and ${vegetable_info_cucumber_1_harvested} = 'yes'</t>
-  </si>
-  <si>
-    <t>biochar_info_cucumber_1_note</t>
-  </si>
-  <si>
-    <t>biochar_info_cucumber_1_used</t>
-  </si>
-  <si>
-    <t>biochar_info_cucumber_1_seasons</t>
-  </si>
-  <si>
-    <t>biochar_info_green_pepper_1</t>
-  </si>
-  <si>
-    <t>selected(${growed_and_harvested_produce}, 'vegetables') and ${vegetable_info_green_pepper_1_harvested} = 'yes'</t>
-  </si>
-  <si>
-    <t>biochar_info_green_pepper_1_note</t>
-  </si>
-  <si>
-    <t>##### Green Pepper</t>
-  </si>
-  <si>
-    <t>biochar_info_green_pepper_1_used</t>
-  </si>
-  <si>
-    <t>biochar_info_green_pepper_1_seasons</t>
-  </si>
-  <si>
-    <t>biochar_info_yellow_pepper_1</t>
-  </si>
-  <si>
-    <t>selected(${growed_and_harvested_produce}, 'vegetables') and ${vegetable_info_yellow_pepper_1_harvested} = 'yes'</t>
-  </si>
-  <si>
-    <t>biochar_info_yellow_pepper_1_note</t>
-  </si>
-  <si>
-    <t>##### Yellow Pepper</t>
-  </si>
-  <si>
-    <t>biochar_info_yellow_pepper_1_used</t>
-  </si>
-  <si>
-    <t>biochar_info_yellow_pepper_1_seasons</t>
-  </si>
-  <si>
-    <t>biochar_info_brown_pepper_1</t>
-  </si>
-  <si>
-    <t>selected(${growed_and_harvested_produce}, 'vegetables') and ${vegetable_info_brown_pepper_1_harvested} = 'yes'</t>
-  </si>
-  <si>
-    <t>biochar_info_brown_pepper_1_note</t>
-  </si>
-  <si>
-    <t>##### Brown Pepper</t>
-  </si>
-  <si>
-    <t>biochar_info_brown_pepper_1_used</t>
-  </si>
-  <si>
-    <t>biochar_info_brown_pepper_1_seasons</t>
-  </si>
-  <si>
-    <t>biochar_info_tomatoes_1</t>
-  </si>
-  <si>
-    <t>selected(${growed_and_harvested_produce}, 'vegetables') and ${vegetable_info_tomatoes_1_harvested} = 'yes'</t>
-  </si>
-  <si>
-    <t>biochar_info_tomatoes_1_note</t>
-  </si>
-  <si>
-    <t>biochar_info_tomatoes_1_used</t>
-  </si>
-  <si>
-    <t>biochar_info_tomatoes_1_seasons</t>
-  </si>
-  <si>
-    <t>biochar_info_bitter_tomatoes_1</t>
-  </si>
-  <si>
-    <t>selected(${growed_and_harvested_produce}, 'vegetables') and ${vegetable_info_bitter_tomatoes_1_harvested} = 'yes'</t>
-  </si>
-  <si>
-    <t>biochar_info_bitter_tomatoes_1_note</t>
-  </si>
-  <si>
-    <t>biochar_info_bitter_tomatoes_1_used</t>
-  </si>
-  <si>
-    <t>biochar_info_bitter_tomatoes_1_seasons</t>
-  </si>
-  <si>
-    <t>biochar_info_chili_pepper_1</t>
-  </si>
-  <si>
-    <t>selected(${growed_and_harvested_produce}, 'vegetables') and ${vegetable_info_chilli_pepper_1_harvested} = 'yes'</t>
-  </si>
-  <si>
-    <t>biochar_info_chili_pepper_1_note</t>
-  </si>
-  <si>
-    <t>biochar_info_chili_pepper_1_used</t>
-  </si>
-  <si>
-    <t>biochar_info_chili_pepper_1_seasons</t>
-  </si>
-  <si>
-    <t>biochar_info_sweet_pepper_1</t>
-  </si>
-  <si>
-    <t>selected(${growed_and_harvested_produce}, 'vegetables') and ${vegetable_info_sweet_pepper_1_harvested} = 'yes'</t>
-  </si>
-  <si>
-    <t>biochar_info_sweet_pepper_1_note</t>
-  </si>
-  <si>
-    <t>biochar_info_sweet_pepper_1_used</t>
-  </si>
-  <si>
-    <t>biochar_info_sweet_pepper_1_seasons</t>
-  </si>
-  <si>
-    <t>biochar_info_lettuce_1</t>
-  </si>
-  <si>
-    <t>selected(${growed_and_harvested_produce}, 'vegetables') and ${vegetable_info_lettuce_1_harvested} = 'yes'</t>
-  </si>
-  <si>
-    <t>biochar_info_lettuce_1_note</t>
-  </si>
-  <si>
-    <t>biochar_info_lettuce_1_used</t>
-  </si>
-  <si>
-    <t>biochar_info_lettuce_1_seasons</t>
-  </si>
-  <si>
-    <t>biochar_info_watermelon_1</t>
-  </si>
-  <si>
-    <t>selected(${growed_and_harvested_produce}, 'vegetables') and ${vegetable_info_watermelon_1_harvested} = 'yes'</t>
-  </si>
-  <si>
-    <t>biochar_info_watermelon_1_note</t>
-  </si>
-  <si>
-    <t>biochar_info_watermelon_1_used</t>
-  </si>
-  <si>
-    <t>biochar_info_watermelon_1_seasons</t>
-  </si>
-  <si>
-    <t>biochar_info_cassava_1</t>
-  </si>
-  <si>
-    <t>selected(${growed_and_harvested_produce}, 'tubers') and ${tuber_info_cassava_1_harvested} = 'yes'</t>
-  </si>
-  <si>
-    <t>biochar_info_cassava_1_note</t>
-  </si>
-  <si>
-    <t>biochar_info_cassava_1_used</t>
-  </si>
-  <si>
-    <t>biochar_info_cassava_1_seasons</t>
-  </si>
-  <si>
-    <t>biochar_info_sweet_potato_1</t>
-  </si>
-  <si>
-    <t>selected(${growed_and_harvested_produce}, 'tubers') and ${tuber_info_sweetpotato_1_harvested} = 'yes'</t>
-  </si>
-  <si>
-    <t>biochar_info_sweet_potato_1_note</t>
-  </si>
-  <si>
-    <t>biochar_info_sweet_potato_1_used</t>
-  </si>
-  <si>
-    <t>biochar_info_sweet_potato_1_seasons</t>
-  </si>
-  <si>
-    <t>biochar_info_yams_1</t>
-  </si>
-  <si>
-    <t>selected(${growed_and_harvested_produce}, 'tubers') and ${tuber_info_yams_1_harvested} = 'yes'</t>
-  </si>
-  <si>
-    <t>biochar_info_yams_1_note</t>
-  </si>
-  <si>
-    <t>biochar_info_yams_1_used</t>
-  </si>
-  <si>
-    <t>biochar_info_yams_1_seasons</t>
-  </si>
-  <si>
-    <t>select_one gc78m99</t>
-  </si>
-  <si>
-    <t>biochar_crop_usage</t>
-  </si>
-  <si>
-    <t>For the crops where you used biochar, did you use it equally on the entire crop or only on part of it?</t>
-  </si>
-  <si>
-    <t>select_multiple hs11j39</t>
-  </si>
-  <si>
-    <t>biochar_application</t>
-  </si>
-  <si>
-    <t>If you used biochar on your crops, how did you apply it?</t>
-  </si>
-  <si>
-    <t>select_one ve5vd39</t>
-  </si>
-  <si>
-    <t>biochar_application_interval</t>
-  </si>
-  <si>
-    <t>How often did you apply the biochar?</t>
-  </si>
-  <si>
-    <t>select_one bg18r68</t>
-  </si>
-  <si>
-    <t>amount_of_biochar_applied_grow</t>
-  </si>
-  <si>
-    <t>For how many growing season have you been applying biochar?</t>
-  </si>
-  <si>
-    <t>${biochar_application_interval} = 'every_growing_season'</t>
-  </si>
-  <si>
-    <t>amount_of_used_biochar_terms</t>
-  </si>
-  <si>
-    <t>How much biochar did you use, when you applied it?</t>
-  </si>
-  <si>
-    <t>select_one yw1ml89</t>
-  </si>
-  <si>
-    <t>fertilizer_before_biochar</t>
-  </si>
-  <si>
-    <t>Before using biochar, did you use fertilizer?</t>
-  </si>
-  <si>
-    <t>select_multiple td2jb01</t>
-  </si>
-  <si>
-    <t>fertilizers_used_with_biochar</t>
-  </si>
-  <si>
-    <t>When you applied biochar, did you also use another soil fertilizer in addition to biochar? (Select all that apply)</t>
-  </si>
-  <si>
-    <t>select_multiple pc1lg93</t>
-  </si>
-  <si>
-    <t>fertilizers_used_before_biocha</t>
-  </si>
-  <si>
-    <t>What kind of fertilizer did you use before biochar? (Select all that apply)</t>
-  </si>
-  <si>
-    <t>group_ad9ws92</t>
-  </si>
-  <si>
-    <t>Observation and Results</t>
-  </si>
-  <si>
-    <t>select_one sj05t62</t>
-  </si>
-  <si>
-    <t>biochar_used_on_different_area</t>
-  </si>
-  <si>
-    <t>If you used biochar, did you use it on different areas where the same crop was grown?</t>
-  </si>
-  <si>
-    <t>select_one xj9am89</t>
-  </si>
-  <si>
-    <t>noticed_difference</t>
-  </si>
-  <si>
-    <t>Did  you notice any difference between the plot where you used biochar and the plots where you did not?</t>
-  </si>
-  <si>
-    <t>${biochar_used_on_different_area} = 'yes'</t>
-  </si>
-  <si>
-    <t>select_one hd83z15</t>
-  </si>
-  <si>
-    <t>significance_difference</t>
-  </si>
-  <si>
-    <t>How significant was the difference?</t>
-  </si>
-  <si>
-    <t>${noticed_difference} = 'yes'</t>
-  </si>
-  <si>
-    <t>select_one hy91q54</t>
-  </si>
-  <si>
-    <t>noticeable_difference_in_yield</t>
-  </si>
-  <si>
-    <t>For crops for which you used biochar over the entire plot, can you judge whether there was a different in the yield from the crop was last cultivated, without biochar?</t>
-  </si>
-  <si>
-    <t>select_one ln0re11</t>
-  </si>
-  <si>
-    <t>significance_difference_yield</t>
-  </si>
-  <si>
-    <t>How significant was the difference in yield volume to the last yield without biochar?</t>
-  </si>
-  <si>
-    <t>most_affected_crop</t>
-  </si>
-  <si>
-    <t>If you used biochar on more than one crop, for which crops did it make the biggest difference? (Leave empty when cannot judge)</t>
-  </si>
-  <si>
-    <t>select_one po8ix91</t>
-  </si>
-  <si>
-    <t>wants_to_continue_biochar</t>
-  </si>
-  <si>
-    <t>Do you plan to continue making and using biochar?</t>
-  </si>
-  <si>
-    <t>reason_why_stopping_biochar</t>
-  </si>
-  <si>
-    <t>Why do you not plan to continue making biochar</t>
-  </si>
-  <si>
-    <t>${wants_to_continue_biochar} = 'no'</t>
-  </si>
-  <si>
-    <t>select_multiple bx92j53</t>
-  </si>
-  <si>
-    <t>simplification_for_biochar_use</t>
-  </si>
-  <si>
-    <t>What would make it easier for you to use biochar in future seasons?</t>
-  </si>
-  <si>
-    <t>specified_simplifications</t>
-  </si>
-  <si>
-    <t>Please specify what would make it easier:</t>
-  </si>
-  <si>
-    <t>selected(${simplification_for_biochar_use}, 'other')</t>
-  </si>
-  <si>
-    <t>select_one sl9eb19</t>
-  </si>
-  <si>
-    <t>would_purchase_biochar</t>
-  </si>
-  <si>
-    <t>Would you purchase biochar if it were available?</t>
-  </si>
-  <si>
-    <t>field-list</t>
-  </si>
-  <si>
-    <t>select_multiple rm9rw73</t>
-  </si>
-  <si>
-    <t>why_not_purchase_biochar</t>
-  </si>
-  <si>
-    <t>Why not?</t>
-  </si>
-  <si>
-    <t>${would_purchase_biochar} = 'no'</t>
-  </si>
-  <si>
-    <t>specification_why_not_purchase</t>
-  </si>
-  <si>
-    <t>Please specify why not:</t>
-  </si>
-  <si>
-    <t>selected(${why_not_purchase_biochar}, 'other')</t>
-  </si>
-  <si>
-    <t>list-nolabel</t>
-  </si>
-  <si>
-    <t>group_go5wl54</t>
-  </si>
-  <si>
-    <t>Awareness of Biochar</t>
-  </si>
-  <si>
-    <t>biochar_impact_rating</t>
-  </si>
-  <si>
-    <t>select_one xk6do75</t>
-  </si>
-  <si>
-    <t>biochar_impact_rating_header</t>
-  </si>
-  <si>
-    <t>Rate the impact of biochar on the following aspects</t>
-  </si>
-  <si>
-    <t>Soil_Fertility</t>
-  </si>
-  <si>
-    <t>Soil Fertility</t>
-  </si>
-  <si>
-    <t>Crop_Health</t>
-  </si>
-  <si>
-    <t>Crop Health</t>
-  </si>
-  <si>
-    <t>Water_Retention</t>
-  </si>
-  <si>
-    <t>Water Retention</t>
-  </si>
-  <si>
-    <t>select_one cx3zq25</t>
-  </si>
-  <si>
-    <t>overall_satisfaction_rating</t>
-  </si>
-  <si>
-    <t>Rate your overall satisfaction with the results of using Biochar</t>
-  </si>
-  <si>
-    <t>select_multiple rx5ov52</t>
-  </si>
-  <si>
-    <t>preferred_data</t>
-  </si>
-  <si>
-    <t>If you could store and analyze data about your crops and yields, what kind of data would you like to have?</t>
-  </si>
-  <si>
-    <t>specified_preferred_data</t>
-  </si>
-  <si>
-    <t>Please specify the data:</t>
-  </si>
-  <si>
-    <t>selected(${preferred_data}, 'other')</t>
-  </si>
-  <si>
     <t>list_name</t>
   </si>
   <si>
@@ -2184,12 +2178,6 @@
   </si>
   <si>
     <t>Monthly</t>
-  </si>
-  <si>
-    <t>every_growing_season</t>
-  </si>
-  <si>
-    <t>Every growing season since learning to make it</t>
   </si>
   <si>
     <t>bg18r68</t>
@@ -2811,12 +2799,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F512"/>
+  <dimension ref="A1:F514"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.28515625" customWidth="1"/>
     <col min="2" max="2" width="43.140625" customWidth="1"/>
-    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="3" max="3" width="72.42578125" customWidth="1"/>
     <col min="5" max="5" width="101.42578125" customWidth="1"/>
     <col min="6" max="6" width="22.140625" customWidth="1"/>
   </cols>
@@ -7241,43 +7229,40 @@
     </row>
     <row r="305" spans="1:6">
       <c r="A305" t="s">
-        <v>342</v>
-      </c>
-      <c r="B305" t="s">
-        <v>343</v>
-      </c>
-      <c r="C305" t="s">
-        <v>344</v>
-      </c>
-      <c r="D305" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="306" spans="1:6">
       <c r="A306" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B306" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C306" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="D306" t="s">
         <v>11</v>
-      </c>
-      <c r="E306" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="307" spans="1:6">
       <c r="A307" t="s">
-        <v>22</v>
+        <v>344</v>
+      </c>
+      <c r="B307" t="s">
+        <v>345</v>
+      </c>
+      <c r="C307" t="s">
+        <v>346</v>
+      </c>
+      <c r="D307" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="308" spans="1:6">
       <c r="A308" t="s">
-        <v>8</v>
+        <v>347</v>
       </c>
       <c r="B308" t="s">
         <v>348</v>
@@ -7288,36 +7273,25 @@
       <c r="D308" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="309" spans="1:6">
-      <c r="A309" t="s">
+      <c r="E308" t="s">
         <v>350</v>
-      </c>
-      <c r="B309" t="s">
-        <v>351</v>
-      </c>
-      <c r="C309" t="s">
-        <v>352</v>
-      </c>
-      <c r="D309" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="310" spans="1:6">
       <c r="A310" t="s">
+        <v>8</v>
+      </c>
+      <c r="B310" t="s">
+        <v>351</v>
+      </c>
+      <c r="C310" t="s">
+        <v>352</v>
+      </c>
+      <c r="D310" t="s">
+        <v>11</v>
+      </c>
+      <c r="E310" t="s">
         <v>353</v>
-      </c>
-      <c r="B310" t="s">
-        <v>354</v>
-      </c>
-      <c r="C310" t="s">
-        <v>355</v>
-      </c>
-      <c r="D310" t="s">
-        <v>11</v>
-      </c>
-      <c r="E310" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="312" spans="1:6">
@@ -7325,2437 +7299,2425 @@
         <v>8</v>
       </c>
       <c r="B312" t="s">
+        <v>354</v>
+      </c>
+      <c r="D312" t="s">
+        <v>11</v>
+      </c>
+      <c r="E312" t="s">
+        <v>355</v>
+      </c>
+      <c r="F312" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6">
+      <c r="A313" t="s">
+        <v>35</v>
+      </c>
+      <c r="B313" t="s">
+        <v>356</v>
+      </c>
+      <c r="C313" t="s">
+        <v>37</v>
+      </c>
+      <c r="D313" t="s">
+        <v>11</v>
+      </c>
+      <c r="F313" t="s">
         <v>357</v>
-      </c>
-      <c r="C312" t="s">
-        <v>358</v>
-      </c>
-      <c r="D312" t="s">
-        <v>11</v>
-      </c>
-      <c r="E312" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="314" spans="1:6">
       <c r="A314" t="s">
-        <v>8</v>
+        <v>358</v>
       </c>
       <c r="B314" t="s">
+        <v>359</v>
+      </c>
+      <c r="C314" t="s">
         <v>360</v>
       </c>
       <c r="D314" t="s">
         <v>11</v>
       </c>
-      <c r="E314" t="s">
-        <v>361</v>
-      </c>
       <c r="F314" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="315" spans="1:6">
       <c r="A315" t="s">
-        <v>35</v>
+        <v>361</v>
       </c>
       <c r="B315" t="s">
         <v>362</v>
       </c>
       <c r="C315" t="s">
-        <v>37</v>
+        <v>363</v>
       </c>
       <c r="D315" t="s">
         <v>11</v>
       </c>
       <c r="F315" t="s">
-        <v>363</v>
+        <v>42</v>
       </c>
     </row>
     <row r="316" spans="1:6">
       <c r="A316" t="s">
-        <v>364</v>
-      </c>
-      <c r="B316" t="s">
-        <v>365</v>
-      </c>
-      <c r="C316" t="s">
-        <v>366</v>
-      </c>
-      <c r="D316" t="s">
-        <v>11</v>
-      </c>
-      <c r="F316" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="317" spans="1:6">
       <c r="A317" t="s">
-        <v>367</v>
+        <v>8</v>
       </c>
       <c r="B317" t="s">
-        <v>368</v>
-      </c>
-      <c r="C317" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="D317" t="s">
         <v>11</v>
       </c>
+      <c r="E317" t="s">
+        <v>365</v>
+      </c>
       <c r="F317" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="318" spans="1:6">
       <c r="A318" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="B318" t="s">
+        <v>366</v>
+      </c>
+      <c r="C318" t="s">
+        <v>57</v>
+      </c>
+      <c r="D318" t="s">
+        <v>11</v>
+      </c>
+      <c r="F318" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="319" spans="1:6">
       <c r="A319" t="s">
-        <v>8</v>
+        <v>358</v>
       </c>
       <c r="B319" t="s">
-        <v>370</v>
+        <v>367</v>
+      </c>
+      <c r="C319" t="s">
+        <v>360</v>
       </c>
       <c r="D319" t="s">
         <v>11</v>
       </c>
-      <c r="E319" t="s">
-        <v>371</v>
-      </c>
       <c r="F319" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="320" spans="1:6">
       <c r="A320" t="s">
-        <v>35</v>
+        <v>361</v>
       </c>
       <c r="B320" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C320" t="s">
-        <v>57</v>
+        <v>363</v>
       </c>
       <c r="D320" t="s">
         <v>11</v>
       </c>
       <c r="F320" t="s">
-        <v>363</v>
+        <v>42</v>
       </c>
     </row>
     <row r="321" spans="1:6">
       <c r="A321" t="s">
-        <v>364</v>
-      </c>
-      <c r="B321" t="s">
-        <v>373</v>
-      </c>
-      <c r="C321" t="s">
-        <v>366</v>
-      </c>
-      <c r="D321" t="s">
-        <v>11</v>
-      </c>
-      <c r="F321" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="322" spans="1:6">
       <c r="A322" t="s">
-        <v>367</v>
+        <v>8</v>
       </c>
       <c r="B322" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C322" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D322" t="s">
         <v>11</v>
       </c>
+      <c r="E322" t="s">
+        <v>371</v>
+      </c>
       <c r="F322" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="323" spans="1:6">
       <c r="A323" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="B323" t="s">
+        <v>372</v>
+      </c>
+      <c r="C323" t="s">
+        <v>65</v>
+      </c>
+      <c r="D323" t="s">
+        <v>11</v>
+      </c>
+      <c r="F323" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="324" spans="1:6">
       <c r="A324" t="s">
-        <v>8</v>
+        <v>358</v>
       </c>
       <c r="B324" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C324" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="D324" t="s">
         <v>11</v>
       </c>
-      <c r="E324" t="s">
-        <v>377</v>
-      </c>
       <c r="F324" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="325" spans="1:6">
       <c r="A325" t="s">
-        <v>35</v>
+        <v>361</v>
       </c>
       <c r="B325" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C325" t="s">
-        <v>65</v>
+        <v>375</v>
       </c>
       <c r="D325" t="s">
         <v>11</v>
       </c>
       <c r="F325" t="s">
-        <v>363</v>
+        <v>42</v>
       </c>
     </row>
     <row r="326" spans="1:6">
       <c r="A326" t="s">
-        <v>364</v>
-      </c>
-      <c r="B326" t="s">
-        <v>379</v>
-      </c>
-      <c r="C326" t="s">
-        <v>380</v>
-      </c>
-      <c r="D326" t="s">
-        <v>11</v>
-      </c>
-      <c r="F326" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="327" spans="1:6">
       <c r="A327" t="s">
-        <v>367</v>
+        <v>8</v>
       </c>
       <c r="B327" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C327" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="D327" t="s">
         <v>11</v>
       </c>
+      <c r="E327" t="s">
+        <v>377</v>
+      </c>
       <c r="F327" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="328" spans="1:6">
       <c r="A328" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="B328" t="s">
+        <v>378</v>
+      </c>
+      <c r="C328" t="s">
+        <v>73</v>
+      </c>
+      <c r="D328" t="s">
+        <v>11</v>
+      </c>
+      <c r="F328" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="329" spans="1:6">
       <c r="A329" t="s">
-        <v>8</v>
+        <v>358</v>
       </c>
       <c r="B329" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C329" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="D329" t="s">
         <v>11</v>
       </c>
-      <c r="E329" t="s">
-        <v>384</v>
-      </c>
       <c r="F329" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="330" spans="1:6">
       <c r="A330" t="s">
-        <v>35</v>
+        <v>361</v>
       </c>
       <c r="B330" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="C330" t="s">
-        <v>73</v>
+        <v>363</v>
       </c>
       <c r="D330" t="s">
         <v>11</v>
       </c>
       <c r="F330" t="s">
-        <v>363</v>
+        <v>42</v>
       </c>
     </row>
     <row r="331" spans="1:6">
       <c r="A331" t="s">
-        <v>364</v>
-      </c>
-      <c r="B331" t="s">
-        <v>386</v>
-      </c>
-      <c r="C331" t="s">
-        <v>380</v>
-      </c>
-      <c r="D331" t="s">
-        <v>11</v>
-      </c>
-      <c r="F331" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="332" spans="1:6">
       <c r="A332" t="s">
-        <v>367</v>
+        <v>8</v>
       </c>
       <c r="B332" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="C332" t="s">
+        <v>370</v>
+      </c>
+      <c r="D332" t="s">
+        <v>11</v>
+      </c>
+      <c r="E332" t="s">
         <v>382</v>
       </c>
-      <c r="D332" t="s">
-        <v>11</v>
-      </c>
       <c r="F332" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="333" spans="1:6">
       <c r="A333" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="B333" t="s">
+        <v>383</v>
+      </c>
+      <c r="C333" t="s">
+        <v>84</v>
+      </c>
+      <c r="D333" t="s">
+        <v>11</v>
+      </c>
+      <c r="F333" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="334" spans="1:6">
       <c r="A334" t="s">
-        <v>8</v>
+        <v>358</v>
       </c>
       <c r="B334" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C334" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="D334" t="s">
         <v>11</v>
       </c>
-      <c r="E334" t="s">
-        <v>389</v>
-      </c>
       <c r="F334" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="335" spans="1:6">
       <c r="A335" t="s">
-        <v>35</v>
+        <v>361</v>
       </c>
       <c r="B335" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="C335" t="s">
-        <v>84</v>
+        <v>363</v>
       </c>
       <c r="D335" t="s">
         <v>11</v>
       </c>
       <c r="F335" t="s">
-        <v>363</v>
+        <v>42</v>
       </c>
     </row>
     <row r="336" spans="1:6">
       <c r="A336" t="s">
-        <v>364</v>
-      </c>
-      <c r="B336" t="s">
-        <v>391</v>
-      </c>
-      <c r="C336" t="s">
-        <v>380</v>
-      </c>
-      <c r="D336" t="s">
-        <v>11</v>
-      </c>
-      <c r="F336" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="337" spans="1:6">
       <c r="A337" t="s">
-        <v>367</v>
+        <v>8</v>
       </c>
       <c r="B337" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="C337" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="D337" t="s">
         <v>11</v>
       </c>
+      <c r="E337" t="s">
+        <v>387</v>
+      </c>
       <c r="F337" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="338" spans="1:6">
       <c r="A338" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="B338" t="s">
+        <v>388</v>
+      </c>
+      <c r="C338" t="s">
+        <v>92</v>
+      </c>
+      <c r="D338" t="s">
+        <v>11</v>
+      </c>
+      <c r="F338" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="339" spans="1:6">
       <c r="A339" t="s">
-        <v>8</v>
+        <v>358</v>
       </c>
       <c r="B339" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C339" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="D339" t="s">
         <v>11</v>
       </c>
-      <c r="E339" t="s">
-        <v>394</v>
-      </c>
       <c r="F339" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="340" spans="1:6">
       <c r="A340" t="s">
-        <v>35</v>
+        <v>361</v>
       </c>
       <c r="B340" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="C340" t="s">
-        <v>92</v>
+        <v>363</v>
       </c>
       <c r="D340" t="s">
         <v>11</v>
       </c>
       <c r="F340" t="s">
-        <v>363</v>
+        <v>42</v>
       </c>
     </row>
     <row r="341" spans="1:6">
       <c r="A341" t="s">
-        <v>364</v>
-      </c>
-      <c r="B341" t="s">
-        <v>396</v>
-      </c>
-      <c r="C341" t="s">
-        <v>380</v>
-      </c>
-      <c r="D341" t="s">
-        <v>11</v>
-      </c>
-      <c r="F341" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="342" spans="1:6">
       <c r="A342" t="s">
-        <v>367</v>
+        <v>8</v>
       </c>
       <c r="B342" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="C342" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="D342" t="s">
         <v>11</v>
       </c>
+      <c r="E342" t="s">
+        <v>392</v>
+      </c>
       <c r="F342" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="343" spans="1:6">
       <c r="A343" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="B343" t="s">
+        <v>393</v>
+      </c>
+      <c r="C343" t="s">
+        <v>100</v>
+      </c>
+      <c r="D343" t="s">
+        <v>11</v>
+      </c>
+      <c r="F343" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="344" spans="1:6">
       <c r="A344" t="s">
-        <v>8</v>
+        <v>358</v>
       </c>
       <c r="B344" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C344" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="D344" t="s">
         <v>11</v>
       </c>
-      <c r="E344" t="s">
-        <v>399</v>
-      </c>
       <c r="F344" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="345" spans="1:6">
       <c r="A345" t="s">
-        <v>35</v>
+        <v>361</v>
       </c>
       <c r="B345" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="C345" t="s">
-        <v>100</v>
+        <v>363</v>
       </c>
       <c r="D345" t="s">
         <v>11</v>
       </c>
       <c r="F345" t="s">
-        <v>363</v>
+        <v>42</v>
       </c>
     </row>
     <row r="346" spans="1:6">
       <c r="A346" t="s">
-        <v>364</v>
-      </c>
-      <c r="B346" t="s">
-        <v>401</v>
-      </c>
-      <c r="C346" t="s">
-        <v>380</v>
-      </c>
-      <c r="D346" t="s">
-        <v>11</v>
-      </c>
-      <c r="F346" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="347" spans="1:6">
       <c r="A347" t="s">
-        <v>367</v>
+        <v>8</v>
       </c>
       <c r="B347" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="C347" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="D347" t="s">
         <v>11</v>
       </c>
+      <c r="E347" t="s">
+        <v>397</v>
+      </c>
       <c r="F347" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="348" spans="1:6">
       <c r="A348" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="B348" t="s">
+        <v>398</v>
+      </c>
+      <c r="C348" t="s">
+        <v>288</v>
+      </c>
+      <c r="D348" t="s">
+        <v>11</v>
+      </c>
+      <c r="F348" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="349" spans="1:6">
       <c r="A349" t="s">
-        <v>8</v>
+        <v>358</v>
       </c>
       <c r="B349" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C349" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="D349" t="s">
         <v>11</v>
       </c>
-      <c r="E349" t="s">
-        <v>404</v>
-      </c>
       <c r="F349" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="350" spans="1:6">
       <c r="A350" t="s">
-        <v>35</v>
+        <v>361</v>
       </c>
       <c r="B350" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="C350" t="s">
-        <v>288</v>
+        <v>363</v>
       </c>
       <c r="D350" t="s">
         <v>11</v>
       </c>
       <c r="F350" t="s">
-        <v>363</v>
+        <v>42</v>
       </c>
     </row>
     <row r="351" spans="1:6">
       <c r="A351" t="s">
-        <v>364</v>
-      </c>
-      <c r="B351" t="s">
-        <v>406</v>
-      </c>
-      <c r="C351" t="s">
-        <v>380</v>
-      </c>
-      <c r="D351" t="s">
-        <v>11</v>
-      </c>
-      <c r="F351" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="352" spans="1:6">
       <c r="A352" t="s">
-        <v>367</v>
+        <v>8</v>
       </c>
       <c r="B352" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="C352" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="D352" t="s">
         <v>11</v>
       </c>
+      <c r="E352" t="s">
+        <v>402</v>
+      </c>
       <c r="F352" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="353" spans="1:6">
       <c r="A353" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="B353" t="s">
+        <v>403</v>
+      </c>
+      <c r="C353" t="s">
+        <v>296</v>
+      </c>
+      <c r="D353" t="s">
+        <v>11</v>
+      </c>
+      <c r="F353" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="354" spans="1:6">
       <c r="A354" t="s">
-        <v>8</v>
+        <v>358</v>
       </c>
       <c r="B354" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="C354" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="D354" t="s">
         <v>11</v>
       </c>
-      <c r="E354" t="s">
-        <v>409</v>
-      </c>
       <c r="F354" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="355" spans="1:6">
       <c r="A355" t="s">
-        <v>35</v>
+        <v>361</v>
       </c>
       <c r="B355" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="C355" t="s">
-        <v>296</v>
+        <v>363</v>
       </c>
       <c r="D355" t="s">
         <v>11</v>
       </c>
       <c r="F355" t="s">
-        <v>363</v>
+        <v>42</v>
       </c>
     </row>
     <row r="356" spans="1:6">
       <c r="A356" t="s">
-        <v>364</v>
-      </c>
-      <c r="B356" t="s">
-        <v>411</v>
-      </c>
-      <c r="C356" t="s">
-        <v>380</v>
-      </c>
-      <c r="D356" t="s">
-        <v>11</v>
-      </c>
-      <c r="F356" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="357" spans="1:6">
       <c r="A357" t="s">
-        <v>367</v>
+        <v>8</v>
       </c>
       <c r="B357" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="C357" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="D357" t="s">
         <v>11</v>
       </c>
+      <c r="E357" t="s">
+        <v>407</v>
+      </c>
       <c r="F357" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="358" spans="1:6">
       <c r="A358" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="B358" t="s">
+        <v>408</v>
+      </c>
+      <c r="C358" t="s">
+        <v>304</v>
+      </c>
+      <c r="D358" t="s">
+        <v>11</v>
+      </c>
+      <c r="F358" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="359" spans="1:6">
       <c r="A359" t="s">
-        <v>8</v>
+        <v>358</v>
       </c>
       <c r="B359" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C359" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="D359" t="s">
         <v>11</v>
       </c>
-      <c r="E359" t="s">
-        <v>414</v>
-      </c>
       <c r="F359" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="360" spans="1:6">
       <c r="A360" t="s">
-        <v>35</v>
+        <v>361</v>
       </c>
       <c r="B360" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="C360" t="s">
-        <v>304</v>
+        <v>363</v>
       </c>
       <c r="D360" t="s">
         <v>11</v>
       </c>
       <c r="F360" t="s">
-        <v>363</v>
+        <v>42</v>
       </c>
     </row>
     <row r="361" spans="1:6">
       <c r="A361" t="s">
-        <v>364</v>
-      </c>
-      <c r="B361" t="s">
-        <v>416</v>
-      </c>
-      <c r="C361" t="s">
-        <v>380</v>
-      </c>
-      <c r="D361" t="s">
-        <v>11</v>
-      </c>
-      <c r="F361" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="362" spans="1:6">
       <c r="A362" t="s">
-        <v>367</v>
+        <v>8</v>
       </c>
       <c r="B362" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="C362" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="D362" t="s">
         <v>11</v>
       </c>
+      <c r="E362" t="s">
+        <v>412</v>
+      </c>
       <c r="F362" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="363" spans="1:6">
       <c r="A363" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="B363" t="s">
+        <v>413</v>
+      </c>
+      <c r="C363" t="s">
+        <v>312</v>
+      </c>
+      <c r="D363" t="s">
+        <v>11</v>
+      </c>
+      <c r="F363" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="364" spans="1:6">
       <c r="A364" t="s">
-        <v>8</v>
+        <v>358</v>
       </c>
       <c r="B364" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="C364" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="D364" t="s">
         <v>11</v>
       </c>
-      <c r="E364" t="s">
-        <v>419</v>
-      </c>
       <c r="F364" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="365" spans="1:6">
       <c r="A365" t="s">
-        <v>35</v>
+        <v>361</v>
       </c>
       <c r="B365" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="C365" t="s">
-        <v>312</v>
+        <v>363</v>
       </c>
       <c r="D365" t="s">
         <v>11</v>
       </c>
       <c r="F365" t="s">
-        <v>363</v>
+        <v>42</v>
       </c>
     </row>
     <row r="366" spans="1:6">
       <c r="A366" t="s">
-        <v>364</v>
-      </c>
-      <c r="B366" t="s">
-        <v>421</v>
-      </c>
-      <c r="C366" t="s">
-        <v>380</v>
-      </c>
-      <c r="D366" t="s">
-        <v>11</v>
-      </c>
-      <c r="F366" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="367" spans="1:6">
       <c r="A367" t="s">
-        <v>367</v>
+        <v>8</v>
       </c>
       <c r="B367" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="C367" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="D367" t="s">
         <v>11</v>
       </c>
+      <c r="E367" t="s">
+        <v>417</v>
+      </c>
       <c r="F367" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="368" spans="1:6">
       <c r="A368" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="B368" t="s">
+        <v>418</v>
+      </c>
+      <c r="C368" t="s">
+        <v>320</v>
+      </c>
+      <c r="D368" t="s">
+        <v>11</v>
+      </c>
+      <c r="F368" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="369" spans="1:6">
       <c r="A369" t="s">
-        <v>8</v>
+        <v>358</v>
       </c>
       <c r="B369" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C369" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="D369" t="s">
         <v>11</v>
       </c>
-      <c r="E369" t="s">
-        <v>424</v>
-      </c>
       <c r="F369" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="370" spans="1:6">
       <c r="A370" t="s">
-        <v>35</v>
+        <v>361</v>
       </c>
       <c r="B370" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="C370" t="s">
-        <v>320</v>
+        <v>363</v>
       </c>
       <c r="D370" t="s">
         <v>11</v>
       </c>
       <c r="F370" t="s">
-        <v>363</v>
+        <v>42</v>
       </c>
     </row>
     <row r="371" spans="1:6">
       <c r="A371" t="s">
-        <v>364</v>
-      </c>
-      <c r="B371" t="s">
-        <v>426</v>
-      </c>
-      <c r="C371" t="s">
-        <v>380</v>
-      </c>
-      <c r="D371" t="s">
-        <v>11</v>
-      </c>
-      <c r="F371" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="372" spans="1:6">
       <c r="A372" t="s">
-        <v>367</v>
+        <v>8</v>
       </c>
       <c r="B372" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C372" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="D372" t="s">
         <v>11</v>
       </c>
+      <c r="E372" t="s">
+        <v>422</v>
+      </c>
       <c r="F372" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="373" spans="1:6">
       <c r="A373" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="B373" t="s">
+        <v>423</v>
+      </c>
+      <c r="C373" t="s">
+        <v>328</v>
+      </c>
+      <c r="D373" t="s">
+        <v>11</v>
+      </c>
+      <c r="F373" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="374" spans="1:6">
       <c r="A374" t="s">
-        <v>8</v>
+        <v>358</v>
       </c>
       <c r="B374" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C374" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="D374" t="s">
         <v>11</v>
       </c>
-      <c r="E374" t="s">
-        <v>429</v>
-      </c>
       <c r="F374" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="375" spans="1:6">
       <c r="A375" t="s">
-        <v>35</v>
+        <v>361</v>
       </c>
       <c r="B375" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="C375" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="D375" t="s">
         <v>11</v>
       </c>
       <c r="F375" t="s">
-        <v>363</v>
+        <v>42</v>
       </c>
     </row>
     <row r="376" spans="1:6">
       <c r="A376" t="s">
-        <v>364</v>
-      </c>
-      <c r="B376" t="s">
-        <v>431</v>
-      </c>
-      <c r="C376" t="s">
-        <v>380</v>
-      </c>
-      <c r="D376" t="s">
-        <v>11</v>
-      </c>
-      <c r="F376" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="377" spans="1:6">
       <c r="A377" t="s">
-        <v>367</v>
+        <v>8</v>
       </c>
       <c r="B377" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="C377" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="D377" t="s">
         <v>11</v>
       </c>
+      <c r="E377" t="s">
+        <v>427</v>
+      </c>
       <c r="F377" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="378" spans="1:6">
       <c r="A378" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="B378" t="s">
+        <v>428</v>
+      </c>
+      <c r="C378" t="s">
+        <v>336</v>
+      </c>
+      <c r="D378" t="s">
+        <v>11</v>
+      </c>
+      <c r="F378" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="379" spans="1:6">
       <c r="A379" t="s">
-        <v>8</v>
+        <v>358</v>
       </c>
       <c r="B379" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C379" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="D379" t="s">
         <v>11</v>
       </c>
-      <c r="E379" t="s">
-        <v>434</v>
-      </c>
       <c r="F379" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="380" spans="1:6">
       <c r="A380" t="s">
-        <v>35</v>
+        <v>361</v>
       </c>
       <c r="B380" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="C380" t="s">
-        <v>336</v>
+        <v>363</v>
       </c>
       <c r="D380" t="s">
         <v>11</v>
       </c>
       <c r="F380" t="s">
-        <v>363</v>
+        <v>42</v>
       </c>
     </row>
     <row r="381" spans="1:6">
       <c r="A381" t="s">
-        <v>364</v>
-      </c>
-      <c r="B381" t="s">
-        <v>436</v>
-      </c>
-      <c r="C381" t="s">
-        <v>380</v>
-      </c>
-      <c r="D381" t="s">
-        <v>11</v>
-      </c>
-      <c r="F381" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="382" spans="1:6">
       <c r="A382" t="s">
-        <v>367</v>
+        <v>8</v>
       </c>
       <c r="B382" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="C382" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="D382" t="s">
         <v>11</v>
       </c>
+      <c r="E382" t="s">
+        <v>432</v>
+      </c>
       <c r="F382" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="383" spans="1:6">
       <c r="A383" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="B383" t="s">
+        <v>433</v>
+      </c>
+      <c r="C383" t="s">
+        <v>111</v>
+      </c>
+      <c r="D383" t="s">
+        <v>11</v>
+      </c>
+      <c r="F383" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="384" spans="1:6">
       <c r="A384" t="s">
-        <v>8</v>
+        <v>358</v>
       </c>
       <c r="B384" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="C384" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="D384" t="s">
         <v>11</v>
       </c>
-      <c r="E384" t="s">
-        <v>439</v>
-      </c>
       <c r="F384" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="385" spans="1:6">
       <c r="A385" t="s">
-        <v>35</v>
+        <v>361</v>
       </c>
       <c r="B385" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C385" t="s">
-        <v>111</v>
+        <v>363</v>
       </c>
       <c r="D385" t="s">
         <v>11</v>
       </c>
       <c r="F385" t="s">
-        <v>363</v>
+        <v>42</v>
       </c>
     </row>
     <row r="386" spans="1:6">
       <c r="A386" t="s">
-        <v>364</v>
-      </c>
-      <c r="B386" t="s">
-        <v>441</v>
-      </c>
-      <c r="C386" t="s">
-        <v>380</v>
-      </c>
-      <c r="D386" t="s">
-        <v>11</v>
-      </c>
-      <c r="F386" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="387" spans="1:6">
       <c r="A387" t="s">
-        <v>367</v>
+        <v>8</v>
       </c>
       <c r="B387" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="C387" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="D387" t="s">
         <v>11</v>
       </c>
+      <c r="E387" t="s">
+        <v>437</v>
+      </c>
       <c r="F387" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="388" spans="1:6">
       <c r="A388" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="B388" t="s">
+        <v>438</v>
+      </c>
+      <c r="C388" t="s">
+        <v>119</v>
+      </c>
+      <c r="D388" t="s">
+        <v>11</v>
+      </c>
+      <c r="F388" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="389" spans="1:6">
       <c r="A389" t="s">
-        <v>8</v>
+        <v>358</v>
       </c>
       <c r="B389" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="C389" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="D389" t="s">
         <v>11</v>
       </c>
-      <c r="E389" t="s">
-        <v>444</v>
-      </c>
       <c r="F389" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="390" spans="1:6">
       <c r="A390" t="s">
-        <v>35</v>
+        <v>361</v>
       </c>
       <c r="B390" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C390" t="s">
-        <v>119</v>
+        <v>363</v>
       </c>
       <c r="D390" t="s">
         <v>11</v>
       </c>
       <c r="F390" t="s">
-        <v>363</v>
+        <v>42</v>
       </c>
     </row>
     <row r="391" spans="1:6">
       <c r="A391" t="s">
-        <v>364</v>
-      </c>
-      <c r="B391" t="s">
-        <v>446</v>
-      </c>
-      <c r="C391" t="s">
-        <v>380</v>
-      </c>
-      <c r="D391" t="s">
-        <v>11</v>
-      </c>
-      <c r="F391" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="392" spans="1:6">
       <c r="A392" t="s">
-        <v>367</v>
+        <v>8</v>
       </c>
       <c r="B392" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C392" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="D392" t="s">
         <v>11</v>
       </c>
+      <c r="E392" t="s">
+        <v>442</v>
+      </c>
       <c r="F392" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="393" spans="1:6">
       <c r="A393" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="B393" t="s">
+        <v>443</v>
+      </c>
+      <c r="C393" t="s">
+        <v>127</v>
+      </c>
+      <c r="D393" t="s">
+        <v>11</v>
+      </c>
+      <c r="F393" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="394" spans="1:6">
       <c r="A394" t="s">
-        <v>8</v>
+        <v>358</v>
       </c>
       <c r="B394" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="C394" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="D394" t="s">
         <v>11</v>
       </c>
-      <c r="E394" t="s">
-        <v>449</v>
-      </c>
       <c r="F394" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="395" spans="1:6">
       <c r="A395" t="s">
-        <v>35</v>
+        <v>361</v>
       </c>
       <c r="B395" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="C395" t="s">
-        <v>127</v>
+        <v>363</v>
       </c>
       <c r="D395" t="s">
         <v>11</v>
       </c>
       <c r="F395" t="s">
-        <v>363</v>
+        <v>42</v>
       </c>
     </row>
     <row r="396" spans="1:6">
       <c r="A396" t="s">
-        <v>364</v>
-      </c>
-      <c r="B396" t="s">
-        <v>451</v>
-      </c>
-      <c r="C396" t="s">
-        <v>380</v>
-      </c>
-      <c r="D396" t="s">
-        <v>11</v>
-      </c>
-      <c r="F396" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="397" spans="1:6">
       <c r="A397" t="s">
-        <v>367</v>
+        <v>8</v>
       </c>
       <c r="B397" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="C397" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="D397" t="s">
         <v>11</v>
       </c>
+      <c r="E397" t="s">
+        <v>447</v>
+      </c>
       <c r="F397" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="398" spans="1:6">
       <c r="A398" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="B398" t="s">
+        <v>448</v>
+      </c>
+      <c r="C398" t="s">
+        <v>135</v>
+      </c>
+      <c r="D398" t="s">
+        <v>11</v>
+      </c>
+      <c r="F398" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="399" spans="1:6">
       <c r="A399" t="s">
-        <v>8</v>
+        <v>358</v>
       </c>
       <c r="B399" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="C399" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="D399" t="s">
         <v>11</v>
       </c>
-      <c r="E399" t="s">
-        <v>454</v>
-      </c>
       <c r="F399" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="400" spans="1:6">
       <c r="A400" t="s">
-        <v>35</v>
+        <v>361</v>
       </c>
       <c r="B400" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="C400" t="s">
-        <v>135</v>
+        <v>363</v>
       </c>
       <c r="D400" t="s">
         <v>11</v>
       </c>
       <c r="F400" t="s">
-        <v>363</v>
+        <v>42</v>
       </c>
     </row>
     <row r="401" spans="1:6">
       <c r="A401" t="s">
-        <v>364</v>
-      </c>
-      <c r="B401" t="s">
-        <v>456</v>
-      </c>
-      <c r="C401" t="s">
-        <v>380</v>
-      </c>
-      <c r="D401" t="s">
-        <v>11</v>
-      </c>
-      <c r="F401" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="402" spans="1:6">
       <c r="A402" t="s">
-        <v>367</v>
+        <v>8</v>
       </c>
       <c r="B402" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="C402" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="D402" t="s">
         <v>11</v>
       </c>
+      <c r="E402" t="s">
+        <v>452</v>
+      </c>
       <c r="F402" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="403" spans="1:6">
       <c r="A403" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="B403" t="s">
+        <v>453</v>
+      </c>
+      <c r="C403" t="s">
+        <v>143</v>
+      </c>
+      <c r="D403" t="s">
+        <v>11</v>
+      </c>
+      <c r="F403" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="404" spans="1:6">
       <c r="A404" t="s">
-        <v>8</v>
+        <v>358</v>
       </c>
       <c r="B404" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="C404" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="D404" t="s">
         <v>11</v>
       </c>
-      <c r="E404" t="s">
-        <v>459</v>
-      </c>
       <c r="F404" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="405" spans="1:6">
       <c r="A405" t="s">
-        <v>35</v>
+        <v>361</v>
       </c>
       <c r="B405" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="C405" t="s">
-        <v>143</v>
+        <v>363</v>
       </c>
       <c r="D405" t="s">
         <v>11</v>
       </c>
       <c r="F405" t="s">
-        <v>363</v>
+        <v>42</v>
       </c>
     </row>
     <row r="406" spans="1:6">
       <c r="A406" t="s">
-        <v>364</v>
-      </c>
-      <c r="B406" t="s">
-        <v>461</v>
-      </c>
-      <c r="C406" t="s">
-        <v>380</v>
-      </c>
-      <c r="D406" t="s">
-        <v>11</v>
-      </c>
-      <c r="F406" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="407" spans="1:6">
       <c r="A407" t="s">
-        <v>367</v>
+        <v>8</v>
       </c>
       <c r="B407" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="C407" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="D407" t="s">
         <v>11</v>
       </c>
+      <c r="E407" t="s">
+        <v>457</v>
+      </c>
       <c r="F407" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="408" spans="1:6">
       <c r="A408" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="B408" t="s">
+        <v>458</v>
+      </c>
+      <c r="C408" t="s">
+        <v>151</v>
+      </c>
+      <c r="D408" t="s">
+        <v>11</v>
+      </c>
+      <c r="F408" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="409" spans="1:6">
       <c r="A409" t="s">
-        <v>8</v>
+        <v>358</v>
       </c>
       <c r="B409" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="C409" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="D409" t="s">
         <v>11</v>
       </c>
-      <c r="E409" t="s">
-        <v>464</v>
-      </c>
       <c r="F409" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="410" spans="1:6">
       <c r="A410" t="s">
-        <v>35</v>
+        <v>361</v>
       </c>
       <c r="B410" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="C410" t="s">
-        <v>151</v>
+        <v>363</v>
       </c>
       <c r="D410" t="s">
         <v>11</v>
       </c>
       <c r="F410" t="s">
-        <v>363</v>
+        <v>42</v>
       </c>
     </row>
     <row r="411" spans="1:6">
       <c r="A411" t="s">
-        <v>364</v>
-      </c>
-      <c r="B411" t="s">
-        <v>466</v>
-      </c>
-      <c r="C411" t="s">
-        <v>380</v>
-      </c>
-      <c r="D411" t="s">
-        <v>11</v>
-      </c>
-      <c r="F411" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="412" spans="1:6">
       <c r="A412" t="s">
-        <v>367</v>
+        <v>8</v>
       </c>
       <c r="B412" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="C412" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="D412" t="s">
         <v>11</v>
       </c>
+      <c r="E412" t="s">
+        <v>462</v>
+      </c>
       <c r="F412" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="413" spans="1:6">
       <c r="A413" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="B413" t="s">
+        <v>463</v>
+      </c>
+      <c r="C413" t="s">
+        <v>464</v>
+      </c>
+      <c r="D413" t="s">
+        <v>11</v>
+      </c>
+      <c r="F413" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="414" spans="1:6">
       <c r="A414" t="s">
-        <v>8</v>
+        <v>358</v>
       </c>
       <c r="B414" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="C414" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="D414" t="s">
         <v>11</v>
       </c>
-      <c r="E414" t="s">
-        <v>469</v>
-      </c>
       <c r="F414" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="415" spans="1:6">
       <c r="A415" t="s">
-        <v>35</v>
+        <v>361</v>
       </c>
       <c r="B415" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C415" t="s">
-        <v>471</v>
+        <v>363</v>
       </c>
       <c r="D415" t="s">
         <v>11</v>
       </c>
       <c r="F415" t="s">
-        <v>363</v>
+        <v>42</v>
       </c>
     </row>
     <row r="416" spans="1:6">
       <c r="A416" t="s">
-        <v>364</v>
-      </c>
-      <c r="B416" t="s">
-        <v>472</v>
-      </c>
-      <c r="C416" t="s">
-        <v>380</v>
-      </c>
-      <c r="D416" t="s">
-        <v>11</v>
-      </c>
-      <c r="F416" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="417" spans="1:6">
       <c r="A417" t="s">
-        <v>367</v>
+        <v>8</v>
       </c>
       <c r="B417" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="C417" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="D417" t="s">
         <v>11</v>
       </c>
+      <c r="E417" t="s">
+        <v>468</v>
+      </c>
       <c r="F417" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="418" spans="1:6">
       <c r="A418" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="B418" t="s">
+        <v>469</v>
+      </c>
+      <c r="C418" t="s">
+        <v>470</v>
+      </c>
+      <c r="D418" t="s">
+        <v>11</v>
+      </c>
+      <c r="F418" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="419" spans="1:6">
       <c r="A419" t="s">
-        <v>8</v>
+        <v>358</v>
       </c>
       <c r="B419" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="C419" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="D419" t="s">
         <v>11</v>
       </c>
-      <c r="E419" t="s">
-        <v>475</v>
-      </c>
       <c r="F419" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="420" spans="1:6">
       <c r="A420" t="s">
-        <v>35</v>
+        <v>361</v>
       </c>
       <c r="B420" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="C420" t="s">
-        <v>477</v>
+        <v>363</v>
       </c>
       <c r="D420" t="s">
         <v>11</v>
       </c>
       <c r="F420" t="s">
-        <v>363</v>
+        <v>42</v>
       </c>
     </row>
     <row r="421" spans="1:6">
       <c r="A421" t="s">
-        <v>364</v>
-      </c>
-      <c r="B421" t="s">
-        <v>478</v>
-      </c>
-      <c r="C421" t="s">
-        <v>380</v>
-      </c>
-      <c r="D421" t="s">
-        <v>11</v>
-      </c>
-      <c r="F421" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="422" spans="1:6">
       <c r="A422" t="s">
-        <v>367</v>
+        <v>8</v>
       </c>
       <c r="B422" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="C422" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="D422" t="s">
         <v>11</v>
       </c>
+      <c r="E422" t="s">
+        <v>474</v>
+      </c>
       <c r="F422" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="423" spans="1:6">
       <c r="A423" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="B423" t="s">
+        <v>475</v>
+      </c>
+      <c r="C423" t="s">
+        <v>476</v>
+      </c>
+      <c r="D423" t="s">
+        <v>11</v>
+      </c>
+      <c r="F423" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="424" spans="1:6">
       <c r="A424" t="s">
-        <v>8</v>
+        <v>358</v>
       </c>
       <c r="B424" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="C424" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="D424" t="s">
         <v>11</v>
       </c>
-      <c r="E424" t="s">
-        <v>481</v>
-      </c>
       <c r="F424" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="425" spans="1:6">
       <c r="A425" t="s">
-        <v>35</v>
+        <v>361</v>
       </c>
       <c r="B425" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="C425" t="s">
-        <v>483</v>
+        <v>363</v>
       </c>
       <c r="D425" t="s">
         <v>11</v>
       </c>
       <c r="F425" t="s">
-        <v>363</v>
+        <v>42</v>
       </c>
     </row>
     <row r="426" spans="1:6">
       <c r="A426" t="s">
-        <v>364</v>
-      </c>
-      <c r="B426" t="s">
-        <v>484</v>
-      </c>
-      <c r="C426" t="s">
-        <v>380</v>
-      </c>
-      <c r="D426" t="s">
-        <v>11</v>
-      </c>
-      <c r="F426" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="427" spans="1:6">
       <c r="A427" t="s">
-        <v>367</v>
+        <v>8</v>
       </c>
       <c r="B427" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="C427" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="D427" t="s">
         <v>11</v>
       </c>
+      <c r="E427" t="s">
+        <v>480</v>
+      </c>
       <c r="F427" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="428" spans="1:6">
       <c r="A428" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="B428" t="s">
+        <v>481</v>
+      </c>
+      <c r="C428" t="s">
+        <v>183</v>
+      </c>
+      <c r="D428" t="s">
+        <v>11</v>
+      </c>
+      <c r="F428" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="429" spans="1:6">
       <c r="A429" t="s">
-        <v>8</v>
+        <v>358</v>
       </c>
       <c r="B429" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="C429" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="D429" t="s">
         <v>11</v>
       </c>
-      <c r="E429" t="s">
-        <v>487</v>
-      </c>
       <c r="F429" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="430" spans="1:6">
       <c r="A430" t="s">
-        <v>35</v>
+        <v>361</v>
       </c>
       <c r="B430" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="C430" t="s">
-        <v>183</v>
+        <v>363</v>
       </c>
       <c r="D430" t="s">
         <v>11</v>
       </c>
       <c r="F430" t="s">
-        <v>363</v>
+        <v>42</v>
       </c>
     </row>
     <row r="431" spans="1:6">
       <c r="A431" t="s">
-        <v>364</v>
-      </c>
-      <c r="B431" t="s">
-        <v>489</v>
-      </c>
-      <c r="C431" t="s">
-        <v>380</v>
-      </c>
-      <c r="D431" t="s">
-        <v>11</v>
-      </c>
-      <c r="F431" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="432" spans="1:6">
       <c r="A432" t="s">
-        <v>367</v>
+        <v>8</v>
       </c>
       <c r="B432" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="C432" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="D432" t="s">
         <v>11</v>
       </c>
+      <c r="E432" t="s">
+        <v>485</v>
+      </c>
       <c r="F432" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="433" spans="1:6">
       <c r="A433" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="B433" t="s">
+        <v>486</v>
+      </c>
+      <c r="C433" t="s">
+        <v>191</v>
+      </c>
+      <c r="D433" t="s">
+        <v>11</v>
+      </c>
+      <c r="F433" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="434" spans="1:6">
       <c r="A434" t="s">
-        <v>8</v>
+        <v>358</v>
       </c>
       <c r="B434" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C434" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="D434" t="s">
         <v>11</v>
       </c>
-      <c r="E434" t="s">
-        <v>492</v>
-      </c>
       <c r="F434" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="435" spans="1:6">
       <c r="A435" t="s">
-        <v>35</v>
+        <v>361</v>
       </c>
       <c r="B435" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="C435" t="s">
-        <v>191</v>
+        <v>363</v>
       </c>
       <c r="D435" t="s">
         <v>11</v>
       </c>
       <c r="F435" t="s">
-        <v>363</v>
+        <v>42</v>
       </c>
     </row>
     <row r="436" spans="1:6">
       <c r="A436" t="s">
-        <v>364</v>
-      </c>
-      <c r="B436" t="s">
-        <v>494</v>
-      </c>
-      <c r="C436" t="s">
-        <v>380</v>
-      </c>
-      <c r="D436" t="s">
-        <v>11</v>
-      </c>
-      <c r="F436" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="437" spans="1:6">
       <c r="A437" t="s">
-        <v>367</v>
+        <v>8</v>
       </c>
       <c r="B437" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="C437" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="D437" t="s">
         <v>11</v>
       </c>
+      <c r="E437" t="s">
+        <v>490</v>
+      </c>
       <c r="F437" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="438" spans="1:6">
       <c r="A438" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="B438" t="s">
+        <v>491</v>
+      </c>
+      <c r="C438" t="s">
+        <v>199</v>
+      </c>
+      <c r="D438" t="s">
+        <v>11</v>
+      </c>
+      <c r="F438" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="439" spans="1:6">
       <c r="A439" t="s">
-        <v>8</v>
+        <v>358</v>
       </c>
       <c r="B439" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="C439" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="D439" t="s">
         <v>11</v>
       </c>
-      <c r="E439" t="s">
-        <v>497</v>
-      </c>
       <c r="F439" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="440" spans="1:6">
       <c r="A440" t="s">
-        <v>35</v>
+        <v>361</v>
       </c>
       <c r="B440" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="C440" t="s">
-        <v>199</v>
+        <v>363</v>
       </c>
       <c r="D440" t="s">
         <v>11</v>
       </c>
       <c r="F440" t="s">
-        <v>363</v>
+        <v>42</v>
       </c>
     </row>
     <row r="441" spans="1:6">
       <c r="A441" t="s">
-        <v>364</v>
-      </c>
-      <c r="B441" t="s">
-        <v>499</v>
-      </c>
-      <c r="C441" t="s">
-        <v>380</v>
-      </c>
-      <c r="D441" t="s">
-        <v>11</v>
-      </c>
-      <c r="F441" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="442" spans="1:6">
       <c r="A442" t="s">
-        <v>367</v>
+        <v>8</v>
       </c>
       <c r="B442" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="C442" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="D442" t="s">
         <v>11</v>
       </c>
+      <c r="E442" t="s">
+        <v>495</v>
+      </c>
       <c r="F442" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="443" spans="1:6">
       <c r="A443" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="B443" t="s">
+        <v>496</v>
+      </c>
+      <c r="C443" t="s">
+        <v>207</v>
+      </c>
+      <c r="D443" t="s">
+        <v>11</v>
+      </c>
+      <c r="F443" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="444" spans="1:6">
       <c r="A444" t="s">
-        <v>8</v>
+        <v>358</v>
       </c>
       <c r="B444" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="C444" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="D444" t="s">
         <v>11</v>
       </c>
-      <c r="E444" t="s">
-        <v>502</v>
-      </c>
       <c r="F444" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="445" spans="1:6">
       <c r="A445" t="s">
-        <v>35</v>
+        <v>361</v>
       </c>
       <c r="B445" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="C445" t="s">
-        <v>207</v>
+        <v>363</v>
       </c>
       <c r="D445" t="s">
         <v>11</v>
       </c>
       <c r="F445" t="s">
-        <v>363</v>
+        <v>42</v>
       </c>
     </row>
     <row r="446" spans="1:6">
       <c r="A446" t="s">
-        <v>364</v>
-      </c>
-      <c r="B446" t="s">
-        <v>504</v>
-      </c>
-      <c r="C446" t="s">
-        <v>380</v>
-      </c>
-      <c r="D446" t="s">
-        <v>11</v>
-      </c>
-      <c r="F446" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="447" spans="1:6">
       <c r="A447" t="s">
-        <v>367</v>
+        <v>8</v>
       </c>
       <c r="B447" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="C447" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="D447" t="s">
         <v>11</v>
       </c>
+      <c r="E447" t="s">
+        <v>500</v>
+      </c>
       <c r="F447" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="448" spans="1:6">
       <c r="A448" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="B448" t="s">
+        <v>501</v>
+      </c>
+      <c r="C448" t="s">
+        <v>215</v>
+      </c>
+      <c r="D448" t="s">
+        <v>11</v>
+      </c>
+      <c r="F448" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="449" spans="1:6">
       <c r="A449" t="s">
-        <v>8</v>
+        <v>358</v>
       </c>
       <c r="B449" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="C449" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="D449" t="s">
         <v>11</v>
       </c>
-      <c r="E449" t="s">
-        <v>507</v>
-      </c>
       <c r="F449" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="450" spans="1:6">
       <c r="A450" t="s">
-        <v>35</v>
+        <v>361</v>
       </c>
       <c r="B450" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="C450" t="s">
-        <v>215</v>
+        <v>363</v>
       </c>
       <c r="D450" t="s">
         <v>11</v>
       </c>
       <c r="F450" t="s">
-        <v>363</v>
+        <v>42</v>
       </c>
     </row>
     <row r="451" spans="1:6">
       <c r="A451" t="s">
-        <v>364</v>
-      </c>
-      <c r="B451" t="s">
-        <v>509</v>
-      </c>
-      <c r="C451" t="s">
-        <v>380</v>
-      </c>
-      <c r="D451" t="s">
-        <v>11</v>
-      </c>
-      <c r="F451" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="452" spans="1:6">
       <c r="A452" t="s">
-        <v>367</v>
+        <v>8</v>
       </c>
       <c r="B452" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="C452" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="D452" t="s">
         <v>11</v>
       </c>
+      <c r="E452" t="s">
+        <v>505</v>
+      </c>
       <c r="F452" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="453" spans="1:6">
       <c r="A453" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="B453" t="s">
+        <v>506</v>
+      </c>
+      <c r="C453" t="s">
+        <v>223</v>
+      </c>
+      <c r="D453" t="s">
+        <v>11</v>
+      </c>
+      <c r="F453" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="454" spans="1:6">
       <c r="A454" t="s">
-        <v>8</v>
+        <v>358</v>
       </c>
       <c r="B454" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="C454" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="D454" t="s">
         <v>11</v>
       </c>
-      <c r="E454" t="s">
-        <v>512</v>
-      </c>
       <c r="F454" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="455" spans="1:6">
       <c r="A455" t="s">
-        <v>35</v>
+        <v>361</v>
       </c>
       <c r="B455" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="C455" t="s">
-        <v>223</v>
+        <v>363</v>
       </c>
       <c r="D455" t="s">
         <v>11</v>
       </c>
       <c r="F455" t="s">
-        <v>363</v>
+        <v>42</v>
       </c>
     </row>
     <row r="456" spans="1:6">
       <c r="A456" t="s">
-        <v>364</v>
-      </c>
-      <c r="B456" t="s">
-        <v>514</v>
-      </c>
-      <c r="C456" t="s">
-        <v>380</v>
-      </c>
-      <c r="D456" t="s">
-        <v>11</v>
-      </c>
-      <c r="F456" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="457" spans="1:6">
       <c r="A457" t="s">
-        <v>367</v>
+        <v>8</v>
       </c>
       <c r="B457" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="C457" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="D457" t="s">
         <v>11</v>
       </c>
+      <c r="E457" t="s">
+        <v>510</v>
+      </c>
       <c r="F457" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="458" spans="1:6">
       <c r="A458" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="B458" t="s">
+        <v>511</v>
+      </c>
+      <c r="C458" t="s">
+        <v>234</v>
+      </c>
+      <c r="D458" t="s">
+        <v>11</v>
+      </c>
+      <c r="F458" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="459" spans="1:6">
       <c r="A459" t="s">
-        <v>8</v>
+        <v>358</v>
       </c>
       <c r="B459" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="C459" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="D459" t="s">
         <v>11</v>
       </c>
-      <c r="E459" t="s">
-        <v>517</v>
-      </c>
       <c r="F459" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="460" spans="1:6">
       <c r="A460" t="s">
-        <v>35</v>
+        <v>361</v>
       </c>
       <c r="B460" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="C460" t="s">
-        <v>234</v>
+        <v>363</v>
       </c>
       <c r="D460" t="s">
         <v>11</v>
       </c>
       <c r="F460" t="s">
-        <v>363</v>
+        <v>42</v>
       </c>
     </row>
     <row r="461" spans="1:6">
       <c r="A461" t="s">
-        <v>364</v>
-      </c>
-      <c r="B461" t="s">
-        <v>519</v>
-      </c>
-      <c r="C461" t="s">
-        <v>380</v>
-      </c>
-      <c r="D461" t="s">
-        <v>11</v>
-      </c>
-      <c r="F461" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="462" spans="1:6">
       <c r="A462" t="s">
-        <v>367</v>
+        <v>8</v>
       </c>
       <c r="B462" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="C462" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="D462" t="s">
         <v>11</v>
       </c>
+      <c r="E462" t="s">
+        <v>515</v>
+      </c>
       <c r="F462" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="463" spans="1:6">
       <c r="A463" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="B463" t="s">
+        <v>516</v>
+      </c>
+      <c r="C463" t="s">
+        <v>242</v>
+      </c>
+      <c r="D463" t="s">
+        <v>11</v>
+      </c>
+      <c r="F463" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="464" spans="1:6">
       <c r="A464" t="s">
-        <v>8</v>
+        <v>358</v>
       </c>
       <c r="B464" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="C464" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="D464" t="s">
         <v>11</v>
       </c>
-      <c r="E464" t="s">
-        <v>522</v>
-      </c>
       <c r="F464" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="465" spans="1:6">
       <c r="A465" t="s">
-        <v>35</v>
+        <v>361</v>
       </c>
       <c r="B465" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="C465" t="s">
-        <v>242</v>
+        <v>363</v>
       </c>
       <c r="D465" t="s">
         <v>11</v>
       </c>
       <c r="F465" t="s">
-        <v>363</v>
+        <v>42</v>
       </c>
     </row>
     <row r="466" spans="1:6">
       <c r="A466" t="s">
-        <v>364</v>
-      </c>
-      <c r="B466" t="s">
-        <v>524</v>
-      </c>
-      <c r="C466" t="s">
-        <v>380</v>
-      </c>
-      <c r="D466" t="s">
-        <v>11</v>
-      </c>
-      <c r="F466" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="467" spans="1:6">
       <c r="A467" t="s">
-        <v>367</v>
+        <v>8</v>
       </c>
       <c r="B467" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="C467" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="D467" t="s">
         <v>11</v>
       </c>
+      <c r="E467" t="s">
+        <v>520</v>
+      </c>
       <c r="F467" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="468" spans="1:6">
       <c r="A468" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="B468" t="s">
+        <v>521</v>
+      </c>
+      <c r="C468" t="s">
+        <v>250</v>
+      </c>
+      <c r="D468" t="s">
+        <v>11</v>
+      </c>
+      <c r="F468" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="469" spans="1:6">
       <c r="A469" t="s">
-        <v>8</v>
+        <v>358</v>
       </c>
       <c r="B469" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="C469" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="D469" t="s">
         <v>11</v>
       </c>
-      <c r="E469" t="s">
-        <v>527</v>
-      </c>
       <c r="F469" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="470" spans="1:6">
       <c r="A470" t="s">
-        <v>35</v>
+        <v>361</v>
       </c>
       <c r="B470" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="C470" t="s">
-        <v>250</v>
+        <v>363</v>
       </c>
       <c r="D470" t="s">
         <v>11</v>
       </c>
       <c r="F470" t="s">
-        <v>363</v>
+        <v>42</v>
       </c>
     </row>
     <row r="471" spans="1:6">
       <c r="A471" t="s">
-        <v>364</v>
-      </c>
-      <c r="B471" t="s">
-        <v>529</v>
-      </c>
-      <c r="C471" t="s">
-        <v>380</v>
-      </c>
-      <c r="D471" t="s">
-        <v>11</v>
-      </c>
-      <c r="F471" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="472" spans="1:6">
-      <c r="A472" t="s">
-        <v>367</v>
-      </c>
-      <c r="B472" t="s">
-        <v>530</v>
-      </c>
-      <c r="C472" t="s">
-        <v>382</v>
-      </c>
-      <c r="D472" t="s">
-        <v>11</v>
-      </c>
-      <c r="F472" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="473" spans="1:6">
@@ -9765,18 +9727,55 @@
     </row>
     <row r="475" spans="1:6">
       <c r="A475" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="B475" t="s">
+        <v>524</v>
+      </c>
+      <c r="C475" t="s">
+        <v>525</v>
+      </c>
+      <c r="D475" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="476" spans="1:6">
+      <c r="A476" t="s">
+        <v>526</v>
+      </c>
+      <c r="B476" t="s">
+        <v>527</v>
+      </c>
+      <c r="C476" t="s">
+        <v>528</v>
+      </c>
+      <c r="D476" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="477" spans="1:6">
+      <c r="A477" t="s">
+        <v>529</v>
+      </c>
+      <c r="B477" t="s">
+        <v>530</v>
+      </c>
+      <c r="C477" t="s">
+        <v>531</v>
+      </c>
+      <c r="D477" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="478" spans="1:6">
       <c r="A478" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B478" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C478" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D478" t="s">
         <v>11</v>
@@ -9784,7 +9783,7 @@
     </row>
     <row r="479" spans="1:6">
       <c r="A479" t="s">
-        <v>534</v>
+        <v>12</v>
       </c>
       <c r="B479" t="s">
         <v>535</v>
@@ -9823,13 +9822,10 @@
       <c r="D481" t="s">
         <v>11</v>
       </c>
-      <c r="E481" t="s">
-        <v>543</v>
-      </c>
     </row>
     <row r="482" spans="1:5">
       <c r="A482" t="s">
-        <v>12</v>
+        <v>543</v>
       </c>
       <c r="B482" t="s">
         <v>544</v>
@@ -9843,41 +9839,35 @@
     </row>
     <row r="483" spans="1:5">
       <c r="A483" t="s">
-        <v>546</v>
-      </c>
-      <c r="B483" t="s">
-        <v>547</v>
-      </c>
-      <c r="C483" t="s">
-        <v>548</v>
-      </c>
-      <c r="D483" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="484" spans="1:5">
       <c r="A484" t="s">
-        <v>549</v>
+        <v>8</v>
       </c>
       <c r="B484" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="C484" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="D484" t="s">
         <v>11</v>
+      </c>
+      <c r="E484" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="485" spans="1:5">
       <c r="A485" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="B485" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="C485" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="D485" t="s">
         <v>11</v>
@@ -9885,32 +9875,47 @@
     </row>
     <row r="486" spans="1:5">
       <c r="A486" t="s">
-        <v>22</v>
+        <v>551</v>
+      </c>
+      <c r="B486" t="s">
+        <v>552</v>
+      </c>
+      <c r="C486" t="s">
+        <v>553</v>
+      </c>
+      <c r="D486" t="s">
+        <v>11</v>
+      </c>
+      <c r="E486" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="487" spans="1:5">
       <c r="A487" t="s">
-        <v>8</v>
+        <v>555</v>
       </c>
       <c r="B487" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C487" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D487" t="s">
         <v>11</v>
+      </c>
+      <c r="E487" t="s">
+        <v>558</v>
       </c>
     </row>
     <row r="488" spans="1:5">
       <c r="A488" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B488" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C488" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D488" t="s">
         <v>11</v>
@@ -9918,27 +9923,27 @@
     </row>
     <row r="489" spans="1:5">
       <c r="A489" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B489" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C489" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D489" t="s">
         <v>11</v>
       </c>
       <c r="E489" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="490" spans="1:5">
       <c r="A490" t="s">
-        <v>564</v>
+        <v>12</v>
       </c>
       <c r="B490" t="s">
-        <v>565</v>
+        <v>535</v>
       </c>
       <c r="C490" t="s">
         <v>566</v>
@@ -9946,19 +9951,16 @@
       <c r="D490" t="s">
         <v>11</v>
       </c>
-      <c r="E490" t="s">
-        <v>567</v>
-      </c>
     </row>
     <row r="491" spans="1:5">
       <c r="A491" t="s">
+        <v>567</v>
+      </c>
+      <c r="B491" t="s">
         <v>568</v>
       </c>
-      <c r="B491" t="s">
+      <c r="C491" t="s">
         <v>569</v>
-      </c>
-      <c r="C491" t="s">
-        <v>570</v>
       </c>
       <c r="D491" t="s">
         <v>11</v>
@@ -9966,24 +9968,24 @@
     </row>
     <row r="492" spans="1:5">
       <c r="A492" t="s">
+        <v>12</v>
+      </c>
+      <c r="B492" t="s">
+        <v>570</v>
+      </c>
+      <c r="C492" t="s">
         <v>571</v>
       </c>
-      <c r="B492" t="s">
+      <c r="D492" t="s">
+        <v>11</v>
+      </c>
+      <c r="E492" t="s">
         <v>572</v>
-      </c>
-      <c r="C492" t="s">
-        <v>573</v>
-      </c>
-      <c r="D492" t="s">
-        <v>11</v>
-      </c>
-      <c r="E492" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="493" spans="1:5">
       <c r="A493" t="s">
-        <v>12</v>
+        <v>573</v>
       </c>
       <c r="B493" t="s">
         <v>574</v>
@@ -9997,33 +9999,33 @@
     </row>
     <row r="494" spans="1:5">
       <c r="A494" t="s">
+        <v>12</v>
+      </c>
+      <c r="B494" t="s">
         <v>576</v>
       </c>
-      <c r="B494" t="s">
+      <c r="C494" t="s">
         <v>577</v>
       </c>
-      <c r="C494" t="s">
+      <c r="D494" t="s">
+        <v>11</v>
+      </c>
+      <c r="E494" t="s">
         <v>578</v>
-      </c>
-      <c r="D494" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="495" spans="1:5">
       <c r="A495" t="s">
-        <v>12</v>
+        <v>579</v>
       </c>
       <c r="B495" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C495" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D495" t="s">
         <v>11</v>
-      </c>
-      <c r="E495" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="496" spans="1:5">
@@ -10039,225 +10041,232 @@
       <c r="D496" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="497" spans="1:6">
+      <c r="E496" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="497" spans="1:5">
       <c r="A497" t="s">
         <v>12</v>
       </c>
       <c r="B497" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C497" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D497" t="s">
         <v>11</v>
       </c>
       <c r="E497" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="498" spans="1:6">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="498" spans="1:5">
       <c r="A498" t="s">
-        <v>588</v>
-      </c>
-      <c r="B498" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="499" spans="1:5">
+      <c r="A499" t="s">
+        <v>8</v>
+      </c>
+      <c r="B499" t="s">
         <v>589</v>
       </c>
-      <c r="C498" t="s">
+      <c r="C499" t="s">
         <v>590</v>
       </c>
-      <c r="D498" t="s">
-        <v>11</v>
-      </c>
-      <c r="F498" t="s">
+      <c r="D499" t="s">
+        <v>11</v>
+      </c>
+      <c r="E499" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="500" spans="1:5">
+      <c r="A500" t="s">
+        <v>8</v>
+      </c>
+      <c r="B500" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="499" spans="1:6">
-      <c r="A499" t="s">
+      <c r="D500" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="501" spans="1:5">
+      <c r="A501" t="s">
+        <v>35</v>
+      </c>
+      <c r="B501" t="s">
         <v>592</v>
       </c>
-      <c r="B499" t="s">
+      <c r="C501" t="s">
         <v>593</v>
       </c>
-      <c r="C499" t="s">
+      <c r="D501" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="502" spans="1:5">
+      <c r="A502" t="s">
         <v>594</v>
       </c>
-      <c r="D499" t="s">
-        <v>11</v>
-      </c>
-      <c r="E499" t="s">
+      <c r="B502" t="s">
         <v>595</v>
       </c>
-      <c r="F499" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="500" spans="1:6">
-      <c r="A500" t="s">
-        <v>12</v>
-      </c>
-      <c r="B500" t="s">
+      <c r="C502" t="s">
         <v>596</v>
       </c>
-      <c r="C500" t="s">
+      <c r="D502" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="503" spans="1:5">
+      <c r="A503" t="s">
+        <v>594</v>
+      </c>
+      <c r="B503" t="s">
         <v>597</v>
       </c>
-      <c r="D500" t="s">
-        <v>11</v>
-      </c>
-      <c r="E500" t="s">
+      <c r="C503" t="s">
         <v>598</v>
       </c>
-      <c r="F500" t="s">
+      <c r="D503" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="504" spans="1:5">
+      <c r="A504" t="s">
+        <v>594</v>
+      </c>
+      <c r="B504" t="s">
         <v>599</v>
       </c>
-    </row>
-    <row r="501" spans="1:6">
-      <c r="A501" t="s">
+      <c r="C504" t="s">
+        <v>600</v>
+      </c>
+      <c r="D504" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="505" spans="1:5">
+      <c r="A505" t="s">
         <v>22</v>
       </c>
-      <c r="F501" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="502" spans="1:6">
-      <c r="A502" t="s">
-        <v>8</v>
-      </c>
-      <c r="B502" t="s">
-        <v>600</v>
-      </c>
-      <c r="C502" t="s">
+    </row>
+    <row r="506" spans="1:5">
+      <c r="A506" t="s">
+        <v>35</v>
+      </c>
+      <c r="B506" t="s">
         <v>601</v>
       </c>
-      <c r="D502" t="s">
-        <v>11</v>
-      </c>
-      <c r="F502" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="503" spans="1:6">
-      <c r="A503" t="s">
-        <v>8</v>
-      </c>
-      <c r="B503" t="s">
+      <c r="C506" t="s">
+        <v>525</v>
+      </c>
+      <c r="D506" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="507" spans="1:5">
+      <c r="A507" t="s">
         <v>602</v>
       </c>
-      <c r="D503" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="504" spans="1:6">
-      <c r="A504" t="s">
+      <c r="B507" t="s">
         <v>603</v>
       </c>
-      <c r="B504" t="s">
+      <c r="C507" t="s">
         <v>604</v>
       </c>
-      <c r="C504" t="s">
-        <v>605</v>
-      </c>
-      <c r="D504" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="505" spans="1:6">
-      <c r="A505" t="s">
-        <v>603</v>
-      </c>
-      <c r="B505" t="s">
-        <v>606</v>
-      </c>
-      <c r="C505" t="s">
-        <v>607</v>
-      </c>
-      <c r="D505" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="506" spans="1:6">
-      <c r="A506" t="s">
-        <v>603</v>
-      </c>
-      <c r="B506" t="s">
-        <v>608</v>
-      </c>
-      <c r="C506" t="s">
-        <v>609</v>
-      </c>
-      <c r="D506" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="507" spans="1:6">
-      <c r="A507" t="s">
-        <v>603</v>
-      </c>
-      <c r="B507" t="s">
-        <v>610</v>
-      </c>
-      <c r="C507" t="s">
-        <v>611</v>
-      </c>
       <c r="D507" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="508" spans="1:6">
+    <row r="508" spans="1:5">
       <c r="A508" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="509" spans="1:6">
+    <row r="509" spans="1:5">
       <c r="A509" t="s">
-        <v>612</v>
+        <v>8</v>
       </c>
       <c r="B509" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="C509" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="D509" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="510" spans="1:6">
+    <row r="510" spans="1:5">
       <c r="A510" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="B510" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="C510" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="D510" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="511" spans="1:6">
+    <row r="511" spans="1:5">
       <c r="A511" t="s">
         <v>12</v>
       </c>
       <c r="B511" t="s">
+        <v>610</v>
+      </c>
+      <c r="C511" t="s">
+        <v>611</v>
+      </c>
+      <c r="D511" t="s">
+        <v>11</v>
+      </c>
+      <c r="E511" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="512" spans="1:5">
+      <c r="A512" t="s">
+        <v>613</v>
+      </c>
+      <c r="B512" t="s">
+        <v>614</v>
+      </c>
+      <c r="C512" t="s">
+        <v>615</v>
+      </c>
+      <c r="D512" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="513" spans="1:5">
+      <c r="A513" t="s">
+        <v>12</v>
+      </c>
+      <c r="B513" t="s">
+        <v>616</v>
+      </c>
+      <c r="C513" t="s">
+        <v>617</v>
+      </c>
+      <c r="D513" t="s">
+        <v>11</v>
+      </c>
+      <c r="E513" t="s">
         <v>618</v>
       </c>
-      <c r="C511" t="s">
-        <v>619</v>
-      </c>
-      <c r="D511" t="s">
-        <v>11</v>
-      </c>
-      <c r="E511" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="512" spans="1:6">
-      <c r="A512" t="s">
+    </row>
+    <row r="514" spans="1:5">
+      <c r="A514" t="s">
         <v>22</v>
       </c>
     </row>
@@ -10268,7 +10277,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D105"/>
+  <dimension ref="A1:D104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="41.85546875" customWidth="1"/>
@@ -10277,7 +10286,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -10286,642 +10295,642 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
+        <v>621</v>
+      </c>
+      <c r="B2" t="s">
+        <v>622</v>
+      </c>
+      <c r="C2" t="s">
         <v>623</v>
-      </c>
-      <c r="B2" t="s">
-        <v>624</v>
-      </c>
-      <c r="C2" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B3" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C3" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
+        <v>626</v>
+      </c>
+      <c r="B4" t="s">
+        <v>627</v>
+      </c>
+      <c r="C4" t="s">
         <v>628</v>
-      </c>
-      <c r="B4" t="s">
-        <v>629</v>
-      </c>
-      <c r="C4" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B5" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C5" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B6" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C6" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B7" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C7" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B8" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C8" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B9" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C9" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B10" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C10" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
+        <v>641</v>
+      </c>
+      <c r="B11" t="s">
+        <v>642</v>
+      </c>
+      <c r="C11" t="s">
         <v>643</v>
-      </c>
-      <c r="B11" t="s">
-        <v>644</v>
-      </c>
-      <c r="C11" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B12" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C12" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B13" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C13" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B14" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C14" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
+        <v>650</v>
+      </c>
+      <c r="B15" t="s">
+        <v>651</v>
+      </c>
+      <c r="C15" t="s">
         <v>652</v>
-      </c>
-      <c r="B15" t="s">
-        <v>653</v>
-      </c>
-      <c r="C15" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B16" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C16" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B17" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C17" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B18" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C18" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B19" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C19" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
+        <v>661</v>
+      </c>
+      <c r="B20" t="s">
+        <v>662</v>
+      </c>
+      <c r="C20" t="s">
         <v>663</v>
-      </c>
-      <c r="B20" t="s">
-        <v>664</v>
-      </c>
-      <c r="C20" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B21" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C21" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B22" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C22" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B23" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C23" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B24" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C24" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
+        <v>672</v>
+      </c>
+      <c r="B25" t="s">
+        <v>673</v>
+      </c>
+      <c r="C25" t="s">
         <v>674</v>
-      </c>
-      <c r="B25" t="s">
-        <v>675</v>
-      </c>
-      <c r="C25" t="s">
-        <v>676</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B26" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C26" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B27" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C27" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
+        <v>679</v>
+      </c>
+      <c r="B28" t="s">
+        <v>680</v>
+      </c>
+      <c r="C28" t="s">
         <v>681</v>
-      </c>
-      <c r="B28" t="s">
-        <v>682</v>
-      </c>
-      <c r="C28" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B29" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C29" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B30" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C30" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
+        <v>685</v>
+      </c>
+      <c r="B31" t="s">
+        <v>686</v>
+      </c>
+      <c r="C31" t="s">
         <v>687</v>
-      </c>
-      <c r="B31" t="s">
-        <v>688</v>
-      </c>
-      <c r="C31" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B32" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="C32" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B33" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C33" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B34" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="C34" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
+        <v>691</v>
+      </c>
+      <c r="B35" t="s">
+        <v>692</v>
+      </c>
+      <c r="C35" t="s">
         <v>693</v>
-      </c>
-      <c r="B35" t="s">
-        <v>694</v>
-      </c>
-      <c r="C35" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B36" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C36" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
+        <v>696</v>
+      </c>
+      <c r="B37" t="s">
+        <v>697</v>
+      </c>
+      <c r="C37" t="s">
         <v>698</v>
-      </c>
-      <c r="B37" t="s">
-        <v>699</v>
-      </c>
-      <c r="C37" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B38" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C38" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
+        <v>701</v>
+      </c>
+      <c r="B39" t="s">
+        <v>702</v>
+      </c>
+      <c r="C39" t="s">
         <v>703</v>
-      </c>
-      <c r="B39" t="s">
-        <v>704</v>
-      </c>
-      <c r="C39" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B40" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C40" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B41" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="C41" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
+        <v>708</v>
+      </c>
+      <c r="B42" t="s">
+        <v>709</v>
+      </c>
+      <c r="C42" t="s">
         <v>710</v>
-      </c>
-      <c r="B42" t="s">
-        <v>711</v>
-      </c>
-      <c r="C42" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B43" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="C43" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B44" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C44" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="B45" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C45" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="B46" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="C46" t="s">
-        <v>720</v>
+        <v>717</v>
+      </c>
+      <c r="D46" t="s">
+        <v>716</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="B47" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="C47" t="s">
-        <v>721</v>
-      </c>
-      <c r="D47" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
+        <v>715</v>
+      </c>
+      <c r="B48" t="s">
         <v>719</v>
       </c>
-      <c r="B48" t="s">
-        <v>722</v>
-      </c>
       <c r="C48" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B49" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C49" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
+        <v>720</v>
+      </c>
+      <c r="B50" t="s">
+        <v>723</v>
+      </c>
+      <c r="C50" t="s">
         <v>724</v>
-      </c>
-      <c r="B50" t="s">
-        <v>725</v>
-      </c>
-      <c r="C50" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="B51" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C51" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="B52" t="s">
+        <v>728</v>
+      </c>
+      <c r="C52" t="s">
         <v>729</v>
-      </c>
-      <c r="C52" t="s">
-        <v>730</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
+        <v>727</v>
+      </c>
+      <c r="B53" t="s">
+        <v>730</v>
+      </c>
+      <c r="C53" t="s">
         <v>731</v>
-      </c>
-      <c r="B53" t="s">
-        <v>732</v>
-      </c>
-      <c r="C53" t="s">
-        <v>733</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B54" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C54" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
+        <v>734</v>
+      </c>
+      <c r="B55" t="s">
+        <v>730</v>
+      </c>
+      <c r="C55" t="s">
         <v>731</v>
-      </c>
-      <c r="B55" t="s">
-        <v>736</v>
-      </c>
-      <c r="C55" t="s">
-        <v>737</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="B56" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C56" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="B57" t="s">
+        <v>735</v>
+      </c>
+      <c r="C57" t="s">
         <v>736</v>
-      </c>
-      <c r="C57" t="s">
-        <v>737</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B58" t="s">
-        <v>739</v>
+        <v>686</v>
       </c>
       <c r="C58" t="s">
-        <v>740</v>
+        <v>687</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B59" t="s">
         <v>688</v>
@@ -10932,18 +10941,18 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="B60" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="C60" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="B61" t="s">
         <v>688</v>
@@ -10954,62 +10963,62 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="B62" t="s">
-        <v>690</v>
+        <v>740</v>
       </c>
       <c r="C62" t="s">
-        <v>691</v>
+        <v>741</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
+        <v>739</v>
+      </c>
+      <c r="B63" t="s">
+        <v>742</v>
+      </c>
+      <c r="C63" t="s">
         <v>743</v>
-      </c>
-      <c r="B63" t="s">
-        <v>744</v>
-      </c>
-      <c r="C63" t="s">
-        <v>745</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="B64" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="C64" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="B65" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C65" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="B66" t="s">
-        <v>750</v>
+        <v>686</v>
       </c>
       <c r="C66" t="s">
-        <v>751</v>
+        <v>687</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="B67" t="s">
         <v>688</v>
@@ -11020,62 +11029,62 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="B68" t="s">
-        <v>690</v>
+        <v>740</v>
       </c>
       <c r="C68" t="s">
-        <v>691</v>
+        <v>741</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B69" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="C69" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B70" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="C70" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B71" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C71" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="B72" t="s">
-        <v>750</v>
+        <v>686</v>
       </c>
       <c r="C72" t="s">
-        <v>751</v>
+        <v>687</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="B73" t="s">
         <v>688</v>
@@ -11086,73 +11095,73 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="B74" t="s">
-        <v>690</v>
+        <v>751</v>
       </c>
       <c r="C74" t="s">
-        <v>691</v>
+        <v>752</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
+        <v>753</v>
+      </c>
+      <c r="B75" t="s">
         <v>754</v>
       </c>
-      <c r="B75" t="s">
+      <c r="C75" t="s">
         <v>755</v>
-      </c>
-      <c r="C75" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
+        <v>753</v>
+      </c>
+      <c r="B76" t="s">
+        <v>756</v>
+      </c>
+      <c r="C76" t="s">
         <v>757</v>
-      </c>
-      <c r="B76" t="s">
-        <v>758</v>
-      </c>
-      <c r="C76" t="s">
-        <v>759</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="B77" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="C77" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="B78" t="s">
-        <v>762</v>
+        <v>639</v>
       </c>
       <c r="C78" t="s">
-        <v>763</v>
+        <v>684</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="B79" t="s">
-        <v>641</v>
+        <v>686</v>
       </c>
       <c r="C79" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="B80" t="s">
         <v>688</v>
@@ -11163,238 +11172,238 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="B81" t="s">
-        <v>690</v>
+        <v>762</v>
       </c>
       <c r="C81" t="s">
-        <v>691</v>
+        <v>763</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
+        <v>761</v>
+      </c>
+      <c r="B82" t="s">
+        <v>764</v>
+      </c>
+      <c r="C82" t="s">
         <v>765</v>
-      </c>
-      <c r="B82" t="s">
-        <v>766</v>
-      </c>
-      <c r="C82" t="s">
-        <v>767</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="B83" t="s">
-        <v>768</v>
+        <v>639</v>
       </c>
       <c r="C83" t="s">
-        <v>769</v>
+        <v>684</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B84" t="s">
-        <v>641</v>
+        <v>767</v>
       </c>
       <c r="C84" t="s">
-        <v>686</v>
+        <v>768</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
+        <v>766</v>
+      </c>
+      <c r="B85" t="s">
+        <v>769</v>
+      </c>
+      <c r="C85" t="s">
         <v>770</v>
-      </c>
-      <c r="B85" t="s">
-        <v>771</v>
-      </c>
-      <c r="C85" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="B86" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C86" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="B87" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C87" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
       <c r="B88" t="s">
+        <v>776</v>
+      </c>
+      <c r="C88" t="s">
         <v>777</v>
-      </c>
-      <c r="C88" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
+        <v>775</v>
+      </c>
+      <c r="B89" t="s">
+        <v>778</v>
+      </c>
+      <c r="C89" t="s">
         <v>779</v>
-      </c>
-      <c r="B89" t="s">
-        <v>780</v>
-      </c>
-      <c r="C89" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="B90" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="C90" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="B91" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C91" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="B92" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C92" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="B93" t="s">
+        <v>787</v>
+      </c>
+      <c r="C93" t="s">
         <v>788</v>
-      </c>
-      <c r="C93" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
+        <v>786</v>
+      </c>
+      <c r="B94" t="s">
+        <v>789</v>
+      </c>
+      <c r="C94" t="s">
         <v>790</v>
-      </c>
-      <c r="B94" t="s">
-        <v>791</v>
-      </c>
-      <c r="C94" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="B95" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="C95" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="B96" t="s">
+        <v>639</v>
+      </c>
+      <c r="C96" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="B97" t="s">
+        <v>794</v>
+      </c>
+      <c r="C97" t="s">
         <v>795</v>
-      </c>
-      <c r="C96" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3">
-      <c r="A97" t="s">
-        <v>790</v>
-      </c>
-      <c r="B97" t="s">
-        <v>641</v>
-      </c>
-      <c r="C97" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="C98" t="s">
         <v>797</v>
-      </c>
-      <c r="B98" t="s">
-        <v>798</v>
-      </c>
-      <c r="C98" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" s="1" t="s">
-        <v>797</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>800</v>
+        <v>793</v>
+      </c>
+      <c r="B99" t="s">
+        <v>798</v>
       </c>
       <c r="C99" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" s="1" t="s">
-        <v>797</v>
-      </c>
-      <c r="B100" t="s">
+        <v>793</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" t="s">
         <v>802</v>
       </c>
-      <c r="C100" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3">
-      <c r="A101" s="1" t="s">
-        <v>797</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>804</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>805</v>
+      <c r="B101" t="s">
+        <v>686</v>
+      </c>
+      <c r="C101" t="s">
+        <v>687</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="B102" t="s">
         <v>688</v>
@@ -11405,35 +11414,24 @@
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="B103" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="C103" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="B104" t="s">
         <v>688</v>
       </c>
       <c r="C104" t="s">
         <v>689</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3">
-      <c r="A105" t="s">
-        <v>807</v>
-      </c>
-      <c r="B105" t="s">
-        <v>690</v>
-      </c>
-      <c r="C105" t="s">
-        <v>691</v>
       </c>
     </row>
   </sheetData>
@@ -11448,12 +11446,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
     </row>
   </sheetData>

--- a/surveys/biochar_survey_december_2025.xlsx
+++ b/surveys/biochar_survey_december_2025.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F12D2D41-994E-45E4-9336-C8146BD259CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C4E07762-31C3-4608-9FAC-991CBC994265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2463" uniqueCount="806">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2466" uniqueCount="802">
   <si>
     <t>type</t>
   </si>
@@ -1076,27 +1076,15 @@
     <t>C.1) Since you were trained in making biochar, have you made it?</t>
   </si>
   <si>
-    <t>select_one ab5ut15</t>
-  </si>
-  <si>
-    <t>used_on_crops</t>
-  </si>
-  <si>
-    <t>C.1.a) Did you use it on crops?</t>
+    <t>group_biochar</t>
+  </si>
+  <si>
+    <t>C.1.a) Answer following:</t>
   </si>
   <si>
     <t>${made_biochar} = 'yes'</t>
   </si>
   <si>
-    <t>group_biochar</t>
-  </si>
-  <si>
-    <t>C.1.b) What crops did you use it on?</t>
-  </si>
-  <si>
-    <t>${used_on_crops} = 'yes'</t>
-  </si>
-  <si>
     <t>biochar_info_maize_1</t>
   </si>
   <si>
@@ -1652,7 +1640,7 @@
     <t>fertilizer_before_biochar</t>
   </si>
   <si>
-    <t>C.6) Before using biochar, did you use fertilizer?</t>
+    <t>C.6) Before using biochar, did you use fertilizer? (Select all that apply)</t>
   </si>
   <si>
     <t>select_multiple td2jb01</t>
@@ -2799,7 +2787,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F514"/>
+  <dimension ref="A1:F513"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.28515625" customWidth="1"/>
@@ -7260,83 +7248,83 @@
         <v>11</v>
       </c>
     </row>
-    <row r="308" spans="1:6">
-      <c r="A308" t="s">
+    <row r="309" spans="1:6">
+      <c r="A309" t="s">
+        <v>8</v>
+      </c>
+      <c r="B309" t="s">
         <v>347</v>
       </c>
-      <c r="B308" t="s">
+      <c r="C309" t="s">
         <v>348</v>
       </c>
-      <c r="C308" t="s">
+      <c r="D309" t="s">
+        <v>11</v>
+      </c>
+      <c r="E309" t="s">
         <v>349</v>
       </c>
-      <c r="D308" t="s">
-        <v>11</v>
-      </c>
-      <c r="E308" t="s">
+    </row>
+    <row r="311" spans="1:6">
+      <c r="A311" t="s">
+        <v>8</v>
+      </c>
+      <c r="B311" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="310" spans="1:6">
-      <c r="A310" t="s">
-        <v>8</v>
-      </c>
-      <c r="B310" t="s">
+      <c r="D311" t="s">
+        <v>11</v>
+      </c>
+      <c r="E311" t="s">
         <v>351</v>
       </c>
-      <c r="C310" t="s">
-        <v>352</v>
-      </c>
-      <c r="D310" t="s">
-        <v>11</v>
-      </c>
-      <c r="E310" t="s">
-        <v>353</v>
+      <c r="F311" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="312" spans="1:6">
       <c r="A312" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B312" t="s">
-        <v>354</v>
+        <v>352</v>
+      </c>
+      <c r="C312" t="s">
+        <v>37</v>
       </c>
       <c r="D312" t="s">
         <v>11</v>
       </c>
-      <c r="E312" t="s">
-        <v>355</v>
-      </c>
       <c r="F312" t="s">
-        <v>38</v>
+        <v>353</v>
       </c>
     </row>
     <row r="313" spans="1:6">
       <c r="A313" t="s">
-        <v>35</v>
+        <v>354</v>
       </c>
       <c r="B313" t="s">
+        <v>355</v>
+      </c>
+      <c r="C313" t="s">
         <v>356</v>
       </c>
-      <c r="C313" t="s">
-        <v>37</v>
-      </c>
       <c r="D313" t="s">
         <v>11</v>
       </c>
       <c r="F313" t="s">
-        <v>357</v>
+        <v>42</v>
       </c>
     </row>
     <row r="314" spans="1:6">
       <c r="A314" t="s">
+        <v>357</v>
+      </c>
+      <c r="B314" t="s">
         <v>358</v>
       </c>
-      <c r="B314" t="s">
+      <c r="C314" t="s">
         <v>359</v>
-      </c>
-      <c r="C314" t="s">
-        <v>360</v>
       </c>
       <c r="D314" t="s">
         <v>11</v>
@@ -7347,69 +7335,69 @@
     </row>
     <row r="315" spans="1:6">
       <c r="A315" t="s">
-        <v>361</v>
-      </c>
-      <c r="B315" t="s">
-        <v>362</v>
-      </c>
-      <c r="C315" t="s">
-        <v>363</v>
-      </c>
-      <c r="D315" t="s">
-        <v>11</v>
-      </c>
-      <c r="F315" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="316" spans="1:6">
       <c r="A316" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B316" t="s">
+        <v>360</v>
+      </c>
+      <c r="D316" t="s">
+        <v>11</v>
+      </c>
+      <c r="E316" t="s">
+        <v>361</v>
+      </c>
+      <c r="F316" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="317" spans="1:6">
       <c r="A317" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B317" t="s">
-        <v>364</v>
+        <v>362</v>
+      </c>
+      <c r="C317" t="s">
+        <v>57</v>
       </c>
       <c r="D317" t="s">
         <v>11</v>
       </c>
-      <c r="E317" t="s">
-        <v>365</v>
-      </c>
       <c r="F317" t="s">
-        <v>38</v>
+        <v>353</v>
       </c>
     </row>
     <row r="318" spans="1:6">
       <c r="A318" t="s">
-        <v>35</v>
+        <v>354</v>
       </c>
       <c r="B318" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C318" t="s">
-        <v>57</v>
+        <v>356</v>
       </c>
       <c r="D318" t="s">
         <v>11</v>
       </c>
       <c r="F318" t="s">
-        <v>357</v>
+        <v>42</v>
       </c>
     </row>
     <row r="319" spans="1:6">
       <c r="A319" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B319" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C319" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D319" t="s">
         <v>11</v>
@@ -7420,72 +7408,72 @@
     </row>
     <row r="320" spans="1:6">
       <c r="A320" t="s">
-        <v>361</v>
-      </c>
-      <c r="B320" t="s">
-        <v>368</v>
-      </c>
-      <c r="C320" t="s">
-        <v>363</v>
-      </c>
-      <c r="D320" t="s">
-        <v>11</v>
-      </c>
-      <c r="F320" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="321" spans="1:6">
       <c r="A321" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B321" t="s">
+        <v>365</v>
+      </c>
+      <c r="C321" t="s">
+        <v>366</v>
+      </c>
+      <c r="D321" t="s">
+        <v>11</v>
+      </c>
+      <c r="E321" t="s">
+        <v>367</v>
+      </c>
+      <c r="F321" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="322" spans="1:6">
       <c r="A322" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B322" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C322" t="s">
-        <v>370</v>
+        <v>65</v>
       </c>
       <c r="D322" t="s">
         <v>11</v>
       </c>
-      <c r="E322" t="s">
-        <v>371</v>
-      </c>
       <c r="F322" t="s">
-        <v>38</v>
+        <v>353</v>
       </c>
     </row>
     <row r="323" spans="1:6">
       <c r="A323" t="s">
-        <v>35</v>
+        <v>354</v>
       </c>
       <c r="B323" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C323" t="s">
-        <v>65</v>
+        <v>356</v>
       </c>
       <c r="D323" t="s">
         <v>11</v>
       </c>
       <c r="F323" t="s">
-        <v>357</v>
+        <v>42</v>
       </c>
     </row>
     <row r="324" spans="1:6">
       <c r="A324" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B324" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C324" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="D324" t="s">
         <v>11</v>
@@ -7496,72 +7484,72 @@
     </row>
     <row r="325" spans="1:6">
       <c r="A325" t="s">
-        <v>361</v>
-      </c>
-      <c r="B325" t="s">
-        <v>374</v>
-      </c>
-      <c r="C325" t="s">
-        <v>375</v>
-      </c>
-      <c r="D325" t="s">
-        <v>11</v>
-      </c>
-      <c r="F325" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="326" spans="1:6">
       <c r="A326" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B326" t="s">
+        <v>372</v>
+      </c>
+      <c r="C326" t="s">
+        <v>366</v>
+      </c>
+      <c r="D326" t="s">
+        <v>11</v>
+      </c>
+      <c r="E326" t="s">
+        <v>373</v>
+      </c>
+      <c r="F326" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="327" spans="1:6">
       <c r="A327" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B327" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C327" t="s">
-        <v>370</v>
+        <v>73</v>
       </c>
       <c r="D327" t="s">
         <v>11</v>
       </c>
-      <c r="E327" t="s">
-        <v>377</v>
-      </c>
       <c r="F327" t="s">
-        <v>38</v>
+        <v>353</v>
       </c>
     </row>
     <row r="328" spans="1:6">
       <c r="A328" t="s">
-        <v>35</v>
+        <v>354</v>
       </c>
       <c r="B328" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C328" t="s">
-        <v>73</v>
+        <v>356</v>
       </c>
       <c r="D328" t="s">
         <v>11</v>
       </c>
       <c r="F328" t="s">
-        <v>357</v>
+        <v>42</v>
       </c>
     </row>
     <row r="329" spans="1:6">
       <c r="A329" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B329" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C329" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D329" t="s">
         <v>11</v>
@@ -7572,72 +7560,72 @@
     </row>
     <row r="330" spans="1:6">
       <c r="A330" t="s">
-        <v>361</v>
-      </c>
-      <c r="B330" t="s">
-        <v>380</v>
-      </c>
-      <c r="C330" t="s">
-        <v>363</v>
-      </c>
-      <c r="D330" t="s">
-        <v>11</v>
-      </c>
-      <c r="F330" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="331" spans="1:6">
       <c r="A331" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B331" t="s">
+        <v>377</v>
+      </c>
+      <c r="C331" t="s">
+        <v>366</v>
+      </c>
+      <c r="D331" t="s">
+        <v>11</v>
+      </c>
+      <c r="E331" t="s">
+        <v>378</v>
+      </c>
+      <c r="F331" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="332" spans="1:6">
       <c r="A332" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B332" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C332" t="s">
-        <v>370</v>
+        <v>84</v>
       </c>
       <c r="D332" t="s">
         <v>11</v>
       </c>
-      <c r="E332" t="s">
-        <v>382</v>
-      </c>
       <c r="F332" t="s">
-        <v>38</v>
+        <v>353</v>
       </c>
     </row>
     <row r="333" spans="1:6">
       <c r="A333" t="s">
-        <v>35</v>
+        <v>354</v>
       </c>
       <c r="B333" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C333" t="s">
-        <v>84</v>
+        <v>356</v>
       </c>
       <c r="D333" t="s">
         <v>11</v>
       </c>
       <c r="F333" t="s">
-        <v>357</v>
+        <v>42</v>
       </c>
     </row>
     <row r="334" spans="1:6">
       <c r="A334" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B334" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C334" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D334" t="s">
         <v>11</v>
@@ -7648,72 +7636,72 @@
     </row>
     <row r="335" spans="1:6">
       <c r="A335" t="s">
-        <v>361</v>
-      </c>
-      <c r="B335" t="s">
-        <v>385</v>
-      </c>
-      <c r="C335" t="s">
-        <v>363</v>
-      </c>
-      <c r="D335" t="s">
-        <v>11</v>
-      </c>
-      <c r="F335" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="336" spans="1:6">
       <c r="A336" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B336" t="s">
+        <v>382</v>
+      </c>
+      <c r="C336" t="s">
+        <v>366</v>
+      </c>
+      <c r="D336" t="s">
+        <v>11</v>
+      </c>
+      <c r="E336" t="s">
+        <v>383</v>
+      </c>
+      <c r="F336" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="337" spans="1:6">
       <c r="A337" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B337" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C337" t="s">
-        <v>370</v>
+        <v>92</v>
       </c>
       <c r="D337" t="s">
         <v>11</v>
       </c>
-      <c r="E337" t="s">
-        <v>387</v>
-      </c>
       <c r="F337" t="s">
-        <v>38</v>
+        <v>353</v>
       </c>
     </row>
     <row r="338" spans="1:6">
       <c r="A338" t="s">
-        <v>35</v>
+        <v>354</v>
       </c>
       <c r="B338" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C338" t="s">
-        <v>92</v>
+        <v>356</v>
       </c>
       <c r="D338" t="s">
         <v>11</v>
       </c>
       <c r="F338" t="s">
-        <v>357</v>
+        <v>42</v>
       </c>
     </row>
     <row r="339" spans="1:6">
       <c r="A339" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B339" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C339" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D339" t="s">
         <v>11</v>
@@ -7724,72 +7712,72 @@
     </row>
     <row r="340" spans="1:6">
       <c r="A340" t="s">
-        <v>361</v>
-      </c>
-      <c r="B340" t="s">
-        <v>390</v>
-      </c>
-      <c r="C340" t="s">
-        <v>363</v>
-      </c>
-      <c r="D340" t="s">
-        <v>11</v>
-      </c>
-      <c r="F340" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="341" spans="1:6">
       <c r="A341" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B341" t="s">
+        <v>387</v>
+      </c>
+      <c r="C341" t="s">
+        <v>366</v>
+      </c>
+      <c r="D341" t="s">
+        <v>11</v>
+      </c>
+      <c r="E341" t="s">
+        <v>388</v>
+      </c>
+      <c r="F341" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="342" spans="1:6">
       <c r="A342" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B342" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C342" t="s">
-        <v>370</v>
+        <v>100</v>
       </c>
       <c r="D342" t="s">
         <v>11</v>
       </c>
-      <c r="E342" t="s">
-        <v>392</v>
-      </c>
       <c r="F342" t="s">
-        <v>38</v>
+        <v>353</v>
       </c>
     </row>
     <row r="343" spans="1:6">
       <c r="A343" t="s">
-        <v>35</v>
+        <v>354</v>
       </c>
       <c r="B343" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C343" t="s">
-        <v>100</v>
+        <v>356</v>
       </c>
       <c r="D343" t="s">
         <v>11</v>
       </c>
       <c r="F343" t="s">
-        <v>357</v>
+        <v>42</v>
       </c>
     </row>
     <row r="344" spans="1:6">
       <c r="A344" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B344" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C344" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D344" t="s">
         <v>11</v>
@@ -7800,72 +7788,72 @@
     </row>
     <row r="345" spans="1:6">
       <c r="A345" t="s">
-        <v>361</v>
-      </c>
-      <c r="B345" t="s">
-        <v>395</v>
-      </c>
-      <c r="C345" t="s">
-        <v>363</v>
-      </c>
-      <c r="D345" t="s">
-        <v>11</v>
-      </c>
-      <c r="F345" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="346" spans="1:6">
       <c r="A346" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B346" t="s">
+        <v>392</v>
+      </c>
+      <c r="C346" t="s">
+        <v>366</v>
+      </c>
+      <c r="D346" t="s">
+        <v>11</v>
+      </c>
+      <c r="E346" t="s">
+        <v>393</v>
+      </c>
+      <c r="F346" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="347" spans="1:6">
       <c r="A347" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B347" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C347" t="s">
-        <v>370</v>
+        <v>288</v>
       </c>
       <c r="D347" t="s">
         <v>11</v>
       </c>
-      <c r="E347" t="s">
-        <v>397</v>
-      </c>
       <c r="F347" t="s">
-        <v>38</v>
+        <v>353</v>
       </c>
     </row>
     <row r="348" spans="1:6">
       <c r="A348" t="s">
-        <v>35</v>
+        <v>354</v>
       </c>
       <c r="B348" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C348" t="s">
-        <v>288</v>
+        <v>356</v>
       </c>
       <c r="D348" t="s">
         <v>11</v>
       </c>
       <c r="F348" t="s">
-        <v>357</v>
+        <v>42</v>
       </c>
     </row>
     <row r="349" spans="1:6">
       <c r="A349" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B349" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C349" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D349" t="s">
         <v>11</v>
@@ -7876,72 +7864,72 @@
     </row>
     <row r="350" spans="1:6">
       <c r="A350" t="s">
-        <v>361</v>
-      </c>
-      <c r="B350" t="s">
-        <v>400</v>
-      </c>
-      <c r="C350" t="s">
-        <v>363</v>
-      </c>
-      <c r="D350" t="s">
-        <v>11</v>
-      </c>
-      <c r="F350" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="351" spans="1:6">
       <c r="A351" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B351" t="s">
+        <v>397</v>
+      </c>
+      <c r="C351" t="s">
+        <v>366</v>
+      </c>
+      <c r="D351" t="s">
+        <v>11</v>
+      </c>
+      <c r="E351" t="s">
+        <v>398</v>
+      </c>
+      <c r="F351" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="352" spans="1:6">
       <c r="A352" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B352" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C352" t="s">
-        <v>370</v>
+        <v>296</v>
       </c>
       <c r="D352" t="s">
         <v>11</v>
       </c>
-      <c r="E352" t="s">
-        <v>402</v>
-      </c>
       <c r="F352" t="s">
-        <v>38</v>
+        <v>353</v>
       </c>
     </row>
     <row r="353" spans="1:6">
       <c r="A353" t="s">
-        <v>35</v>
+        <v>354</v>
       </c>
       <c r="B353" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C353" t="s">
-        <v>296</v>
+        <v>356</v>
       </c>
       <c r="D353" t="s">
         <v>11</v>
       </c>
       <c r="F353" t="s">
-        <v>357</v>
+        <v>42</v>
       </c>
     </row>
     <row r="354" spans="1:6">
       <c r="A354" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B354" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C354" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D354" t="s">
         <v>11</v>
@@ -7952,72 +7940,72 @@
     </row>
     <row r="355" spans="1:6">
       <c r="A355" t="s">
-        <v>361</v>
-      </c>
-      <c r="B355" t="s">
-        <v>405</v>
-      </c>
-      <c r="C355" t="s">
-        <v>363</v>
-      </c>
-      <c r="D355" t="s">
-        <v>11</v>
-      </c>
-      <c r="F355" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="356" spans="1:6">
       <c r="A356" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B356" t="s">
+        <v>402</v>
+      </c>
+      <c r="C356" t="s">
+        <v>366</v>
+      </c>
+      <c r="D356" t="s">
+        <v>11</v>
+      </c>
+      <c r="E356" t="s">
+        <v>403</v>
+      </c>
+      <c r="F356" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="357" spans="1:6">
       <c r="A357" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B357" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C357" t="s">
-        <v>370</v>
+        <v>304</v>
       </c>
       <c r="D357" t="s">
         <v>11</v>
       </c>
-      <c r="E357" t="s">
-        <v>407</v>
-      </c>
       <c r="F357" t="s">
-        <v>38</v>
+        <v>353</v>
       </c>
     </row>
     <row r="358" spans="1:6">
       <c r="A358" t="s">
-        <v>35</v>
+        <v>354</v>
       </c>
       <c r="B358" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C358" t="s">
-        <v>304</v>
+        <v>356</v>
       </c>
       <c r="D358" t="s">
         <v>11</v>
       </c>
       <c r="F358" t="s">
-        <v>357</v>
+        <v>42</v>
       </c>
     </row>
     <row r="359" spans="1:6">
       <c r="A359" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C359" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D359" t="s">
         <v>11</v>
@@ -8028,72 +8016,72 @@
     </row>
     <row r="360" spans="1:6">
       <c r="A360" t="s">
-        <v>361</v>
-      </c>
-      <c r="B360" t="s">
-        <v>410</v>
-      </c>
-      <c r="C360" t="s">
-        <v>363</v>
-      </c>
-      <c r="D360" t="s">
-        <v>11</v>
-      </c>
-      <c r="F360" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="361" spans="1:6">
       <c r="A361" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B361" t="s">
+        <v>407</v>
+      </c>
+      <c r="C361" t="s">
+        <v>366</v>
+      </c>
+      <c r="D361" t="s">
+        <v>11</v>
+      </c>
+      <c r="E361" t="s">
+        <v>408</v>
+      </c>
+      <c r="F361" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="362" spans="1:6">
       <c r="A362" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B362" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C362" t="s">
-        <v>370</v>
+        <v>312</v>
       </c>
       <c r="D362" t="s">
         <v>11</v>
       </c>
-      <c r="E362" t="s">
-        <v>412</v>
-      </c>
       <c r="F362" t="s">
-        <v>38</v>
+        <v>353</v>
       </c>
     </row>
     <row r="363" spans="1:6">
       <c r="A363" t="s">
-        <v>35</v>
+        <v>354</v>
       </c>
       <c r="B363" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C363" t="s">
-        <v>312</v>
+        <v>356</v>
       </c>
       <c r="D363" t="s">
         <v>11</v>
       </c>
       <c r="F363" t="s">
-        <v>357</v>
+        <v>42</v>
       </c>
     </row>
     <row r="364" spans="1:6">
       <c r="A364" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B364" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C364" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D364" t="s">
         <v>11</v>
@@ -8104,72 +8092,72 @@
     </row>
     <row r="365" spans="1:6">
       <c r="A365" t="s">
-        <v>361</v>
-      </c>
-      <c r="B365" t="s">
-        <v>415</v>
-      </c>
-      <c r="C365" t="s">
-        <v>363</v>
-      </c>
-      <c r="D365" t="s">
-        <v>11</v>
-      </c>
-      <c r="F365" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="366" spans="1:6">
       <c r="A366" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B366" t="s">
+        <v>412</v>
+      </c>
+      <c r="C366" t="s">
+        <v>366</v>
+      </c>
+      <c r="D366" t="s">
+        <v>11</v>
+      </c>
+      <c r="E366" t="s">
+        <v>413</v>
+      </c>
+      <c r="F366" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="367" spans="1:6">
       <c r="A367" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B367" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C367" t="s">
-        <v>370</v>
+        <v>320</v>
       </c>
       <c r="D367" t="s">
         <v>11</v>
       </c>
-      <c r="E367" t="s">
-        <v>417</v>
-      </c>
       <c r="F367" t="s">
-        <v>38</v>
+        <v>353</v>
       </c>
     </row>
     <row r="368" spans="1:6">
       <c r="A368" t="s">
-        <v>35</v>
+        <v>354</v>
       </c>
       <c r="B368" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C368" t="s">
-        <v>320</v>
+        <v>356</v>
       </c>
       <c r="D368" t="s">
         <v>11</v>
       </c>
       <c r="F368" t="s">
-        <v>357</v>
+        <v>42</v>
       </c>
     </row>
     <row r="369" spans="1:6">
       <c r="A369" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B369" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C369" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D369" t="s">
         <v>11</v>
@@ -8180,72 +8168,72 @@
     </row>
     <row r="370" spans="1:6">
       <c r="A370" t="s">
-        <v>361</v>
-      </c>
-      <c r="B370" t="s">
-        <v>420</v>
-      </c>
-      <c r="C370" t="s">
-        <v>363</v>
-      </c>
-      <c r="D370" t="s">
-        <v>11</v>
-      </c>
-      <c r="F370" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="371" spans="1:6">
       <c r="A371" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B371" t="s">
+        <v>417</v>
+      </c>
+      <c r="C371" t="s">
+        <v>366</v>
+      </c>
+      <c r="D371" t="s">
+        <v>11</v>
+      </c>
+      <c r="E371" t="s">
+        <v>418</v>
+      </c>
+      <c r="F371" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="372" spans="1:6">
       <c r="A372" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B372" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C372" t="s">
-        <v>370</v>
+        <v>328</v>
       </c>
       <c r="D372" t="s">
         <v>11</v>
       </c>
-      <c r="E372" t="s">
-        <v>422</v>
-      </c>
       <c r="F372" t="s">
-        <v>38</v>
+        <v>353</v>
       </c>
     </row>
     <row r="373" spans="1:6">
       <c r="A373" t="s">
-        <v>35</v>
+        <v>354</v>
       </c>
       <c r="B373" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C373" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="D373" t="s">
         <v>11</v>
       </c>
       <c r="F373" t="s">
-        <v>357</v>
+        <v>42</v>
       </c>
     </row>
     <row r="374" spans="1:6">
       <c r="A374" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B374" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C374" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D374" t="s">
         <v>11</v>
@@ -8256,72 +8244,72 @@
     </row>
     <row r="375" spans="1:6">
       <c r="A375" t="s">
-        <v>361</v>
-      </c>
-      <c r="B375" t="s">
-        <v>425</v>
-      </c>
-      <c r="C375" t="s">
-        <v>363</v>
-      </c>
-      <c r="D375" t="s">
-        <v>11</v>
-      </c>
-      <c r="F375" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="376" spans="1:6">
       <c r="A376" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B376" t="s">
+        <v>422</v>
+      </c>
+      <c r="C376" t="s">
+        <v>366</v>
+      </c>
+      <c r="D376" t="s">
+        <v>11</v>
+      </c>
+      <c r="E376" t="s">
+        <v>423</v>
+      </c>
+      <c r="F376" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="377" spans="1:6">
       <c r="A377" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B377" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C377" t="s">
-        <v>370</v>
+        <v>336</v>
       </c>
       <c r="D377" t="s">
         <v>11</v>
       </c>
-      <c r="E377" t="s">
-        <v>427</v>
-      </c>
       <c r="F377" t="s">
-        <v>38</v>
+        <v>353</v>
       </c>
     </row>
     <row r="378" spans="1:6">
       <c r="A378" t="s">
-        <v>35</v>
+        <v>354</v>
       </c>
       <c r="B378" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C378" t="s">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="D378" t="s">
         <v>11</v>
       </c>
       <c r="F378" t="s">
-        <v>357</v>
+        <v>42</v>
       </c>
     </row>
     <row r="379" spans="1:6">
       <c r="A379" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B379" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C379" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D379" t="s">
         <v>11</v>
@@ -8332,72 +8320,72 @@
     </row>
     <row r="380" spans="1:6">
       <c r="A380" t="s">
-        <v>361</v>
-      </c>
-      <c r="B380" t="s">
-        <v>430</v>
-      </c>
-      <c r="C380" t="s">
-        <v>363</v>
-      </c>
-      <c r="D380" t="s">
-        <v>11</v>
-      </c>
-      <c r="F380" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="381" spans="1:6">
       <c r="A381" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B381" t="s">
+        <v>427</v>
+      </c>
+      <c r="C381" t="s">
+        <v>366</v>
+      </c>
+      <c r="D381" t="s">
+        <v>11</v>
+      </c>
+      <c r="E381" t="s">
+        <v>428</v>
+      </c>
+      <c r="F381" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="382" spans="1:6">
       <c r="A382" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B382" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C382" t="s">
-        <v>370</v>
+        <v>111</v>
       </c>
       <c r="D382" t="s">
         <v>11</v>
       </c>
-      <c r="E382" t="s">
-        <v>432</v>
-      </c>
       <c r="F382" t="s">
-        <v>38</v>
+        <v>353</v>
       </c>
     </row>
     <row r="383" spans="1:6">
       <c r="A383" t="s">
-        <v>35</v>
+        <v>354</v>
       </c>
       <c r="B383" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C383" t="s">
-        <v>111</v>
+        <v>356</v>
       </c>
       <c r="D383" t="s">
         <v>11</v>
       </c>
       <c r="F383" t="s">
-        <v>357</v>
+        <v>42</v>
       </c>
     </row>
     <row r="384" spans="1:6">
       <c r="A384" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B384" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C384" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D384" t="s">
         <v>11</v>
@@ -8408,72 +8396,72 @@
     </row>
     <row r="385" spans="1:6">
       <c r="A385" t="s">
-        <v>361</v>
-      </c>
-      <c r="B385" t="s">
-        <v>435</v>
-      </c>
-      <c r="C385" t="s">
-        <v>363</v>
-      </c>
-      <c r="D385" t="s">
-        <v>11</v>
-      </c>
-      <c r="F385" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="386" spans="1:6">
       <c r="A386" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B386" t="s">
+        <v>432</v>
+      </c>
+      <c r="C386" t="s">
+        <v>366</v>
+      </c>
+      <c r="D386" t="s">
+        <v>11</v>
+      </c>
+      <c r="E386" t="s">
+        <v>433</v>
+      </c>
+      <c r="F386" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="387" spans="1:6">
       <c r="A387" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B387" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C387" t="s">
-        <v>370</v>
+        <v>119</v>
       </c>
       <c r="D387" t="s">
         <v>11</v>
       </c>
-      <c r="E387" t="s">
-        <v>437</v>
-      </c>
       <c r="F387" t="s">
-        <v>38</v>
+        <v>353</v>
       </c>
     </row>
     <row r="388" spans="1:6">
       <c r="A388" t="s">
-        <v>35</v>
+        <v>354</v>
       </c>
       <c r="B388" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C388" t="s">
-        <v>119</v>
+        <v>356</v>
       </c>
       <c r="D388" t="s">
         <v>11</v>
       </c>
       <c r="F388" t="s">
-        <v>357</v>
+        <v>42</v>
       </c>
     </row>
     <row r="389" spans="1:6">
       <c r="A389" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B389" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C389" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D389" t="s">
         <v>11</v>
@@ -8484,72 +8472,72 @@
     </row>
     <row r="390" spans="1:6">
       <c r="A390" t="s">
-        <v>361</v>
-      </c>
-      <c r="B390" t="s">
-        <v>440</v>
-      </c>
-      <c r="C390" t="s">
-        <v>363</v>
-      </c>
-      <c r="D390" t="s">
-        <v>11</v>
-      </c>
-      <c r="F390" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="391" spans="1:6">
       <c r="A391" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B391" t="s">
+        <v>437</v>
+      </c>
+      <c r="C391" t="s">
+        <v>366</v>
+      </c>
+      <c r="D391" t="s">
+        <v>11</v>
+      </c>
+      <c r="E391" t="s">
+        <v>438</v>
+      </c>
+      <c r="F391" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="392" spans="1:6">
       <c r="A392" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B392" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C392" t="s">
-        <v>370</v>
+        <v>127</v>
       </c>
       <c r="D392" t="s">
         <v>11</v>
       </c>
-      <c r="E392" t="s">
-        <v>442</v>
-      </c>
       <c r="F392" t="s">
-        <v>38</v>
+        <v>353</v>
       </c>
     </row>
     <row r="393" spans="1:6">
       <c r="A393" t="s">
-        <v>35</v>
+        <v>354</v>
       </c>
       <c r="B393" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C393" t="s">
-        <v>127</v>
+        <v>356</v>
       </c>
       <c r="D393" t="s">
         <v>11</v>
       </c>
       <c r="F393" t="s">
-        <v>357</v>
+        <v>42</v>
       </c>
     </row>
     <row r="394" spans="1:6">
       <c r="A394" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B394" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C394" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D394" t="s">
         <v>11</v>
@@ -8560,72 +8548,72 @@
     </row>
     <row r="395" spans="1:6">
       <c r="A395" t="s">
-        <v>361</v>
-      </c>
-      <c r="B395" t="s">
-        <v>445</v>
-      </c>
-      <c r="C395" t="s">
-        <v>363</v>
-      </c>
-      <c r="D395" t="s">
-        <v>11</v>
-      </c>
-      <c r="F395" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="396" spans="1:6">
       <c r="A396" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B396" t="s">
+        <v>442</v>
+      </c>
+      <c r="C396" t="s">
+        <v>366</v>
+      </c>
+      <c r="D396" t="s">
+        <v>11</v>
+      </c>
+      <c r="E396" t="s">
+        <v>443</v>
+      </c>
+      <c r="F396" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="397" spans="1:6">
       <c r="A397" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B397" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C397" t="s">
-        <v>370</v>
+        <v>135</v>
       </c>
       <c r="D397" t="s">
         <v>11</v>
       </c>
-      <c r="E397" t="s">
-        <v>447</v>
-      </c>
       <c r="F397" t="s">
-        <v>38</v>
+        <v>353</v>
       </c>
     </row>
     <row r="398" spans="1:6">
       <c r="A398" t="s">
-        <v>35</v>
+        <v>354</v>
       </c>
       <c r="B398" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C398" t="s">
-        <v>135</v>
+        <v>356</v>
       </c>
       <c r="D398" t="s">
         <v>11</v>
       </c>
       <c r="F398" t="s">
-        <v>357</v>
+        <v>42</v>
       </c>
     </row>
     <row r="399" spans="1:6">
       <c r="A399" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B399" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C399" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D399" t="s">
         <v>11</v>
@@ -8636,72 +8624,72 @@
     </row>
     <row r="400" spans="1:6">
       <c r="A400" t="s">
-        <v>361</v>
-      </c>
-      <c r="B400" t="s">
-        <v>450</v>
-      </c>
-      <c r="C400" t="s">
-        <v>363</v>
-      </c>
-      <c r="D400" t="s">
-        <v>11</v>
-      </c>
-      <c r="F400" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="401" spans="1:6">
       <c r="A401" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B401" t="s">
+        <v>447</v>
+      </c>
+      <c r="C401" t="s">
+        <v>366</v>
+      </c>
+      <c r="D401" t="s">
+        <v>11</v>
+      </c>
+      <c r="E401" t="s">
+        <v>448</v>
+      </c>
+      <c r="F401" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="402" spans="1:6">
       <c r="A402" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B402" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C402" t="s">
-        <v>370</v>
+        <v>143</v>
       </c>
       <c r="D402" t="s">
         <v>11</v>
       </c>
-      <c r="E402" t="s">
-        <v>452</v>
-      </c>
       <c r="F402" t="s">
-        <v>38</v>
+        <v>353</v>
       </c>
     </row>
     <row r="403" spans="1:6">
       <c r="A403" t="s">
-        <v>35</v>
+        <v>354</v>
       </c>
       <c r="B403" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C403" t="s">
-        <v>143</v>
+        <v>356</v>
       </c>
       <c r="D403" t="s">
         <v>11</v>
       </c>
       <c r="F403" t="s">
-        <v>357</v>
+        <v>42</v>
       </c>
     </row>
     <row r="404" spans="1:6">
       <c r="A404" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B404" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C404" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D404" t="s">
         <v>11</v>
@@ -8712,72 +8700,72 @@
     </row>
     <row r="405" spans="1:6">
       <c r="A405" t="s">
-        <v>361</v>
-      </c>
-      <c r="B405" t="s">
-        <v>455</v>
-      </c>
-      <c r="C405" t="s">
-        <v>363</v>
-      </c>
-      <c r="D405" t="s">
-        <v>11</v>
-      </c>
-      <c r="F405" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="406" spans="1:6">
       <c r="A406" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B406" t="s">
+        <v>452</v>
+      </c>
+      <c r="C406" t="s">
+        <v>366</v>
+      </c>
+      <c r="D406" t="s">
+        <v>11</v>
+      </c>
+      <c r="E406" t="s">
+        <v>453</v>
+      </c>
+      <c r="F406" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="407" spans="1:6">
       <c r="A407" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B407" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C407" t="s">
-        <v>370</v>
+        <v>151</v>
       </c>
       <c r="D407" t="s">
         <v>11</v>
       </c>
-      <c r="E407" t="s">
-        <v>457</v>
-      </c>
       <c r="F407" t="s">
-        <v>38</v>
+        <v>353</v>
       </c>
     </row>
     <row r="408" spans="1:6">
       <c r="A408" t="s">
-        <v>35</v>
+        <v>354</v>
       </c>
       <c r="B408" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C408" t="s">
-        <v>151</v>
+        <v>356</v>
       </c>
       <c r="D408" t="s">
         <v>11</v>
       </c>
       <c r="F408" t="s">
-        <v>357</v>
+        <v>42</v>
       </c>
     </row>
     <row r="409" spans="1:6">
       <c r="A409" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B409" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C409" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D409" t="s">
         <v>11</v>
@@ -8788,72 +8776,72 @@
     </row>
     <row r="410" spans="1:6">
       <c r="A410" t="s">
-        <v>361</v>
-      </c>
-      <c r="B410" t="s">
-        <v>460</v>
-      </c>
-      <c r="C410" t="s">
-        <v>363</v>
-      </c>
-      <c r="D410" t="s">
-        <v>11</v>
-      </c>
-      <c r="F410" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="411" spans="1:6">
       <c r="A411" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B411" t="s">
+        <v>457</v>
+      </c>
+      <c r="C411" t="s">
+        <v>366</v>
+      </c>
+      <c r="D411" t="s">
+        <v>11</v>
+      </c>
+      <c r="E411" t="s">
+        <v>458</v>
+      </c>
+      <c r="F411" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="412" spans="1:6">
       <c r="A412" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B412" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C412" t="s">
-        <v>370</v>
+        <v>460</v>
       </c>
       <c r="D412" t="s">
         <v>11</v>
       </c>
-      <c r="E412" t="s">
-        <v>462</v>
-      </c>
       <c r="F412" t="s">
-        <v>38</v>
+        <v>353</v>
       </c>
     </row>
     <row r="413" spans="1:6">
       <c r="A413" t="s">
-        <v>35</v>
+        <v>354</v>
       </c>
       <c r="B413" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C413" t="s">
-        <v>464</v>
+        <v>356</v>
       </c>
       <c r="D413" t="s">
         <v>11</v>
       </c>
       <c r="F413" t="s">
-        <v>357</v>
+        <v>42</v>
       </c>
     </row>
     <row r="414" spans="1:6">
       <c r="A414" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B414" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C414" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D414" t="s">
         <v>11</v>
@@ -8864,72 +8852,72 @@
     </row>
     <row r="415" spans="1:6">
       <c r="A415" t="s">
-        <v>361</v>
-      </c>
-      <c r="B415" t="s">
-        <v>466</v>
-      </c>
-      <c r="C415" t="s">
-        <v>363</v>
-      </c>
-      <c r="D415" t="s">
-        <v>11</v>
-      </c>
-      <c r="F415" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="416" spans="1:6">
       <c r="A416" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B416" t="s">
+        <v>463</v>
+      </c>
+      <c r="C416" t="s">
+        <v>366</v>
+      </c>
+      <c r="D416" t="s">
+        <v>11</v>
+      </c>
+      <c r="E416" t="s">
+        <v>464</v>
+      </c>
+      <c r="F416" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="417" spans="1:6">
       <c r="A417" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B417" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C417" t="s">
-        <v>370</v>
+        <v>466</v>
       </c>
       <c r="D417" t="s">
         <v>11</v>
       </c>
-      <c r="E417" t="s">
-        <v>468</v>
-      </c>
       <c r="F417" t="s">
-        <v>38</v>
+        <v>353</v>
       </c>
     </row>
     <row r="418" spans="1:6">
       <c r="A418" t="s">
-        <v>35</v>
+        <v>354</v>
       </c>
       <c r="B418" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C418" t="s">
-        <v>470</v>
+        <v>356</v>
       </c>
       <c r="D418" t="s">
         <v>11</v>
       </c>
       <c r="F418" t="s">
-        <v>357</v>
+        <v>42</v>
       </c>
     </row>
     <row r="419" spans="1:6">
       <c r="A419" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B419" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C419" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D419" t="s">
         <v>11</v>
@@ -8940,72 +8928,72 @@
     </row>
     <row r="420" spans="1:6">
       <c r="A420" t="s">
-        <v>361</v>
-      </c>
-      <c r="B420" t="s">
-        <v>472</v>
-      </c>
-      <c r="C420" t="s">
-        <v>363</v>
-      </c>
-      <c r="D420" t="s">
-        <v>11</v>
-      </c>
-      <c r="F420" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="421" spans="1:6">
       <c r="A421" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B421" t="s">
+        <v>469</v>
+      </c>
+      <c r="C421" t="s">
+        <v>366</v>
+      </c>
+      <c r="D421" t="s">
+        <v>11</v>
+      </c>
+      <c r="E421" t="s">
+        <v>470</v>
+      </c>
+      <c r="F421" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="422" spans="1:6">
       <c r="A422" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B422" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C422" t="s">
-        <v>370</v>
+        <v>472</v>
       </c>
       <c r="D422" t="s">
         <v>11</v>
       </c>
-      <c r="E422" t="s">
-        <v>474</v>
-      </c>
       <c r="F422" t="s">
-        <v>38</v>
+        <v>353</v>
       </c>
     </row>
     <row r="423" spans="1:6">
       <c r="A423" t="s">
-        <v>35</v>
+        <v>354</v>
       </c>
       <c r="B423" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C423" t="s">
-        <v>476</v>
+        <v>356</v>
       </c>
       <c r="D423" t="s">
         <v>11</v>
       </c>
       <c r="F423" t="s">
-        <v>357</v>
+        <v>42</v>
       </c>
     </row>
     <row r="424" spans="1:6">
       <c r="A424" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B424" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C424" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D424" t="s">
         <v>11</v>
@@ -9016,72 +9004,72 @@
     </row>
     <row r="425" spans="1:6">
       <c r="A425" t="s">
-        <v>361</v>
-      </c>
-      <c r="B425" t="s">
-        <v>478</v>
-      </c>
-      <c r="C425" t="s">
-        <v>363</v>
-      </c>
-      <c r="D425" t="s">
-        <v>11</v>
-      </c>
-      <c r="F425" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="426" spans="1:6">
       <c r="A426" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B426" t="s">
+        <v>475</v>
+      </c>
+      <c r="C426" t="s">
+        <v>366</v>
+      </c>
+      <c r="D426" t="s">
+        <v>11</v>
+      </c>
+      <c r="E426" t="s">
+        <v>476</v>
+      </c>
+      <c r="F426" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="427" spans="1:6">
       <c r="A427" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B427" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C427" t="s">
-        <v>370</v>
+        <v>183</v>
       </c>
       <c r="D427" t="s">
         <v>11</v>
       </c>
-      <c r="E427" t="s">
-        <v>480</v>
-      </c>
       <c r="F427" t="s">
-        <v>38</v>
+        <v>353</v>
       </c>
     </row>
     <row r="428" spans="1:6">
       <c r="A428" t="s">
-        <v>35</v>
+        <v>354</v>
       </c>
       <c r="B428" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C428" t="s">
-        <v>183</v>
+        <v>356</v>
       </c>
       <c r="D428" t="s">
         <v>11</v>
       </c>
       <c r="F428" t="s">
-        <v>357</v>
+        <v>42</v>
       </c>
     </row>
     <row r="429" spans="1:6">
       <c r="A429" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B429" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C429" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D429" t="s">
         <v>11</v>
@@ -9092,72 +9080,72 @@
     </row>
     <row r="430" spans="1:6">
       <c r="A430" t="s">
-        <v>361</v>
-      </c>
-      <c r="B430" t="s">
-        <v>483</v>
-      </c>
-      <c r="C430" t="s">
-        <v>363</v>
-      </c>
-      <c r="D430" t="s">
-        <v>11</v>
-      </c>
-      <c r="F430" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="431" spans="1:6">
       <c r="A431" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B431" t="s">
+        <v>480</v>
+      </c>
+      <c r="C431" t="s">
+        <v>366</v>
+      </c>
+      <c r="D431" t="s">
+        <v>11</v>
+      </c>
+      <c r="E431" t="s">
+        <v>481</v>
+      </c>
+      <c r="F431" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="432" spans="1:6">
       <c r="A432" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B432" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C432" t="s">
-        <v>370</v>
+        <v>191</v>
       </c>
       <c r="D432" t="s">
         <v>11</v>
       </c>
-      <c r="E432" t="s">
-        <v>485</v>
-      </c>
       <c r="F432" t="s">
-        <v>38</v>
+        <v>353</v>
       </c>
     </row>
     <row r="433" spans="1:6">
       <c r="A433" t="s">
-        <v>35</v>
+        <v>354</v>
       </c>
       <c r="B433" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C433" t="s">
-        <v>191</v>
+        <v>356</v>
       </c>
       <c r="D433" t="s">
         <v>11</v>
       </c>
       <c r="F433" t="s">
-        <v>357</v>
+        <v>42</v>
       </c>
     </row>
     <row r="434" spans="1:6">
       <c r="A434" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B434" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C434" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D434" t="s">
         <v>11</v>
@@ -9168,72 +9156,72 @@
     </row>
     <row r="435" spans="1:6">
       <c r="A435" t="s">
-        <v>361</v>
-      </c>
-      <c r="B435" t="s">
-        <v>488</v>
-      </c>
-      <c r="C435" t="s">
-        <v>363</v>
-      </c>
-      <c r="D435" t="s">
-        <v>11</v>
-      </c>
-      <c r="F435" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="436" spans="1:6">
       <c r="A436" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B436" t="s">
+        <v>485</v>
+      </c>
+      <c r="C436" t="s">
+        <v>366</v>
+      </c>
+      <c r="D436" t="s">
+        <v>11</v>
+      </c>
+      <c r="E436" t="s">
+        <v>486</v>
+      </c>
+      <c r="F436" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="437" spans="1:6">
       <c r="A437" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B437" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C437" t="s">
-        <v>370</v>
+        <v>199</v>
       </c>
       <c r="D437" t="s">
         <v>11</v>
       </c>
-      <c r="E437" t="s">
-        <v>490</v>
-      </c>
       <c r="F437" t="s">
-        <v>38</v>
+        <v>353</v>
       </c>
     </row>
     <row r="438" spans="1:6">
       <c r="A438" t="s">
-        <v>35</v>
+        <v>354</v>
       </c>
       <c r="B438" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C438" t="s">
-        <v>199</v>
+        <v>356</v>
       </c>
       <c r="D438" t="s">
         <v>11</v>
       </c>
       <c r="F438" t="s">
-        <v>357</v>
+        <v>42</v>
       </c>
     </row>
     <row r="439" spans="1:6">
       <c r="A439" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B439" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C439" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D439" t="s">
         <v>11</v>
@@ -9244,72 +9232,72 @@
     </row>
     <row r="440" spans="1:6">
       <c r="A440" t="s">
-        <v>361</v>
-      </c>
-      <c r="B440" t="s">
-        <v>493</v>
-      </c>
-      <c r="C440" t="s">
-        <v>363</v>
-      </c>
-      <c r="D440" t="s">
-        <v>11</v>
-      </c>
-      <c r="F440" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="441" spans="1:6">
       <c r="A441" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B441" t="s">
+        <v>490</v>
+      </c>
+      <c r="C441" t="s">
+        <v>366</v>
+      </c>
+      <c r="D441" t="s">
+        <v>11</v>
+      </c>
+      <c r="E441" t="s">
+        <v>491</v>
+      </c>
+      <c r="F441" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="442" spans="1:6">
       <c r="A442" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B442" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C442" t="s">
-        <v>370</v>
+        <v>207</v>
       </c>
       <c r="D442" t="s">
         <v>11</v>
       </c>
-      <c r="E442" t="s">
-        <v>495</v>
-      </c>
       <c r="F442" t="s">
-        <v>38</v>
+        <v>353</v>
       </c>
     </row>
     <row r="443" spans="1:6">
       <c r="A443" t="s">
-        <v>35</v>
+        <v>354</v>
       </c>
       <c r="B443" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C443" t="s">
-        <v>207</v>
+        <v>356</v>
       </c>
       <c r="D443" t="s">
         <v>11</v>
       </c>
       <c r="F443" t="s">
-        <v>357</v>
+        <v>42</v>
       </c>
     </row>
     <row r="444" spans="1:6">
       <c r="A444" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B444" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C444" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D444" t="s">
         <v>11</v>
@@ -9320,72 +9308,72 @@
     </row>
     <row r="445" spans="1:6">
       <c r="A445" t="s">
-        <v>361</v>
-      </c>
-      <c r="B445" t="s">
-        <v>498</v>
-      </c>
-      <c r="C445" t="s">
-        <v>363</v>
-      </c>
-      <c r="D445" t="s">
-        <v>11</v>
-      </c>
-      <c r="F445" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="446" spans="1:6">
       <c r="A446" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B446" t="s">
+        <v>495</v>
+      </c>
+      <c r="C446" t="s">
+        <v>366</v>
+      </c>
+      <c r="D446" t="s">
+        <v>11</v>
+      </c>
+      <c r="E446" t="s">
+        <v>496</v>
+      </c>
+      <c r="F446" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="447" spans="1:6">
       <c r="A447" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B447" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C447" t="s">
-        <v>370</v>
+        <v>215</v>
       </c>
       <c r="D447" t="s">
         <v>11</v>
       </c>
-      <c r="E447" t="s">
-        <v>500</v>
-      </c>
       <c r="F447" t="s">
-        <v>38</v>
+        <v>353</v>
       </c>
     </row>
     <row r="448" spans="1:6">
       <c r="A448" t="s">
-        <v>35</v>
+        <v>354</v>
       </c>
       <c r="B448" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="C448" t="s">
-        <v>215</v>
+        <v>356</v>
       </c>
       <c r="D448" t="s">
         <v>11</v>
       </c>
       <c r="F448" t="s">
-        <v>357</v>
+        <v>42</v>
       </c>
     </row>
     <row r="449" spans="1:6">
       <c r="A449" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B449" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="C449" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D449" t="s">
         <v>11</v>
@@ -9396,72 +9384,72 @@
     </row>
     <row r="450" spans="1:6">
       <c r="A450" t="s">
-        <v>361</v>
-      </c>
-      <c r="B450" t="s">
-        <v>503</v>
-      </c>
-      <c r="C450" t="s">
-        <v>363</v>
-      </c>
-      <c r="D450" t="s">
-        <v>11</v>
-      </c>
-      <c r="F450" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="451" spans="1:6">
       <c r="A451" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B451" t="s">
+        <v>500</v>
+      </c>
+      <c r="C451" t="s">
+        <v>366</v>
+      </c>
+      <c r="D451" t="s">
+        <v>11</v>
+      </c>
+      <c r="E451" t="s">
+        <v>501</v>
+      </c>
+      <c r="F451" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="452" spans="1:6">
       <c r="A452" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B452" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C452" t="s">
-        <v>370</v>
+        <v>223</v>
       </c>
       <c r="D452" t="s">
         <v>11</v>
       </c>
-      <c r="E452" t="s">
-        <v>505</v>
-      </c>
       <c r="F452" t="s">
-        <v>38</v>
+        <v>353</v>
       </c>
     </row>
     <row r="453" spans="1:6">
       <c r="A453" t="s">
-        <v>35</v>
+        <v>354</v>
       </c>
       <c r="B453" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="C453" t="s">
-        <v>223</v>
+        <v>356</v>
       </c>
       <c r="D453" t="s">
         <v>11</v>
       </c>
       <c r="F453" t="s">
-        <v>357</v>
+        <v>42</v>
       </c>
     </row>
     <row r="454" spans="1:6">
       <c r="A454" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B454" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="C454" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D454" t="s">
         <v>11</v>
@@ -9472,72 +9460,72 @@
     </row>
     <row r="455" spans="1:6">
       <c r="A455" t="s">
-        <v>361</v>
-      </c>
-      <c r="B455" t="s">
-        <v>508</v>
-      </c>
-      <c r="C455" t="s">
-        <v>363</v>
-      </c>
-      <c r="D455" t="s">
-        <v>11</v>
-      </c>
-      <c r="F455" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="456" spans="1:6">
       <c r="A456" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B456" t="s">
+        <v>505</v>
+      </c>
+      <c r="C456" t="s">
+        <v>366</v>
+      </c>
+      <c r="D456" t="s">
+        <v>11</v>
+      </c>
+      <c r="E456" t="s">
+        <v>506</v>
+      </c>
+      <c r="F456" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="457" spans="1:6">
       <c r="A457" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B457" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C457" t="s">
-        <v>370</v>
+        <v>234</v>
       </c>
       <c r="D457" t="s">
         <v>11</v>
       </c>
-      <c r="E457" t="s">
-        <v>510</v>
-      </c>
       <c r="F457" t="s">
-        <v>38</v>
+        <v>353</v>
       </c>
     </row>
     <row r="458" spans="1:6">
       <c r="A458" t="s">
-        <v>35</v>
+        <v>354</v>
       </c>
       <c r="B458" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="C458" t="s">
-        <v>234</v>
+        <v>356</v>
       </c>
       <c r="D458" t="s">
         <v>11</v>
       </c>
       <c r="F458" t="s">
-        <v>357</v>
+        <v>42</v>
       </c>
     </row>
     <row r="459" spans="1:6">
       <c r="A459" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B459" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="C459" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D459" t="s">
         <v>11</v>
@@ -9548,72 +9536,72 @@
     </row>
     <row r="460" spans="1:6">
       <c r="A460" t="s">
-        <v>361</v>
-      </c>
-      <c r="B460" t="s">
-        <v>513</v>
-      </c>
-      <c r="C460" t="s">
-        <v>363</v>
-      </c>
-      <c r="D460" t="s">
-        <v>11</v>
-      </c>
-      <c r="F460" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="461" spans="1:6">
       <c r="A461" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B461" t="s">
+        <v>510</v>
+      </c>
+      <c r="C461" t="s">
+        <v>366</v>
+      </c>
+      <c r="D461" t="s">
+        <v>11</v>
+      </c>
+      <c r="E461" t="s">
+        <v>511</v>
+      </c>
+      <c r="F461" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="462" spans="1:6">
       <c r="A462" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B462" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C462" t="s">
-        <v>370</v>
+        <v>242</v>
       </c>
       <c r="D462" t="s">
         <v>11</v>
       </c>
-      <c r="E462" t="s">
-        <v>515</v>
-      </c>
       <c r="F462" t="s">
-        <v>38</v>
+        <v>353</v>
       </c>
     </row>
     <row r="463" spans="1:6">
       <c r="A463" t="s">
-        <v>35</v>
+        <v>354</v>
       </c>
       <c r="B463" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="C463" t="s">
-        <v>242</v>
+        <v>356</v>
       </c>
       <c r="D463" t="s">
         <v>11</v>
       </c>
       <c r="F463" t="s">
-        <v>357</v>
+        <v>42</v>
       </c>
     </row>
     <row r="464" spans="1:6">
       <c r="A464" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B464" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="C464" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D464" t="s">
         <v>11</v>
@@ -9624,72 +9612,72 @@
     </row>
     <row r="465" spans="1:6">
       <c r="A465" t="s">
-        <v>361</v>
-      </c>
-      <c r="B465" t="s">
-        <v>518</v>
-      </c>
-      <c r="C465" t="s">
-        <v>363</v>
-      </c>
-      <c r="D465" t="s">
-        <v>11</v>
-      </c>
-      <c r="F465" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="466" spans="1:6">
       <c r="A466" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B466" t="s">
+        <v>515</v>
+      </c>
+      <c r="C466" t="s">
+        <v>366</v>
+      </c>
+      <c r="D466" t="s">
+        <v>11</v>
+      </c>
+      <c r="E466" t="s">
+        <v>516</v>
+      </c>
+      <c r="F466" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="467" spans="1:6">
       <c r="A467" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B467" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C467" t="s">
-        <v>370</v>
+        <v>250</v>
       </c>
       <c r="D467" t="s">
         <v>11</v>
       </c>
-      <c r="E467" t="s">
-        <v>520</v>
-      </c>
       <c r="F467" t="s">
-        <v>38</v>
+        <v>353</v>
       </c>
     </row>
     <row r="468" spans="1:6">
       <c r="A468" t="s">
-        <v>35</v>
+        <v>354</v>
       </c>
       <c r="B468" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="C468" t="s">
-        <v>250</v>
+        <v>356</v>
       </c>
       <c r="D468" t="s">
         <v>11</v>
       </c>
       <c r="F468" t="s">
-        <v>357</v>
+        <v>42</v>
       </c>
     </row>
     <row r="469" spans="1:6">
       <c r="A469" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B469" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="C469" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D469" t="s">
         <v>11</v>
@@ -9700,177 +9688,201 @@
     </row>
     <row r="470" spans="1:6">
       <c r="A470" t="s">
-        <v>361</v>
-      </c>
-      <c r="B470" t="s">
-        <v>523</v>
-      </c>
-      <c r="C470" t="s">
-        <v>363</v>
-      </c>
-      <c r="D470" t="s">
-        <v>11</v>
-      </c>
-      <c r="F470" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="471" spans="1:6">
-      <c r="A471" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="473" spans="1:6">
-      <c r="A473" t="s">
+    <row r="472" spans="1:6">
+      <c r="A472" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="474" spans="1:6">
+      <c r="A474" t="s">
+        <v>35</v>
+      </c>
+      <c r="B474" t="s">
+        <v>520</v>
+      </c>
+      <c r="C474" t="s">
+        <v>521</v>
+      </c>
+      <c r="D474" t="s">
+        <v>11</v>
+      </c>
+      <c r="E474" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="475" spans="1:6">
       <c r="A475" t="s">
-        <v>35</v>
+        <v>522</v>
       </c>
       <c r="B475" t="s">
+        <v>523</v>
+      </c>
+      <c r="C475" t="s">
         <v>524</v>
       </c>
-      <c r="C475" t="s">
-        <v>525</v>
-      </c>
       <c r="D475" t="s">
         <v>11</v>
+      </c>
+      <c r="E475" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="476" spans="1:6">
       <c r="A476" t="s">
+        <v>525</v>
+      </c>
+      <c r="B476" t="s">
         <v>526</v>
       </c>
-      <c r="B476" t="s">
+      <c r="C476" t="s">
         <v>527</v>
       </c>
-      <c r="C476" t="s">
-        <v>528</v>
-      </c>
       <c r="D476" t="s">
         <v>11</v>
+      </c>
+      <c r="E476" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="477" spans="1:6">
       <c r="A477" t="s">
+        <v>528</v>
+      </c>
+      <c r="B477" t="s">
         <v>529</v>
       </c>
-      <c r="B477" t="s">
+      <c r="C477" t="s">
         <v>530</v>
       </c>
-      <c r="C477" t="s">
-        <v>531</v>
-      </c>
       <c r="D477" t="s">
         <v>11</v>
+      </c>
+      <c r="E477" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="478" spans="1:6">
       <c r="A478" t="s">
+        <v>12</v>
+      </c>
+      <c r="B478" t="s">
+        <v>531</v>
+      </c>
+      <c r="C478" t="s">
         <v>532</v>
       </c>
-      <c r="B478" t="s">
-        <v>533</v>
-      </c>
-      <c r="C478" t="s">
-        <v>534</v>
-      </c>
       <c r="D478" t="s">
         <v>11</v>
+      </c>
+      <c r="E478" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="479" spans="1:6">
       <c r="A479" t="s">
-        <v>12</v>
+        <v>533</v>
       </c>
       <c r="B479" t="s">
+        <v>534</v>
+      </c>
+      <c r="C479" t="s">
         <v>535</v>
       </c>
-      <c r="C479" t="s">
-        <v>536</v>
-      </c>
       <c r="D479" t="s">
         <v>11</v>
+      </c>
+      <c r="E479" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="480" spans="1:6">
       <c r="A480" t="s">
+        <v>536</v>
+      </c>
+      <c r="B480" t="s">
         <v>537</v>
       </c>
-      <c r="B480" t="s">
+      <c r="C480" t="s">
         <v>538</v>
       </c>
-      <c r="C480" t="s">
-        <v>539</v>
-      </c>
       <c r="D480" t="s">
         <v>11</v>
+      </c>
+      <c r="E480" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="481" spans="1:5">
       <c r="A481" t="s">
+        <v>539</v>
+      </c>
+      <c r="B481" t="s">
         <v>540</v>
       </c>
-      <c r="B481" t="s">
+      <c r="C481" t="s">
         <v>541</v>
       </c>
-      <c r="C481" t="s">
-        <v>542</v>
-      </c>
       <c r="D481" t="s">
         <v>11</v>
+      </c>
+      <c r="E481" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="482" spans="1:5">
       <c r="A482" t="s">
-        <v>543</v>
-      </c>
-      <c r="B482" t="s">
-        <v>544</v>
-      </c>
-      <c r="C482" t="s">
-        <v>545</v>
-      </c>
-      <c r="D482" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="483" spans="1:5">
       <c r="A483" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B483" t="s">
+        <v>542</v>
+      </c>
+      <c r="C483" t="s">
+        <v>543</v>
+      </c>
+      <c r="D483" t="s">
+        <v>11</v>
+      </c>
+      <c r="E483" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="484" spans="1:5">
       <c r="A484" t="s">
-        <v>8</v>
+        <v>544</v>
       </c>
       <c r="B484" t="s">
+        <v>545</v>
+      </c>
+      <c r="C484" t="s">
         <v>546</v>
       </c>
-      <c r="C484" t="s">
-        <v>547</v>
-      </c>
       <c r="D484" t="s">
         <v>11</v>
-      </c>
-      <c r="E484" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="485" spans="1:5">
       <c r="A485" t="s">
+        <v>547</v>
+      </c>
+      <c r="B485" t="s">
         <v>548</v>
       </c>
-      <c r="B485" t="s">
+      <c r="C485" t="s">
         <v>549</v>
       </c>
-      <c r="C485" t="s">
+      <c r="D485" t="s">
+        <v>11</v>
+      </c>
+      <c r="E485" t="s">
         <v>550</v>
-      </c>
-      <c r="D485" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="486" spans="1:5">
@@ -9903,50 +9915,47 @@
       <c r="D487" t="s">
         <v>11</v>
       </c>
-      <c r="E487" t="s">
-        <v>558</v>
-      </c>
     </row>
     <row r="488" spans="1:5">
       <c r="A488" t="s">
+        <v>558</v>
+      </c>
+      <c r="B488" t="s">
         <v>559</v>
       </c>
-      <c r="B488" t="s">
+      <c r="C488" t="s">
         <v>560</v>
       </c>
-      <c r="C488" t="s">
+      <c r="D488" t="s">
+        <v>11</v>
+      </c>
+      <c r="E488" t="s">
         <v>561</v>
-      </c>
-      <c r="D488" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="489" spans="1:5">
       <c r="A489" t="s">
+        <v>12</v>
+      </c>
+      <c r="B489" t="s">
+        <v>531</v>
+      </c>
+      <c r="C489" t="s">
         <v>562</v>
       </c>
-      <c r="B489" t="s">
-        <v>563</v>
-      </c>
-      <c r="C489" t="s">
-        <v>564</v>
-      </c>
       <c r="D489" t="s">
         <v>11</v>
-      </c>
-      <c r="E489" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="490" spans="1:5">
       <c r="A490" t="s">
-        <v>12</v>
+        <v>563</v>
       </c>
       <c r="B490" t="s">
-        <v>535</v>
+        <v>564</v>
       </c>
       <c r="C490" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D490" t="s">
         <v>11</v>
@@ -9954,21 +9963,24 @@
     </row>
     <row r="491" spans="1:5">
       <c r="A491" t="s">
+        <v>12</v>
+      </c>
+      <c r="B491" t="s">
+        <v>566</v>
+      </c>
+      <c r="C491" t="s">
         <v>567</v>
       </c>
-      <c r="B491" t="s">
+      <c r="D491" t="s">
+        <v>11</v>
+      </c>
+      <c r="E491" t="s">
         <v>568</v>
-      </c>
-      <c r="C491" t="s">
-        <v>569</v>
-      </c>
-      <c r="D491" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="492" spans="1:5">
       <c r="A492" t="s">
-        <v>12</v>
+        <v>569</v>
       </c>
       <c r="B492" t="s">
         <v>570</v>
@@ -9979,27 +9991,27 @@
       <c r="D492" t="s">
         <v>11</v>
       </c>
-      <c r="E492" t="s">
-        <v>572</v>
-      </c>
     </row>
     <row r="493" spans="1:5">
       <c r="A493" t="s">
+        <v>12</v>
+      </c>
+      <c r="B493" t="s">
+        <v>572</v>
+      </c>
+      <c r="C493" t="s">
         <v>573</v>
       </c>
-      <c r="B493" t="s">
+      <c r="D493" t="s">
+        <v>11</v>
+      </c>
+      <c r="E493" t="s">
         <v>574</v>
-      </c>
-      <c r="C493" t="s">
-        <v>575</v>
-      </c>
-      <c r="D493" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="494" spans="1:5">
       <c r="A494" t="s">
-        <v>12</v>
+        <v>575</v>
       </c>
       <c r="B494" t="s">
         <v>576</v>
@@ -10010,61 +10022,61 @@
       <c r="D494" t="s">
         <v>11</v>
       </c>
-      <c r="E494" t="s">
-        <v>578</v>
-      </c>
     </row>
     <row r="495" spans="1:5">
       <c r="A495" t="s">
+        <v>578</v>
+      </c>
+      <c r="B495" t="s">
         <v>579</v>
       </c>
-      <c r="B495" t="s">
+      <c r="C495" t="s">
         <v>580</v>
       </c>
-      <c r="C495" t="s">
+      <c r="D495" t="s">
+        <v>11</v>
+      </c>
+      <c r="E495" t="s">
         <v>581</v>
-      </c>
-      <c r="D495" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="496" spans="1:5">
       <c r="A496" t="s">
+        <v>12</v>
+      </c>
+      <c r="B496" t="s">
         <v>582</v>
       </c>
-      <c r="B496" t="s">
+      <c r="C496" t="s">
         <v>583</v>
       </c>
-      <c r="C496" t="s">
+      <c r="D496" t="s">
+        <v>11</v>
+      </c>
+      <c r="E496" t="s">
         <v>584</v>
-      </c>
-      <c r="D496" t="s">
-        <v>11</v>
-      </c>
-      <c r="E496" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="497" spans="1:5">
       <c r="A497" t="s">
-        <v>12</v>
-      </c>
-      <c r="B497" t="s">
-        <v>586</v>
-      </c>
-      <c r="C497" t="s">
-        <v>587</v>
-      </c>
-      <c r="D497" t="s">
-        <v>11</v>
-      </c>
-      <c r="E497" t="s">
-        <v>588</v>
+        <v>22</v>
       </c>
     </row>
     <row r="498" spans="1:5">
       <c r="A498" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B498" t="s">
+        <v>585</v>
+      </c>
+      <c r="C498" t="s">
+        <v>586</v>
+      </c>
+      <c r="D498" t="s">
+        <v>11</v>
+      </c>
+      <c r="E498" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="499" spans="1:5">
@@ -10072,24 +10084,21 @@
         <v>8</v>
       </c>
       <c r="B499" t="s">
-        <v>589</v>
-      </c>
-      <c r="C499" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="D499" t="s">
         <v>11</v>
-      </c>
-      <c r="E499" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="500" spans="1:5">
       <c r="A500" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B500" t="s">
-        <v>591</v>
+        <v>588</v>
+      </c>
+      <c r="C500" t="s">
+        <v>589</v>
       </c>
       <c r="D500" t="s">
         <v>11</v>
@@ -10097,13 +10106,13 @@
     </row>
     <row r="501" spans="1:5">
       <c r="A501" t="s">
-        <v>35</v>
+        <v>590</v>
       </c>
       <c r="B501" t="s">
+        <v>591</v>
+      </c>
+      <c r="C501" t="s">
         <v>592</v>
-      </c>
-      <c r="C501" t="s">
-        <v>593</v>
       </c>
       <c r="D501" t="s">
         <v>11</v>
@@ -10111,13 +10120,13 @@
     </row>
     <row r="502" spans="1:5">
       <c r="A502" t="s">
+        <v>590</v>
+      </c>
+      <c r="B502" t="s">
+        <v>593</v>
+      </c>
+      <c r="C502" t="s">
         <v>594</v>
-      </c>
-      <c r="B502" t="s">
-        <v>595</v>
-      </c>
-      <c r="C502" t="s">
-        <v>596</v>
       </c>
       <c r="D502" t="s">
         <v>11</v>
@@ -10125,13 +10134,13 @@
     </row>
     <row r="503" spans="1:5">
       <c r="A503" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="B503" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C503" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D503" t="s">
         <v>11</v>
@@ -10139,32 +10148,32 @@
     </row>
     <row r="504" spans="1:5">
       <c r="A504" t="s">
-        <v>594</v>
-      </c>
-      <c r="B504" t="s">
-        <v>599</v>
-      </c>
-      <c r="C504" t="s">
-        <v>600</v>
-      </c>
-      <c r="D504" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="505" spans="1:5">
       <c r="A505" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="B505" t="s">
+        <v>597</v>
+      </c>
+      <c r="C505" t="s">
+        <v>521</v>
+      </c>
+      <c r="D505" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="506" spans="1:5">
       <c r="A506" t="s">
-        <v>35</v>
+        <v>598</v>
       </c>
       <c r="B506" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C506" t="s">
-        <v>525</v>
+        <v>600</v>
       </c>
       <c r="D506" t="s">
         <v>11</v>
@@ -10172,32 +10181,32 @@
     </row>
     <row r="507" spans="1:5">
       <c r="A507" t="s">
-        <v>602</v>
-      </c>
-      <c r="B507" t="s">
-        <v>603</v>
-      </c>
-      <c r="C507" t="s">
-        <v>604</v>
-      </c>
-      <c r="D507" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="508" spans="1:5">
       <c r="A508" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B508" t="s">
+        <v>601</v>
+      </c>
+      <c r="C508" t="s">
+        <v>602</v>
+      </c>
+      <c r="D508" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="509" spans="1:5">
       <c r="A509" t="s">
-        <v>8</v>
+        <v>603</v>
       </c>
       <c r="B509" t="s">
+        <v>604</v>
+      </c>
+      <c r="C509" t="s">
         <v>605</v>
-      </c>
-      <c r="C509" t="s">
-        <v>606</v>
       </c>
       <c r="D509" t="s">
         <v>11</v>
@@ -10205,21 +10214,24 @@
     </row>
     <row r="510" spans="1:5">
       <c r="A510" t="s">
+        <v>12</v>
+      </c>
+      <c r="B510" t="s">
+        <v>606</v>
+      </c>
+      <c r="C510" t="s">
         <v>607</v>
       </c>
-      <c r="B510" t="s">
+      <c r="D510" t="s">
+        <v>11</v>
+      </c>
+      <c r="E510" t="s">
         <v>608</v>
-      </c>
-      <c r="C510" t="s">
-        <v>609</v>
-      </c>
-      <c r="D510" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="511" spans="1:5">
       <c r="A511" t="s">
-        <v>12</v>
+        <v>609</v>
       </c>
       <c r="B511" t="s">
         <v>610</v>
@@ -10230,43 +10242,26 @@
       <c r="D511" t="s">
         <v>11</v>
       </c>
-      <c r="E511" t="s">
-        <v>612</v>
-      </c>
     </row>
     <row r="512" spans="1:5">
       <c r="A512" t="s">
+        <v>12</v>
+      </c>
+      <c r="B512" t="s">
+        <v>612</v>
+      </c>
+      <c r="C512" t="s">
         <v>613</v>
       </c>
-      <c r="B512" t="s">
+      <c r="D512" t="s">
+        <v>11</v>
+      </c>
+      <c r="E512" t="s">
         <v>614</v>
       </c>
-      <c r="C512" t="s">
-        <v>615</v>
-      </c>
-      <c r="D512" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="513" spans="1:5">
+    </row>
+    <row r="513" spans="1:1">
       <c r="A513" t="s">
-        <v>12</v>
-      </c>
-      <c r="B513" t="s">
-        <v>616</v>
-      </c>
-      <c r="C513" t="s">
-        <v>617</v>
-      </c>
-      <c r="D513" t="s">
-        <v>11</v>
-      </c>
-      <c r="E513" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="514" spans="1:5">
-      <c r="A514" t="s">
         <v>22</v>
       </c>
     </row>
@@ -10286,7 +10281,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -10295,1143 +10290,1143 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="B2" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="C2" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
+        <v>617</v>
+      </c>
+      <c r="B3" t="s">
+        <v>620</v>
+      </c>
+      <c r="C3" t="s">
         <v>621</v>
-      </c>
-      <c r="B3" t="s">
-        <v>624</v>
-      </c>
-      <c r="C3" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="B4" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="C4" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
+        <v>622</v>
+      </c>
+      <c r="B5" t="s">
+        <v>625</v>
+      </c>
+      <c r="C5" t="s">
         <v>626</v>
-      </c>
-      <c r="B5" t="s">
-        <v>629</v>
-      </c>
-      <c r="C5" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="B6" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="C6" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="B7" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="C7" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="B8" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="C8" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="B9" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="C9" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="B10" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="C10" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="B11" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="C11" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
+        <v>637</v>
+      </c>
+      <c r="B12" t="s">
+        <v>640</v>
+      </c>
+      <c r="C12" t="s">
         <v>641</v>
-      </c>
-      <c r="B12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C12" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="B13" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="C13" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="B14" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="C14" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="B15" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="C15" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
+        <v>646</v>
+      </c>
+      <c r="B16" t="s">
+        <v>649</v>
+      </c>
+      <c r="C16" t="s">
         <v>650</v>
-      </c>
-      <c r="B16" t="s">
-        <v>653</v>
-      </c>
-      <c r="C16" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="B17" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C17" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="B18" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C18" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="B19" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="C19" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="B20" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="C20" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
+        <v>657</v>
+      </c>
+      <c r="B21" t="s">
+        <v>660</v>
+      </c>
+      <c r="C21" t="s">
         <v>661</v>
-      </c>
-      <c r="B21" t="s">
-        <v>664</v>
-      </c>
-      <c r="C21" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="B22" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="C22" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="B23" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="C23" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="B24" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="C24" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="B25" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="C25" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
+        <v>668</v>
+      </c>
+      <c r="B26" t="s">
+        <v>671</v>
+      </c>
+      <c r="C26" t="s">
         <v>672</v>
-      </c>
-      <c r="B26" t="s">
-        <v>675</v>
-      </c>
-      <c r="C26" t="s">
-        <v>676</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="B27" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="C27" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="B28" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="C28" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
+        <v>675</v>
+      </c>
+      <c r="B29" t="s">
+        <v>678</v>
+      </c>
+      <c r="C29" t="s">
         <v>679</v>
-      </c>
-      <c r="B29" t="s">
-        <v>682</v>
-      </c>
-      <c r="C29" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="B30" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="C30" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="B31" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="C31" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
+        <v>681</v>
+      </c>
+      <c r="B32" t="s">
+        <v>684</v>
+      </c>
+      <c r="C32" t="s">
         <v>685</v>
-      </c>
-      <c r="B32" t="s">
-        <v>688</v>
-      </c>
-      <c r="C32" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="B33" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="C33" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="B34" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="C34" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="B35" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="C35" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
+        <v>687</v>
+      </c>
+      <c r="B36" t="s">
+        <v>690</v>
+      </c>
+      <c r="C36" t="s">
         <v>691</v>
-      </c>
-      <c r="B36" t="s">
-        <v>694</v>
-      </c>
-      <c r="C36" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="B37" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="C37" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
+        <v>692</v>
+      </c>
+      <c r="B38" t="s">
+        <v>695</v>
+      </c>
+      <c r="C38" t="s">
         <v>696</v>
-      </c>
-      <c r="B38" t="s">
-        <v>699</v>
-      </c>
-      <c r="C38" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="B39" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="C39" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
+        <v>697</v>
+      </c>
+      <c r="B40" t="s">
+        <v>700</v>
+      </c>
+      <c r="C40" t="s">
         <v>701</v>
-      </c>
-      <c r="B40" t="s">
-        <v>704</v>
-      </c>
-      <c r="C40" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="B41" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="C41" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="B42" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="C42" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
+        <v>704</v>
+      </c>
+      <c r="B43" t="s">
+        <v>707</v>
+      </c>
+      <c r="C43" t="s">
         <v>708</v>
-      </c>
-      <c r="B43" t="s">
-        <v>711</v>
-      </c>
-      <c r="C43" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="B44" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="C44" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="B45" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="C45" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="B46" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="C46" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="D46" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="B47" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="C47" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
+        <v>711</v>
+      </c>
+      <c r="B48" t="s">
         <v>715</v>
       </c>
-      <c r="B48" t="s">
-        <v>719</v>
-      </c>
       <c r="C48" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="B49" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="C49" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
+        <v>716</v>
+      </c>
+      <c r="B50" t="s">
+        <v>719</v>
+      </c>
+      <c r="C50" t="s">
         <v>720</v>
-      </c>
-      <c r="B50" t="s">
-        <v>723</v>
-      </c>
-      <c r="C50" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="B51" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="C51" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="B52" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="C52" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
+        <v>723</v>
+      </c>
+      <c r="B53" t="s">
+        <v>726</v>
+      </c>
+      <c r="C53" t="s">
         <v>727</v>
-      </c>
-      <c r="B53" t="s">
-        <v>730</v>
-      </c>
-      <c r="C53" t="s">
-        <v>731</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="B54" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="C54" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="B55" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="C55" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="B56" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="C56" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="B57" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="C57" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="B58" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="C58" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="B59" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="C59" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="B60" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="C60" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="B61" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="C61" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="B62" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="C62" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
+        <v>735</v>
+      </c>
+      <c r="B63" t="s">
+        <v>738</v>
+      </c>
+      <c r="C63" t="s">
         <v>739</v>
-      </c>
-      <c r="B63" t="s">
-        <v>742</v>
-      </c>
-      <c r="C63" t="s">
-        <v>743</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="B64" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="C64" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="B65" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="C65" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="B66" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="C66" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="B67" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="C67" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="B68" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="C68" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="B69" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="C69" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="B70" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="C70" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="B71" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="C71" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="B72" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="C72" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="B73" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="C73" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="B74" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="C74" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B75" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="C75" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
+        <v>749</v>
+      </c>
+      <c r="B76" t="s">
+        <v>752</v>
+      </c>
+      <c r="C76" t="s">
         <v>753</v>
-      </c>
-      <c r="B76" t="s">
-        <v>756</v>
-      </c>
-      <c r="C76" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B77" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="C77" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B78" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="C78" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="B79" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="C79" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="B80" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="C80" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="B81" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="C81" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
+        <v>757</v>
+      </c>
+      <c r="B82" t="s">
+        <v>760</v>
+      </c>
+      <c r="C82" t="s">
         <v>761</v>
-      </c>
-      <c r="B82" t="s">
-        <v>764</v>
-      </c>
-      <c r="C82" t="s">
-        <v>765</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="B83" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="C83" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="B84" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="C84" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
+        <v>762</v>
+      </c>
+      <c r="B85" t="s">
+        <v>765</v>
+      </c>
+      <c r="C85" t="s">
         <v>766</v>
-      </c>
-      <c r="B85" t="s">
-        <v>769</v>
-      </c>
-      <c r="C85" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="B86" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="C86" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="B87" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="C87" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="B88" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="C88" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
+        <v>771</v>
+      </c>
+      <c r="B89" t="s">
+        <v>774</v>
+      </c>
+      <c r="C89" t="s">
         <v>775</v>
-      </c>
-      <c r="B89" t="s">
-        <v>778</v>
-      </c>
-      <c r="C89" t="s">
-        <v>779</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="B90" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="C90" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="B91" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="C91" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="B92" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="C92" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="B93" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="C93" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
+        <v>782</v>
+      </c>
+      <c r="B94" t="s">
+        <v>785</v>
+      </c>
+      <c r="C94" t="s">
         <v>786</v>
-      </c>
-      <c r="B94" t="s">
-        <v>789</v>
-      </c>
-      <c r="C94" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="B95" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="C95" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="B96" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="C96" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" s="1" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="B97" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="C97" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="C98" t="s">
         <v>793</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>796</v>
-      </c>
-      <c r="C98" t="s">
-        <v>797</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" s="1" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="B99" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="C99" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" s="1" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="B101" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="C101" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="B102" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="C102" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="B103" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="C103" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="B104" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="C104" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
     </row>
   </sheetData>
@@ -11446,12 +11441,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
     </row>
   </sheetData>

--- a/surveys/biochar_survey_december_2025.xlsx
+++ b/surveys/biochar_survey_december_2025.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C4E07762-31C3-4608-9FAC-991CBC994265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4749A2D0-5141-4F66-B9AF-FE73F9785B49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2466" uniqueCount="802">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2461" uniqueCount="801">
   <si>
     <t>type</t>
   </si>
@@ -1628,100 +1628,97 @@
     <t>C.4) During the seasons you applied biochar, how often did you apply it?</t>
   </si>
   <si>
+    <t>select_multiple yw1ml89</t>
+  </si>
+  <si>
+    <t>fertilizer_before_biochar</t>
+  </si>
+  <si>
+    <t>C.5) Prior to the season when you applied biochar, did you use fertilizer on that plot? (Select all that apply)</t>
+  </si>
+  <si>
+    <t>select_multiple pc1lg93</t>
+  </si>
+  <si>
+    <t>fertilizers_used_before_biocha</t>
+  </si>
+  <si>
+    <t>C.6) What kind of fertilizer did you use before biochar? (Select all that apply)</t>
+  </si>
+  <si>
+    <t>select_multiple td2jb01</t>
+  </si>
+  <si>
+    <t>fertilizers_used_with_biochar</t>
+  </si>
+  <si>
+    <t>C.7) When you applied biochar, did you also use another soil fertilizer in addition to biochar? (Select all that apply)</t>
+  </si>
+  <si>
+    <t>group_ad9ws92</t>
+  </si>
+  <si>
+    <t>Observation and Results</t>
+  </si>
+  <si>
+    <t>select_one sj05t62</t>
+  </si>
+  <si>
+    <t>biochar_used_on_different_area</t>
+  </si>
+  <si>
+    <t>D.1) On the crops where you used biochar, did you use it on some plots and not on other plots?</t>
+  </si>
+  <si>
+    <t>select_one xj9am89</t>
+  </si>
+  <si>
+    <t>noticed_difference</t>
+  </si>
+  <si>
+    <t>D.1.a) Did  you notice any difference between the plots where you used biochar and the plots where you did not or if you used biochar on only part of the plot did you see a difference in yield between where biochar was used and where it was not?</t>
+  </si>
+  <si>
+    <t>${biochar_used_on_different_area} = 'yes'</t>
+  </si>
+  <si>
+    <t>select_one hd83z15</t>
+  </si>
+  <si>
+    <t>significance_difference</t>
+  </si>
+  <si>
+    <t>D.1.b) How significant was the difference?</t>
+  </si>
+  <si>
+    <t>${noticed_difference} = 'yes' and ${biochar_used_on_different_area} = 'yes'</t>
+  </si>
+  <si>
+    <t>select_one hy91q54</t>
+  </si>
+  <si>
+    <t>noticeable_difference_in_yield</t>
+  </si>
+  <si>
+    <t>D.2) For crops for which you used biochar over the entire plot, can you judge whether there was a different in the yield from the crop was last cultivated, without biochar?</t>
+  </si>
+  <si>
+    <t>select_one ln0re11</t>
+  </si>
+  <si>
+    <t>significance_difference_yield</t>
+  </si>
+  <si>
+    <t>D.2.a) How significant was the difference in yield volume to the last yield without biochar?</t>
+  </si>
+  <si>
+    <t>${noticeable_difference_in_yield} = 'yes'</t>
+  </si>
+  <si>
     <t>most_affected_crop</t>
   </si>
   <si>
-    <t>C.5) If you used biochar on more than one crop, for which crops did it make the biggest difference? (Leave empty when cannot judge)</t>
-  </si>
-  <si>
-    <t>select_multiple yw1ml89</t>
-  </si>
-  <si>
-    <t>fertilizer_before_biochar</t>
-  </si>
-  <si>
-    <t>C.6) Before using biochar, did you use fertilizer? (Select all that apply)</t>
-  </si>
-  <si>
-    <t>select_multiple td2jb01</t>
-  </si>
-  <si>
-    <t>fertilizers_used_with_biochar</t>
-  </si>
-  <si>
-    <t>C.7) When you applied biochar, did you also use another soil fertilizer in addition to biochar? (Select all that apply)</t>
-  </si>
-  <si>
-    <t>select_multiple pc1lg93</t>
-  </si>
-  <si>
-    <t>fertilizers_used_before_biocha</t>
-  </si>
-  <si>
-    <t>C.8) What kind of fertilizer did you use before biochar? (Select all that apply)</t>
-  </si>
-  <si>
-    <t>group_ad9ws92</t>
-  </si>
-  <si>
-    <t>Observation and Results</t>
-  </si>
-  <si>
-    <t>select_one sj05t62</t>
-  </si>
-  <si>
-    <t>biochar_used_on_different_area</t>
-  </si>
-  <si>
-    <t>D.1) On the crops where you used biochar, did you use it on some plots and not one other plots?</t>
-  </si>
-  <si>
-    <t>select_one xj9am89</t>
-  </si>
-  <si>
-    <t>noticed_difference</t>
-  </si>
-  <si>
-    <t>D.2) Did  you notice any difference between the plots where you used biochar and the plots where you did not?</t>
-  </si>
-  <si>
-    <t>${biochar_used_on_different_area} = 'yes'</t>
-  </si>
-  <si>
-    <t>select_one hd83z15</t>
-  </si>
-  <si>
-    <t>significance_difference</t>
-  </si>
-  <si>
-    <t>D.2.a) How significant was the difference?</t>
-  </si>
-  <si>
-    <t>${noticed_difference} = 'yes'</t>
-  </si>
-  <si>
-    <t>select_one hy91q54</t>
-  </si>
-  <si>
-    <t>noticeable_difference_in_yield</t>
-  </si>
-  <si>
-    <t>D.3) For crops for which you used biochar over the entire plot, can you judge whether there was a different in the yield from the crop was last cultivated, without biochar?</t>
-  </si>
-  <si>
-    <t>select_one ln0re11</t>
-  </si>
-  <si>
-    <t>significance_difference_yield</t>
-  </si>
-  <si>
-    <t>D.3.a) How significant was the difference in yield volume to the last yield without biochar?</t>
-  </si>
-  <si>
-    <t>${noticeable_difference_in_yield} = 'yes'</t>
-  </si>
-  <si>
-    <t>D.4) If you used biochar on more than one crop, for which crops did it make the biggest difference? (Leave empty when cannot judge)</t>
+    <t>D.3) If you used biochar on more than one crop, for which crops did it make the biggest difference? (Leave empty when cannot judge)</t>
   </si>
   <si>
     <t>select_one po8ix91</t>
@@ -1730,13 +1727,13 @@
     <t>wants_to_continue_biochar</t>
   </si>
   <si>
-    <t>D.5) Do you plan to continue making and using biochar?</t>
+    <t>D.4) Do you plan to continue making and using biochar?</t>
   </si>
   <si>
     <t>reason_why_stopping_biochar</t>
   </si>
   <si>
-    <t>D.5.a) Why do you not plan to continue making biochar</t>
+    <t>D.4.a) Why do you not plan to continue making biochar</t>
   </si>
   <si>
     <t>${wants_to_continue_biochar} = 'no'</t>
@@ -1748,13 +1745,13 @@
     <t>simplification_for_biochar_use</t>
   </si>
   <si>
-    <t>D.6) What would make it easier for you to use biochar in future seasons?</t>
+    <t>D.5) What would make it easier for you to use biochar in future seasons?</t>
   </si>
   <si>
     <t>specified_simplifications</t>
   </si>
   <si>
-    <t>D.6.a) Please specify what would make it easier:</t>
+    <t>D.5.a) Please specify what would make it easier:</t>
   </si>
   <si>
     <t>selected(${simplification_for_biochar_use}, 'other')</t>
@@ -1766,7 +1763,7 @@
     <t>would_purchase_biochar</t>
   </si>
   <si>
-    <t>D.7) Would you purchase biochar if it were available?</t>
+    <t>D.6) Would you purchase biochar if it were available?</t>
   </si>
   <si>
     <t>select_multiple rm9rw73</t>
@@ -1775,7 +1772,7 @@
     <t>why_not_purchase_biochar</t>
   </si>
   <si>
-    <t>D.7.a) Why not?</t>
+    <t>D.6.a) Why not?</t>
   </si>
   <si>
     <t>${would_purchase_biochar} = 'no'</t>
@@ -1784,7 +1781,7 @@
     <t>specification_why_not_purchase</t>
   </si>
   <si>
-    <t>D.7.b) Please specify why not:</t>
+    <t>D.6.b) Please specify why not:</t>
   </si>
   <si>
     <t>selected(${why_not_purchase_biochar}, 'other')</t>
@@ -2787,7 +2784,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F513"/>
+  <dimension ref="A1:F512"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.28515625" customWidth="1"/>
@@ -9766,13 +9763,13 @@
     </row>
     <row r="478" spans="1:6">
       <c r="A478" t="s">
-        <v>12</v>
+        <v>531</v>
       </c>
       <c r="B478" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C478" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D478" t="s">
         <v>11</v>
@@ -9783,13 +9780,13 @@
     </row>
     <row r="479" spans="1:6">
       <c r="A479" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B479" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C479" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D479" t="s">
         <v>11</v>
@@ -9800,13 +9797,13 @@
     </row>
     <row r="480" spans="1:6">
       <c r="A480" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B480" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C480" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D480" t="s">
         <v>11</v>
@@ -9817,131 +9814,128 @@
     </row>
     <row r="481" spans="1:5">
       <c r="A481" t="s">
-        <v>539</v>
-      </c>
-      <c r="B481" t="s">
-        <v>540</v>
-      </c>
-      <c r="C481" t="s">
-        <v>541</v>
-      </c>
-      <c r="D481" t="s">
-        <v>11</v>
-      </c>
-      <c r="E481" t="s">
-        <v>349</v>
+        <v>22</v>
       </c>
     </row>
     <row r="482" spans="1:5">
       <c r="A482" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B482" t="s">
+        <v>540</v>
+      </c>
+      <c r="C482" t="s">
+        <v>541</v>
+      </c>
+      <c r="D482" t="s">
+        <v>11</v>
+      </c>
+      <c r="E482" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="483" spans="1:5">
       <c r="A483" t="s">
-        <v>8</v>
+        <v>542</v>
       </c>
       <c r="B483" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C483" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D483" t="s">
         <v>11</v>
-      </c>
-      <c r="E483" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="484" spans="1:5">
       <c r="A484" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B484" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C484" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D484" t="s">
         <v>11</v>
+      </c>
+      <c r="E484" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="485" spans="1:5">
       <c r="A485" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B485" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C485" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="D485" t="s">
         <v>11</v>
       </c>
       <c r="E485" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="486" spans="1:5">
       <c r="A486" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B486" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C486" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="D486" t="s">
         <v>11</v>
-      </c>
-      <c r="E486" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="487" spans="1:5">
       <c r="A487" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B487" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C487" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D487" t="s">
         <v>11</v>
+      </c>
+      <c r="E487" t="s">
+        <v>559</v>
       </c>
     </row>
     <row r="488" spans="1:5">
       <c r="A488" t="s">
-        <v>558</v>
+        <v>12</v>
       </c>
       <c r="B488" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C488" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D488" t="s">
         <v>11</v>
-      </c>
-      <c r="E488" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="489" spans="1:5">
       <c r="A489" t="s">
-        <v>12</v>
+        <v>562</v>
       </c>
       <c r="B489" t="s">
-        <v>531</v>
+        <v>563</v>
       </c>
       <c r="C489" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D489" t="s">
         <v>11</v>
@@ -9949,117 +9943,120 @@
     </row>
     <row r="490" spans="1:5">
       <c r="A490" t="s">
-        <v>563</v>
+        <v>12</v>
       </c>
       <c r="B490" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C490" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D490" t="s">
         <v>11</v>
+      </c>
+      <c r="E490" t="s">
+        <v>567</v>
       </c>
     </row>
     <row r="491" spans="1:5">
       <c r="A491" t="s">
-        <v>12</v>
+        <v>568</v>
       </c>
       <c r="B491" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="C491" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="D491" t="s">
         <v>11</v>
-      </c>
-      <c r="E491" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="492" spans="1:5">
       <c r="A492" t="s">
-        <v>569</v>
+        <v>12</v>
       </c>
       <c r="B492" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C492" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D492" t="s">
         <v>11</v>
+      </c>
+      <c r="E492" t="s">
+        <v>573</v>
       </c>
     </row>
     <row r="493" spans="1:5">
       <c r="A493" t="s">
-        <v>12</v>
+        <v>574</v>
       </c>
       <c r="B493" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C493" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="D493" t="s">
         <v>11</v>
-      </c>
-      <c r="E493" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="494" spans="1:5">
       <c r="A494" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B494" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C494" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="D494" t="s">
         <v>11</v>
+      </c>
+      <c r="E494" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="495" spans="1:5">
       <c r="A495" t="s">
-        <v>578</v>
+        <v>12</v>
       </c>
       <c r="B495" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C495" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="D495" t="s">
         <v>11</v>
       </c>
       <c r="E495" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="496" spans="1:5">
       <c r="A496" t="s">
-        <v>12</v>
-      </c>
-      <c r="B496" t="s">
-        <v>582</v>
-      </c>
-      <c r="C496" t="s">
-        <v>583</v>
-      </c>
-      <c r="D496" t="s">
-        <v>11</v>
-      </c>
-      <c r="E496" t="s">
-        <v>584</v>
+        <v>22</v>
       </c>
     </row>
     <row r="497" spans="1:5">
       <c r="A497" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B497" t="s">
+        <v>584</v>
+      </c>
+      <c r="C497" t="s">
+        <v>585</v>
+      </c>
+      <c r="D497" t="s">
+        <v>11</v>
+      </c>
+      <c r="E497" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="498" spans="1:5">
@@ -10067,38 +10064,35 @@
         <v>8</v>
       </c>
       <c r="B498" t="s">
-        <v>585</v>
-      </c>
-      <c r="C498" t="s">
         <v>586</v>
       </c>
       <c r="D498" t="s">
         <v>11</v>
-      </c>
-      <c r="E498" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="499" spans="1:5">
       <c r="A499" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B499" t="s">
         <v>587</v>
       </c>
+      <c r="C499" t="s">
+        <v>588</v>
+      </c>
       <c r="D499" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="500" spans="1:5">
       <c r="A500" t="s">
-        <v>35</v>
+        <v>589</v>
       </c>
       <c r="B500" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C500" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="D500" t="s">
         <v>11</v>
@@ -10106,13 +10100,13 @@
     </row>
     <row r="501" spans="1:5">
       <c r="A501" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B501" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C501" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D501" t="s">
         <v>11</v>
@@ -10120,13 +10114,13 @@
     </row>
     <row r="502" spans="1:5">
       <c r="A502" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B502" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C502" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D502" t="s">
         <v>11</v>
@@ -10134,32 +10128,32 @@
     </row>
     <row r="503" spans="1:5">
       <c r="A503" t="s">
-        <v>590</v>
-      </c>
-      <c r="B503" t="s">
-        <v>595</v>
-      </c>
-      <c r="C503" t="s">
-        <v>596</v>
-      </c>
-      <c r="D503" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="504" spans="1:5">
       <c r="A504" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="B504" t="s">
+        <v>596</v>
+      </c>
+      <c r="C504" t="s">
+        <v>521</v>
+      </c>
+      <c r="D504" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="505" spans="1:5">
       <c r="A505" t="s">
-        <v>35</v>
+        <v>597</v>
       </c>
       <c r="B505" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C505" t="s">
-        <v>521</v>
+        <v>599</v>
       </c>
       <c r="D505" t="s">
         <v>11</v>
@@ -10167,32 +10161,32 @@
     </row>
     <row r="506" spans="1:5">
       <c r="A506" t="s">
-        <v>598</v>
-      </c>
-      <c r="B506" t="s">
-        <v>599</v>
-      </c>
-      <c r="C506" t="s">
-        <v>600</v>
-      </c>
-      <c r="D506" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="507" spans="1:5">
       <c r="A507" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B507" t="s">
+        <v>600</v>
+      </c>
+      <c r="C507" t="s">
+        <v>601</v>
+      </c>
+      <c r="D507" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="508" spans="1:5">
       <c r="A508" t="s">
-        <v>8</v>
+        <v>602</v>
       </c>
       <c r="B508" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C508" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="D508" t="s">
         <v>11</v>
@@ -10200,68 +10194,54 @@
     </row>
     <row r="509" spans="1:5">
       <c r="A509" t="s">
-        <v>603</v>
+        <v>12</v>
       </c>
       <c r="B509" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C509" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D509" t="s">
         <v>11</v>
+      </c>
+      <c r="E509" t="s">
+        <v>607</v>
       </c>
     </row>
     <row r="510" spans="1:5">
       <c r="A510" t="s">
-        <v>12</v>
+        <v>608</v>
       </c>
       <c r="B510" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C510" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D510" t="s">
         <v>11</v>
-      </c>
-      <c r="E510" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="511" spans="1:5">
       <c r="A511" t="s">
-        <v>609</v>
+        <v>12</v>
       </c>
       <c r="B511" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C511" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D511" t="s">
         <v>11</v>
+      </c>
+      <c r="E511" t="s">
+        <v>613</v>
       </c>
     </row>
     <row r="512" spans="1:5">
       <c r="A512" t="s">
-        <v>12</v>
-      </c>
-      <c r="B512" t="s">
-        <v>612</v>
-      </c>
-      <c r="C512" t="s">
-        <v>613</v>
-      </c>
-      <c r="D512" t="s">
-        <v>11</v>
-      </c>
-      <c r="E512" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="513" spans="1:1">
-      <c r="A513" t="s">
         <v>22</v>
       </c>
     </row>
@@ -10281,7 +10261,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -10290,1143 +10270,1143 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
+        <v>616</v>
+      </c>
+      <c r="B2" t="s">
         <v>617</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>618</v>
-      </c>
-      <c r="C2" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B3" t="s">
+        <v>619</v>
+      </c>
+      <c r="C3" t="s">
         <v>620</v>
-      </c>
-      <c r="C3" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
+        <v>621</v>
+      </c>
+      <c r="B4" t="s">
         <v>622</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>623</v>
-      </c>
-      <c r="C4" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B5" t="s">
+        <v>624</v>
+      </c>
+      <c r="C5" t="s">
         <v>625</v>
-      </c>
-      <c r="C5" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B6" t="s">
+        <v>626</v>
+      </c>
+      <c r="C6" t="s">
         <v>627</v>
-      </c>
-      <c r="C6" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B7" t="s">
+        <v>628</v>
+      </c>
+      <c r="C7" t="s">
         <v>629</v>
-      </c>
-      <c r="C7" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B8" t="s">
+        <v>630</v>
+      </c>
+      <c r="C8" t="s">
         <v>631</v>
-      </c>
-      <c r="C8" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B9" t="s">
+        <v>632</v>
+      </c>
+      <c r="C9" t="s">
         <v>633</v>
-      </c>
-      <c r="C9" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B10" t="s">
+        <v>634</v>
+      </c>
+      <c r="C10" t="s">
         <v>635</v>
-      </c>
-      <c r="C10" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
+        <v>636</v>
+      </c>
+      <c r="B11" t="s">
         <v>637</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>638</v>
-      </c>
-      <c r="C11" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B12" t="s">
+        <v>639</v>
+      </c>
+      <c r="C12" t="s">
         <v>640</v>
-      </c>
-      <c r="C12" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B13" t="s">
+        <v>641</v>
+      </c>
+      <c r="C13" t="s">
         <v>642</v>
-      </c>
-      <c r="C13" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B14" t="s">
+        <v>643</v>
+      </c>
+      <c r="C14" t="s">
         <v>644</v>
-      </c>
-      <c r="C14" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
+        <v>645</v>
+      </c>
+      <c r="B15" t="s">
         <v>646</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>647</v>
-      </c>
-      <c r="C15" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B16" t="s">
+        <v>648</v>
+      </c>
+      <c r="C16" t="s">
         <v>649</v>
-      </c>
-      <c r="C16" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B17" t="s">
+        <v>650</v>
+      </c>
+      <c r="C17" t="s">
         <v>651</v>
-      </c>
-      <c r="C17" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B18" t="s">
+        <v>652</v>
+      </c>
+      <c r="C18" t="s">
         <v>653</v>
-      </c>
-      <c r="C18" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B19" t="s">
+        <v>654</v>
+      </c>
+      <c r="C19" t="s">
         <v>655</v>
-      </c>
-      <c r="C19" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
+        <v>656</v>
+      </c>
+      <c r="B20" t="s">
         <v>657</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>658</v>
-      </c>
-      <c r="C20" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B21" t="s">
+        <v>659</v>
+      </c>
+      <c r="C21" t="s">
         <v>660</v>
-      </c>
-      <c r="C21" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B22" t="s">
+        <v>661</v>
+      </c>
+      <c r="C22" t="s">
         <v>662</v>
-      </c>
-      <c r="C22" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B23" t="s">
+        <v>663</v>
+      </c>
+      <c r="C23" t="s">
         <v>664</v>
-      </c>
-      <c r="C23" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B24" t="s">
+        <v>665</v>
+      </c>
+      <c r="C24" t="s">
         <v>666</v>
-      </c>
-      <c r="C24" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
+        <v>667</v>
+      </c>
+      <c r="B25" t="s">
         <v>668</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>669</v>
-      </c>
-      <c r="C25" t="s">
-        <v>670</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B26" t="s">
+        <v>670</v>
+      </c>
+      <c r="C26" t="s">
         <v>671</v>
-      </c>
-      <c r="C26" t="s">
-        <v>672</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B27" t="s">
+        <v>672</v>
+      </c>
+      <c r="C27" t="s">
         <v>673</v>
-      </c>
-      <c r="C27" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
+        <v>674</v>
+      </c>
+      <c r="B28" t="s">
         <v>675</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>676</v>
-      </c>
-      <c r="C28" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B29" t="s">
+        <v>677</v>
+      </c>
+      <c r="C29" t="s">
         <v>678</v>
-      </c>
-      <c r="C29" t="s">
-        <v>679</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B30" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C30" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
+        <v>680</v>
+      </c>
+      <c r="B31" t="s">
         <v>681</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>682</v>
-      </c>
-      <c r="C31" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B32" t="s">
+        <v>683</v>
+      </c>
+      <c r="C32" t="s">
         <v>684</v>
-      </c>
-      <c r="C32" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B33" t="s">
+        <v>681</v>
+      </c>
+      <c r="C33" t="s">
         <v>682</v>
-      </c>
-      <c r="C33" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B34" t="s">
+        <v>683</v>
+      </c>
+      <c r="C34" t="s">
         <v>684</v>
-      </c>
-      <c r="C34" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
+        <v>686</v>
+      </c>
+      <c r="B35" t="s">
         <v>687</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>688</v>
-      </c>
-      <c r="C35" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B36" t="s">
+        <v>689</v>
+      </c>
+      <c r="C36" t="s">
         <v>690</v>
-      </c>
-      <c r="C36" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
+        <v>691</v>
+      </c>
+      <c r="B37" t="s">
         <v>692</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>693</v>
-      </c>
-      <c r="C37" t="s">
-        <v>694</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B38" t="s">
+        <v>694</v>
+      </c>
+      <c r="C38" t="s">
         <v>695</v>
-      </c>
-      <c r="C38" t="s">
-        <v>696</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
+        <v>696</v>
+      </c>
+      <c r="B39" t="s">
         <v>697</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>698</v>
-      </c>
-      <c r="C39" t="s">
-        <v>699</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B40" t="s">
+        <v>699</v>
+      </c>
+      <c r="C40" t="s">
         <v>700</v>
-      </c>
-      <c r="C40" t="s">
-        <v>701</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B41" t="s">
+        <v>701</v>
+      </c>
+      <c r="C41" t="s">
         <v>702</v>
-      </c>
-      <c r="C41" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
+        <v>703</v>
+      </c>
+      <c r="B42" t="s">
         <v>704</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>705</v>
-      </c>
-      <c r="C42" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B43" t="s">
+        <v>706</v>
+      </c>
+      <c r="C43" t="s">
         <v>707</v>
-      </c>
-      <c r="C43" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B44" t="s">
+        <v>708</v>
+      </c>
+      <c r="C44" t="s">
         <v>709</v>
-      </c>
-      <c r="C44" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
+        <v>710</v>
+      </c>
+      <c r="B45" t="s">
         <v>711</v>
       </c>
-      <c r="B45" t="s">
-        <v>712</v>
-      </c>
       <c r="C45" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
+        <v>710</v>
+      </c>
+      <c r="B46" t="s">
+        <v>712</v>
+      </c>
+      <c r="C46" t="s">
+        <v>712</v>
+      </c>
+      <c r="D46" t="s">
         <v>711</v>
-      </c>
-      <c r="B46" t="s">
-        <v>713</v>
-      </c>
-      <c r="C46" t="s">
-        <v>713</v>
-      </c>
-      <c r="D46" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B47" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C47" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B48" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C48" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
+        <v>715</v>
+      </c>
+      <c r="B49" t="s">
         <v>716</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>717</v>
-      </c>
-      <c r="C49" t="s">
-        <v>718</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B50" t="s">
+        <v>718</v>
+      </c>
+      <c r="C50" t="s">
         <v>719</v>
-      </c>
-      <c r="C50" t="s">
-        <v>720</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B51" t="s">
+        <v>720</v>
+      </c>
+      <c r="C51" t="s">
         <v>721</v>
-      </c>
-      <c r="C51" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
+        <v>722</v>
+      </c>
+      <c r="B52" t="s">
         <v>723</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
         <v>724</v>
-      </c>
-      <c r="C52" t="s">
-        <v>725</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B53" t="s">
+        <v>725</v>
+      </c>
+      <c r="C53" t="s">
         <v>726</v>
-      </c>
-      <c r="C53" t="s">
-        <v>727</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B54" t="s">
+        <v>727</v>
+      </c>
+      <c r="C54" t="s">
         <v>728</v>
-      </c>
-      <c r="C54" t="s">
-        <v>729</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B55" t="s">
+        <v>725</v>
+      </c>
+      <c r="C55" t="s">
         <v>726</v>
-      </c>
-      <c r="C55" t="s">
-        <v>727</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B56" t="s">
+        <v>727</v>
+      </c>
+      <c r="C56" t="s">
         <v>728</v>
-      </c>
-      <c r="C56" t="s">
-        <v>729</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
+        <v>729</v>
+      </c>
+      <c r="B57" t="s">
         <v>730</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
         <v>731</v>
-      </c>
-      <c r="C57" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B58" t="s">
+        <v>681</v>
+      </c>
+      <c r="C58" t="s">
         <v>682</v>
-      </c>
-      <c r="C58" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B59" t="s">
+        <v>683</v>
+      </c>
+      <c r="C59" t="s">
         <v>684</v>
-      </c>
-      <c r="C59" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B60" t="s">
+        <v>681</v>
+      </c>
+      <c r="C60" t="s">
         <v>682</v>
-      </c>
-      <c r="C60" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B61" t="s">
+        <v>683</v>
+      </c>
+      <c r="C61" t="s">
         <v>684</v>
-      </c>
-      <c r="C61" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
+        <v>734</v>
+      </c>
+      <c r="B62" t="s">
         <v>735</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C62" t="s">
         <v>736</v>
-      </c>
-      <c r="C62" t="s">
-        <v>737</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B63" t="s">
+        <v>737</v>
+      </c>
+      <c r="C63" t="s">
         <v>738</v>
-      </c>
-      <c r="C63" t="s">
-        <v>739</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B64" t="s">
+        <v>739</v>
+      </c>
+      <c r="C64" t="s">
         <v>740</v>
-      </c>
-      <c r="C64" t="s">
-        <v>741</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B65" t="s">
+        <v>741</v>
+      </c>
+      <c r="C65" t="s">
         <v>742</v>
-      </c>
-      <c r="C65" t="s">
-        <v>743</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B66" t="s">
+        <v>681</v>
+      </c>
+      <c r="C66" t="s">
         <v>682</v>
-      </c>
-      <c r="C66" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B67" t="s">
+        <v>683</v>
+      </c>
+      <c r="C67" t="s">
         <v>684</v>
-      </c>
-      <c r="C67" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B68" t="s">
+        <v>735</v>
+      </c>
+      <c r="C68" t="s">
         <v>736</v>
-      </c>
-      <c r="C68" t="s">
-        <v>737</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B69" t="s">
+        <v>737</v>
+      </c>
+      <c r="C69" t="s">
         <v>738</v>
-      </c>
-      <c r="C69" t="s">
-        <v>739</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B70" t="s">
+        <v>739</v>
+      </c>
+      <c r="C70" t="s">
         <v>740</v>
-      </c>
-      <c r="C70" t="s">
-        <v>741</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B71" t="s">
+        <v>741</v>
+      </c>
+      <c r="C71" t="s">
         <v>742</v>
-      </c>
-      <c r="C71" t="s">
-        <v>743</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B72" t="s">
+        <v>681</v>
+      </c>
+      <c r="C72" t="s">
         <v>682</v>
-      </c>
-      <c r="C72" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B73" t="s">
+        <v>683</v>
+      </c>
+      <c r="C73" t="s">
         <v>684</v>
-      </c>
-      <c r="C73" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
+        <v>745</v>
+      </c>
+      <c r="B74" t="s">
         <v>746</v>
       </c>
-      <c r="B74" t="s">
+      <c r="C74" t="s">
         <v>747</v>
-      </c>
-      <c r="C74" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
+        <v>748</v>
+      </c>
+      <c r="B75" t="s">
         <v>749</v>
       </c>
-      <c r="B75" t="s">
+      <c r="C75" t="s">
         <v>750</v>
-      </c>
-      <c r="C75" t="s">
-        <v>751</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B76" t="s">
+        <v>751</v>
+      </c>
+      <c r="C76" t="s">
         <v>752</v>
-      </c>
-      <c r="C76" t="s">
-        <v>753</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B77" t="s">
+        <v>753</v>
+      </c>
+      <c r="C77" t="s">
         <v>754</v>
-      </c>
-      <c r="C77" t="s">
-        <v>755</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B78" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C78" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B79" t="s">
+        <v>681</v>
+      </c>
+      <c r="C79" t="s">
         <v>682</v>
-      </c>
-      <c r="C79" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B80" t="s">
+        <v>683</v>
+      </c>
+      <c r="C80" t="s">
         <v>684</v>
-      </c>
-      <c r="C80" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
+        <v>756</v>
+      </c>
+      <c r="B81" t="s">
         <v>757</v>
       </c>
-      <c r="B81" t="s">
+      <c r="C81" t="s">
         <v>758</v>
-      </c>
-      <c r="C81" t="s">
-        <v>759</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B82" t="s">
+        <v>759</v>
+      </c>
+      <c r="C82" t="s">
         <v>760</v>
-      </c>
-      <c r="C82" t="s">
-        <v>761</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B83" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C83" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
+        <v>761</v>
+      </c>
+      <c r="B84" t="s">
         <v>762</v>
       </c>
-      <c r="B84" t="s">
+      <c r="C84" t="s">
         <v>763</v>
-      </c>
-      <c r="C84" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B85" t="s">
+        <v>764</v>
+      </c>
+      <c r="C85" t="s">
         <v>765</v>
-      </c>
-      <c r="C85" t="s">
-        <v>766</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B86" t="s">
+        <v>766</v>
+      </c>
+      <c r="C86" t="s">
         <v>767</v>
-      </c>
-      <c r="C86" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B87" t="s">
+        <v>768</v>
+      </c>
+      <c r="C87" t="s">
         <v>769</v>
-      </c>
-      <c r="C87" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
+        <v>770</v>
+      </c>
+      <c r="B88" t="s">
         <v>771</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C88" t="s">
         <v>772</v>
-      </c>
-      <c r="C88" t="s">
-        <v>773</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B89" t="s">
+        <v>773</v>
+      </c>
+      <c r="C89" t="s">
         <v>774</v>
-      </c>
-      <c r="C89" t="s">
-        <v>775</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B90" t="s">
+        <v>775</v>
+      </c>
+      <c r="C90" t="s">
         <v>776</v>
-      </c>
-      <c r="C90" t="s">
-        <v>777</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B91" t="s">
+        <v>777</v>
+      </c>
+      <c r="C91" t="s">
         <v>778</v>
-      </c>
-      <c r="C91" t="s">
-        <v>779</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B92" t="s">
+        <v>779</v>
+      </c>
+      <c r="C92" t="s">
         <v>780</v>
-      </c>
-      <c r="C92" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
+        <v>781</v>
+      </c>
+      <c r="B93" t="s">
         <v>782</v>
       </c>
-      <c r="B93" t="s">
+      <c r="C93" t="s">
         <v>783</v>
-      </c>
-      <c r="C93" t="s">
-        <v>784</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B94" t="s">
+        <v>784</v>
+      </c>
+      <c r="C94" t="s">
         <v>785</v>
-      </c>
-      <c r="C94" t="s">
-        <v>786</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B95" t="s">
+        <v>786</v>
+      </c>
+      <c r="C95" t="s">
         <v>787</v>
-      </c>
-      <c r="C95" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B96" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C96" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="B97" t="s">
         <v>789</v>
       </c>
-      <c r="B97" t="s">
+      <c r="C97" t="s">
         <v>790</v>
-      </c>
-      <c r="C97" t="s">
-        <v>791</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B98" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="C98" t="s">
         <v>792</v>
-      </c>
-      <c r="C98" t="s">
-        <v>793</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B99" t="s">
+        <v>793</v>
+      </c>
+      <c r="C99" t="s">
         <v>794</v>
-      </c>
-      <c r="C99" t="s">
-        <v>795</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B100" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="C100" s="1" t="s">
         <v>796</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>797</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B101" t="s">
+        <v>681</v>
+      </c>
+      <c r="C101" t="s">
         <v>682</v>
-      </c>
-      <c r="C101" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B102" t="s">
+        <v>683</v>
+      </c>
+      <c r="C102" t="s">
         <v>684</v>
-      </c>
-      <c r="C102" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B103" t="s">
+        <v>681</v>
+      </c>
+      <c r="C103" t="s">
         <v>682</v>
-      </c>
-      <c r="C103" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B104" t="s">
+        <v>683</v>
+      </c>
+      <c r="C104" t="s">
         <v>684</v>
-      </c>
-      <c r="C104" t="s">
-        <v>685</v>
       </c>
     </row>
   </sheetData>
@@ -11441,12 +11421,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
   </sheetData>

--- a/surveys/biochar_survey_december_2025.xlsx
+++ b/surveys/biochar_survey_december_2025.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4749A2D0-5141-4F66-B9AF-FE73F9785B49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BA1293E6-5814-446F-9EEC-C8993CFA9364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2461" uniqueCount="801">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2456" uniqueCount="798">
   <si>
     <t>type</t>
   </si>
@@ -1628,22 +1628,13 @@
     <t>C.4) During the seasons you applied biochar, how often did you apply it?</t>
   </si>
   <si>
-    <t>select_multiple yw1ml89</t>
-  </si>
-  <si>
-    <t>fertilizer_before_biochar</t>
-  </si>
-  <si>
-    <t>C.5) Prior to the season when you applied biochar, did you use fertilizer on that plot? (Select all that apply)</t>
-  </si>
-  <si>
     <t>select_multiple pc1lg93</t>
   </si>
   <si>
     <t>fertilizers_used_before_biocha</t>
   </si>
   <si>
-    <t>C.6) What kind of fertilizer did you use before biochar? (Select all that apply)</t>
+    <t>C.5) What kind of fertilizer did you use before biochar? (Select all that apply)</t>
   </si>
   <si>
     <t>select_multiple td2jb01</t>
@@ -1652,7 +1643,7 @@
     <t>fertilizers_used_with_biochar</t>
   </si>
   <si>
-    <t>C.7) When you applied biochar, did you also use another soil fertilizer in addition to biochar? (Select all that apply)</t>
+    <t>C.6) When you applied biochar, did you also use another soil fertilizer in addition to biochar? (Select all that apply)</t>
   </si>
   <si>
     <t>group_ad9ws92</t>
@@ -2784,7 +2775,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F512"/>
+  <dimension ref="A1:F511"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.28515625" customWidth="1"/>
@@ -9797,29 +9788,29 @@
     </row>
     <row r="480" spans="1:6">
       <c r="A480" t="s">
-        <v>537</v>
-      </c>
-      <c r="B480" t="s">
-        <v>538</v>
-      </c>
-      <c r="C480" t="s">
-        <v>539</v>
-      </c>
-      <c r="D480" t="s">
-        <v>11</v>
-      </c>
-      <c r="E480" t="s">
-        <v>349</v>
+        <v>22</v>
       </c>
     </row>
     <row r="481" spans="1:5">
       <c r="A481" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B481" t="s">
+        <v>537</v>
+      </c>
+      <c r="C481" t="s">
+        <v>538</v>
+      </c>
+      <c r="D481" t="s">
+        <v>11</v>
+      </c>
+      <c r="E481" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="482" spans="1:5">
       <c r="A482" t="s">
-        <v>8</v>
+        <v>539</v>
       </c>
       <c r="B482" t="s">
         <v>540</v>
@@ -9829,9 +9820,6 @@
       </c>
       <c r="D482" t="s">
         <v>11</v>
-      </c>
-      <c r="E482" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="483" spans="1:5">
@@ -9847,39 +9835,39 @@
       <c r="D483" t="s">
         <v>11</v>
       </c>
+      <c r="E483" t="s">
+        <v>545</v>
+      </c>
     </row>
     <row r="484" spans="1:5">
       <c r="A484" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B484" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C484" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D484" t="s">
         <v>11</v>
       </c>
       <c r="E484" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="485" spans="1:5">
       <c r="A485" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B485" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C485" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D485" t="s">
         <v>11</v>
-      </c>
-      <c r="E485" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="486" spans="1:5">
@@ -9895,10 +9883,13 @@
       <c r="D486" t="s">
         <v>11</v>
       </c>
+      <c r="E486" t="s">
+        <v>556</v>
+      </c>
     </row>
     <row r="487" spans="1:5">
       <c r="A487" t="s">
-        <v>556</v>
+        <v>12</v>
       </c>
       <c r="B487" t="s">
         <v>557</v>
@@ -9909,13 +9900,10 @@
       <c r="D487" t="s">
         <v>11</v>
       </c>
-      <c r="E487" t="s">
-        <v>559</v>
-      </c>
     </row>
     <row r="488" spans="1:5">
       <c r="A488" t="s">
-        <v>12</v>
+        <v>559</v>
       </c>
       <c r="B488" t="s">
         <v>560</v>
@@ -9929,64 +9917,64 @@
     </row>
     <row r="489" spans="1:5">
       <c r="A489" t="s">
+        <v>12</v>
+      </c>
+      <c r="B489" t="s">
         <v>562</v>
       </c>
-      <c r="B489" t="s">
+      <c r="C489" t="s">
         <v>563</v>
       </c>
-      <c r="C489" t="s">
+      <c r="D489" t="s">
+        <v>11</v>
+      </c>
+      <c r="E489" t="s">
         <v>564</v>
-      </c>
-      <c r="D489" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="490" spans="1:5">
       <c r="A490" t="s">
-        <v>12</v>
+        <v>565</v>
       </c>
       <c r="B490" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C490" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D490" t="s">
         <v>11</v>
-      </c>
-      <c r="E490" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="491" spans="1:5">
       <c r="A491" t="s">
+        <v>12</v>
+      </c>
+      <c r="B491" t="s">
         <v>568</v>
       </c>
-      <c r="B491" t="s">
+      <c r="C491" t="s">
         <v>569</v>
       </c>
-      <c r="C491" t="s">
+      <c r="D491" t="s">
+        <v>11</v>
+      </c>
+      <c r="E491" t="s">
         <v>570</v>
-      </c>
-      <c r="D491" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="492" spans="1:5">
       <c r="A492" t="s">
-        <v>12</v>
+        <v>571</v>
       </c>
       <c r="B492" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C492" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D492" t="s">
         <v>11</v>
-      </c>
-      <c r="E492" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="493" spans="1:5">
@@ -10002,10 +9990,13 @@
       <c r="D493" t="s">
         <v>11</v>
       </c>
+      <c r="E493" t="s">
+        <v>577</v>
+      </c>
     </row>
     <row r="494" spans="1:5">
       <c r="A494" t="s">
-        <v>577</v>
+        <v>12</v>
       </c>
       <c r="B494" t="s">
         <v>578</v>
@@ -10022,24 +10013,24 @@
     </row>
     <row r="495" spans="1:5">
       <c r="A495" t="s">
-        <v>12</v>
-      </c>
-      <c r="B495" t="s">
-        <v>581</v>
-      </c>
-      <c r="C495" t="s">
-        <v>582</v>
-      </c>
-      <c r="D495" t="s">
-        <v>11</v>
-      </c>
-      <c r="E495" t="s">
-        <v>583</v>
+        <v>22</v>
       </c>
     </row>
     <row r="496" spans="1:5">
       <c r="A496" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B496" t="s">
+        <v>581</v>
+      </c>
+      <c r="C496" t="s">
+        <v>582</v>
+      </c>
+      <c r="D496" t="s">
+        <v>11</v>
+      </c>
+      <c r="E496" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="497" spans="1:5">
@@ -10047,24 +10038,21 @@
         <v>8</v>
       </c>
       <c r="B497" t="s">
-        <v>584</v>
-      </c>
-      <c r="C497" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="D497" t="s">
         <v>11</v>
-      </c>
-      <c r="E497" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="498" spans="1:5">
       <c r="A498" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B498" t="s">
-        <v>586</v>
+        <v>584</v>
+      </c>
+      <c r="C498" t="s">
+        <v>585</v>
       </c>
       <c r="D498" t="s">
         <v>11</v>
@@ -10072,7 +10060,7 @@
     </row>
     <row r="499" spans="1:5">
       <c r="A499" t="s">
-        <v>35</v>
+        <v>586</v>
       </c>
       <c r="B499" t="s">
         <v>587</v>
@@ -10086,13 +10074,13 @@
     </row>
     <row r="500" spans="1:5">
       <c r="A500" t="s">
+        <v>586</v>
+      </c>
+      <c r="B500" t="s">
         <v>589</v>
       </c>
-      <c r="B500" t="s">
+      <c r="C500" t="s">
         <v>590</v>
-      </c>
-      <c r="C500" t="s">
-        <v>591</v>
       </c>
       <c r="D500" t="s">
         <v>11</v>
@@ -10100,13 +10088,13 @@
     </row>
     <row r="501" spans="1:5">
       <c r="A501" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="B501" t="s">
+        <v>591</v>
+      </c>
+      <c r="C501" t="s">
         <v>592</v>
-      </c>
-      <c r="C501" t="s">
-        <v>593</v>
       </c>
       <c r="D501" t="s">
         <v>11</v>
@@ -10114,32 +10102,32 @@
     </row>
     <row r="502" spans="1:5">
       <c r="A502" t="s">
-        <v>589</v>
-      </c>
-      <c r="B502" t="s">
-        <v>594</v>
-      </c>
-      <c r="C502" t="s">
-        <v>595</v>
-      </c>
-      <c r="D502" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="503" spans="1:5">
       <c r="A503" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="B503" t="s">
+        <v>593</v>
+      </c>
+      <c r="C503" t="s">
+        <v>521</v>
+      </c>
+      <c r="D503" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="504" spans="1:5">
       <c r="A504" t="s">
-        <v>35</v>
+        <v>594</v>
       </c>
       <c r="B504" t="s">
+        <v>595</v>
+      </c>
+      <c r="C504" t="s">
         <v>596</v>
-      </c>
-      <c r="C504" t="s">
-        <v>521</v>
       </c>
       <c r="D504" t="s">
         <v>11</v>
@@ -10147,26 +10135,26 @@
     </row>
     <row r="505" spans="1:5">
       <c r="A505" t="s">
-        <v>597</v>
-      </c>
-      <c r="B505" t="s">
-        <v>598</v>
-      </c>
-      <c r="C505" t="s">
-        <v>599</v>
-      </c>
-      <c r="D505" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="506" spans="1:5">
       <c r="A506" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B506" t="s">
+        <v>597</v>
+      </c>
+      <c r="C506" t="s">
+        <v>598</v>
+      </c>
+      <c r="D506" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="507" spans="1:5">
       <c r="A507" t="s">
-        <v>8</v>
+        <v>599</v>
       </c>
       <c r="B507" t="s">
         <v>600</v>
@@ -10180,68 +10168,54 @@
     </row>
     <row r="508" spans="1:5">
       <c r="A508" t="s">
+        <v>12</v>
+      </c>
+      <c r="B508" t="s">
         <v>602</v>
       </c>
-      <c r="B508" t="s">
+      <c r="C508" t="s">
         <v>603</v>
       </c>
-      <c r="C508" t="s">
+      <c r="D508" t="s">
+        <v>11</v>
+      </c>
+      <c r="E508" t="s">
         <v>604</v>
-      </c>
-      <c r="D508" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="509" spans="1:5">
       <c r="A509" t="s">
-        <v>12</v>
+        <v>605</v>
       </c>
       <c r="B509" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C509" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D509" t="s">
         <v>11</v>
-      </c>
-      <c r="E509" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="510" spans="1:5">
       <c r="A510" t="s">
+        <v>12</v>
+      </c>
+      <c r="B510" t="s">
         <v>608</v>
       </c>
-      <c r="B510" t="s">
+      <c r="C510" t="s">
         <v>609</v>
       </c>
-      <c r="C510" t="s">
+      <c r="D510" t="s">
+        <v>11</v>
+      </c>
+      <c r="E510" t="s">
         <v>610</v>
-      </c>
-      <c r="D510" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="511" spans="1:5">
       <c r="A511" t="s">
-        <v>12</v>
-      </c>
-      <c r="B511" t="s">
-        <v>611</v>
-      </c>
-      <c r="C511" t="s">
-        <v>612</v>
-      </c>
-      <c r="D511" t="s">
-        <v>11</v>
-      </c>
-      <c r="E511" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="512" spans="1:5">
-      <c r="A512" t="s">
         <v>22</v>
       </c>
     </row>
@@ -10261,7 +10235,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -10270,1143 +10244,1143 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="B2" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C2" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
+        <v>613</v>
+      </c>
+      <c r="B3" t="s">
         <v>616</v>
       </c>
-      <c r="B3" t="s">
-        <v>619</v>
-      </c>
       <c r="C3" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="B4" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="C4" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
+        <v>618</v>
+      </c>
+      <c r="B5" t="s">
         <v>621</v>
       </c>
-      <c r="B5" t="s">
-        <v>624</v>
-      </c>
       <c r="C5" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="B6" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="C6" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="B7" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="C7" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="B8" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="C8" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="B9" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="C9" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="B10" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="C10" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="B11" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="C11" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
+        <v>633</v>
+      </c>
+      <c r="B12" t="s">
         <v>636</v>
       </c>
-      <c r="B12" t="s">
-        <v>639</v>
-      </c>
       <c r="C12" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="B13" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="C13" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="B14" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C14" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="B15" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C15" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
+        <v>642</v>
+      </c>
+      <c r="B16" t="s">
         <v>645</v>
       </c>
-      <c r="B16" t="s">
-        <v>648</v>
-      </c>
       <c r="C16" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="B17" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="C17" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="B18" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="C18" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="B19" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="C19" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="B20" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="C20" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
+        <v>653</v>
+      </c>
+      <c r="B21" t="s">
         <v>656</v>
       </c>
-      <c r="B21" t="s">
-        <v>659</v>
-      </c>
       <c r="C21" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="B22" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="C22" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="B23" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="C23" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="B24" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C24" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="B25" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="C25" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
+        <v>664</v>
+      </c>
+      <c r="B26" t="s">
         <v>667</v>
       </c>
-      <c r="B26" t="s">
-        <v>670</v>
-      </c>
       <c r="C26" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="B27" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="C27" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="B28" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="C28" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
+        <v>671</v>
+      </c>
+      <c r="B29" t="s">
         <v>674</v>
       </c>
-      <c r="B29" t="s">
-        <v>677</v>
-      </c>
       <c r="C29" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="B30" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="C30" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="B31" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="C31" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
+        <v>677</v>
+      </c>
+      <c r="B32" t="s">
         <v>680</v>
       </c>
-      <c r="B32" t="s">
-        <v>683</v>
-      </c>
       <c r="C32" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="B33" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="C33" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="B34" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="C34" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="B35" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="C35" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
+        <v>683</v>
+      </c>
+      <c r="B36" t="s">
         <v>686</v>
       </c>
-      <c r="B36" t="s">
-        <v>689</v>
-      </c>
       <c r="C36" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B37" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="C37" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
+        <v>688</v>
+      </c>
+      <c r="B38" t="s">
         <v>691</v>
       </c>
-      <c r="B38" t="s">
-        <v>694</v>
-      </c>
       <c r="C38" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="B39" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="C39" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
+        <v>693</v>
+      </c>
+      <c r="B40" t="s">
         <v>696</v>
       </c>
-      <c r="B40" t="s">
-        <v>699</v>
-      </c>
       <c r="C40" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="B41" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="C41" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="B42" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="C42" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
+        <v>700</v>
+      </c>
+      <c r="B43" t="s">
         <v>703</v>
       </c>
-      <c r="B43" t="s">
-        <v>706</v>
-      </c>
       <c r="C43" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="B44" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="C44" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B45" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="C45" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B46" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="C46" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="D46" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
+        <v>707</v>
+      </c>
+      <c r="B47" t="s">
         <v>710</v>
       </c>
-      <c r="B47" t="s">
-        <v>713</v>
-      </c>
       <c r="C47" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B48" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="C48" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="B49" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="C49" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
+        <v>712</v>
+      </c>
+      <c r="B50" t="s">
         <v>715</v>
       </c>
-      <c r="B50" t="s">
-        <v>718</v>
-      </c>
       <c r="C50" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="B51" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="C51" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="B52" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="C52" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
+        <v>719</v>
+      </c>
+      <c r="B53" t="s">
         <v>722</v>
       </c>
-      <c r="B53" t="s">
-        <v>725</v>
-      </c>
       <c r="C53" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="B54" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="C54" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="B55" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="C55" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="B56" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="C56" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="B57" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="C57" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="B58" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="C58" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="B59" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="C59" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="B60" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="C60" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="B61" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="C61" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="B62" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="C62" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
+        <v>731</v>
+      </c>
+      <c r="B63" t="s">
         <v>734</v>
       </c>
-      <c r="B63" t="s">
-        <v>737</v>
-      </c>
       <c r="C63" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="B64" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="C64" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="B65" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="C65" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="B66" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="C66" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="B67" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="C67" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="B68" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="C68" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="B69" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="C69" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="B70" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="C70" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="B71" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="C71" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="B72" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="C72" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="B73" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="C73" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="B74" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="C74" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="B75" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="C75" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
+        <v>745</v>
+      </c>
+      <c r="B76" t="s">
         <v>748</v>
       </c>
-      <c r="B76" t="s">
-        <v>751</v>
-      </c>
       <c r="C76" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="B77" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="C77" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="B78" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="C78" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="B79" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="C79" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="B80" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="C80" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="B81" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="C81" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
+        <v>753</v>
+      </c>
+      <c r="B82" t="s">
         <v>756</v>
       </c>
-      <c r="B82" t="s">
-        <v>759</v>
-      </c>
       <c r="C82" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="B83" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="C83" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="B84" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="C84" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
+        <v>758</v>
+      </c>
+      <c r="B85" t="s">
         <v>761</v>
       </c>
-      <c r="B85" t="s">
-        <v>764</v>
-      </c>
       <c r="C85" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="B86" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="C86" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="B87" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="C87" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="B88" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="C88" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
+        <v>767</v>
+      </c>
+      <c r="B89" t="s">
         <v>770</v>
       </c>
-      <c r="B89" t="s">
-        <v>773</v>
-      </c>
       <c r="C89" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="B90" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="C90" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="B91" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="C91" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="B92" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C92" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="B93" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="C93" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
+        <v>778</v>
+      </c>
+      <c r="B94" t="s">
         <v>781</v>
       </c>
-      <c r="B94" t="s">
-        <v>784</v>
-      </c>
       <c r="C94" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="B95" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="C95" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="B96" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="C96" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" s="1" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="B97" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="C97" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>788</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>791</v>
-      </c>
       <c r="C98" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" s="1" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="B99" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="C99" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" s="1" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="B101" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="C101" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="B102" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="C102" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="B103" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="C103" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="B104" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="C104" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
   </sheetData>
@@ -11421,12 +11395,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
     </row>
   </sheetData>
